--- a/Excel/Enterprises/Enterprise_CroppingCotton_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_CroppingCotton_Template_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\Enterprises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD8D776-13E4-46DC-8DF9-80ED9E8341B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37CE8981-2BA5-4F6C-9348-49CEB96E176F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1230" yWindow="180" windowWidth="36330" windowHeight="19485" activeTab="2" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1110" yWindow="465" windowWidth="36330" windowHeight="19485" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -18,10 +18,14 @@
     <sheet name="Results - Product EI" sheetId="80" r:id="rId3"/>
     <sheet name="Input - Site" sheetId="75" r:id="rId4"/>
     <sheet name="Input - Enterprise" sheetId="72" r:id="rId5"/>
-    <sheet name="Input - Fert Prod System" sheetId="76" r:id="rId6"/>
-    <sheet name="Input - Data quality" sheetId="78" r:id="rId7"/>
-    <sheet name="Constants - Common" sheetId="79" r:id="rId8"/>
+    <sheet name="Input - Crop" sheetId="81" r:id="rId6"/>
+    <sheet name="Input - Fert Prod System" sheetId="76" r:id="rId7"/>
+    <sheet name="Input - Data quality" sheetId="78" r:id="rId8"/>
+    <sheet name="Constants - Common" sheetId="79" r:id="rId9"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId10"/>
+  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -183,12 +187,12 @@
     <definedName name="Common_SourceData_DensityOfMethane_Data">'Constants - Common'!$D$175</definedName>
     <definedName name="CommonLivestock_InputFunctions.AverageLiveweightEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR([0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
-    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain" localSheetId="7">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain" localSheetId="8">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
-    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth" localSheetId="7">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth" localSheetId="8">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth">_xlfn.LAMBDA(_xlpm.HeadAtStart,_xlpm.Month,_xlpm.LivestockClass, _xlpm.HeadAtStart + [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) - [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
-    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth" localSheetId="7">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth" localSheetId="8">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStartOfMonth, MAX(_xlpm.HeadAtStartOfMonth - [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate,_xlpm.WeightAtMovementDate,_xlpm.Head, IFERROR(_xlpm.Head * (_xlpm.WeightAtMovementDate + [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownDuringMonthPerHead(_xlpm.LivestockClass, _xlpm.MovementDate)), 0))</definedName>
@@ -200,9 +204,9 @@
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) * CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightRemainingHead(_xlpm.Month, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, IFERROR(MIN(1, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth(_xlpm.HeadAtStart, _xlpm.Month, _xlpm.LivestockClass)), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadRemainingAtEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, IFERROR(MIN(1, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth(_xlpm.HeadAtStart, _xlpm.Month, _xlpm.LivestockClass)), 0))</definedName>
-    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth" localSheetId="7">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth" localSheetId="8">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
-    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth" localSheetId="7">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth" localSheetId="8">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonthAddedAndRemaining">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartTotal(_xlpm.LivestockClass, _xlpm.Month, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
     <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(19, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Symbol","Manure management system","";"1","Anaerobic lagoon","Anaerobic lagoon (m=1)";"2","Liquid systems","Liquid systems (m=2)";"3","Daily spread","Daily spread (m=3)";"3a","Sump and dispersal system","Sump and dispersal system (m=3a)";"3b","Drains to paddock","Drains to paddock (m=3b)";"4","Solid storage","Solid storage (m=4)";"5","Drylot (feed pad)","Drylot (feed pad) (m=5)";"6","Composting (passive windrow)","Composting (passive windrow) (m=6)";"7","Digester / covered lagoons","Digester / covered lagoons (m=7)";"8","Deep litter","Deep litter (m=8)";"9","Pit storage","Pit storage (m=9)";"10","Poultry manure with bedding","Poultry manure with bedding (m=10)";"11","Poultry manure without bedding","Poultry manure without bedding (m=11)";"11a","Belt manure removal","Belt manure removal (m=11a)";"11b","Manure stored in house","Manure stored in house (m=11b)";"12","Direct processing","Direct processing (m=12)";"13","Direct application","Direct application (m=13)";"14","Pasture range and paddock","Pasture range and paddock (m=14)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -232,6 +236,13 @@
     <definedName name="Result_Enterprise_Scope3_Method1">'Results - Activity period'!$H$51</definedName>
     <definedName name="Result_Enterprise_Scope3_Method2">'Results - Activity period'!$I$51</definedName>
     <definedName name="X_Cell_BaledHayYield">'Input - Enterprise'!$E$27</definedName>
+    <definedName name="X_Cell_Crop_AreaUnderCropping">'Input - Crop'!$E$12</definedName>
+    <definedName name="X_Cell_Crop_AverageWeightPerBale">'Input - Crop'!$E$34</definedName>
+    <definedName name="X_Cell_Crop_CropPurpose">'Input - Crop'!$E$10</definedName>
+    <definedName name="X_Cell_Crop_CropType">'Input - Crop'!$E$9</definedName>
+    <definedName name="X_Cell_Crop_PercentResidueBaled">'Input - Crop'!$E$33</definedName>
+    <definedName name="X_Cell_Crop_PercentResidueBurned">'Input - Crop'!$E$39</definedName>
+    <definedName name="X_Cell_Crop_TotalResidueBaled">'Input - Crop'!$E$36</definedName>
     <definedName name="X_Cell_Enterprise_GrainYield">'Input - Enterprise'!$E$22</definedName>
     <definedName name="X_Cell_Enterprise_PercentGrainSold">'Input - Enterprise'!$E$23</definedName>
     <definedName name="X_Cell_Enterprise_PercentGrainUsedAsFeed">'Input - Enterprise'!$E$24</definedName>
@@ -323,7 +334,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="335">
   <si>
     <t>Home</t>
   </si>
@@ -609,9 +620,9 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">← </t>
@@ -619,9 +630,9 @@
     <r>
       <rPr>
         <i/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>DD/MM/YYYY or DD Month YYYY</t>
@@ -630,9 +641,9 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">← </t>
@@ -640,9 +651,9 @@
     <r>
       <rPr>
         <i/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>Automatically calculated, 12 months after start date</t>
@@ -666,9 +677,9 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">← </t>
@@ -676,9 +687,9 @@
     <r>
       <rPr>
         <i/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>Please select</t>
@@ -1271,6 +1282,135 @@
   </si>
   <si>
     <t>Crop management</t>
+  </si>
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>If multiple paddocks were managed in the same way at the same time, you can enter information for them all together.</t>
+  </si>
+  <si>
+    <t>Yield</t>
+  </si>
+  <si>
+    <t>Residue management</t>
+  </si>
+  <si>
+    <t>Baled residue</t>
+  </si>
+  <si>
+    <t>Percentage of residue that was baled</t>
+  </si>
+  <si>
+    <t>Average weight per bale</t>
+  </si>
+  <si>
+    <t>Number of bales</t>
+  </si>
+  <si>
+    <t>Total residue baled</t>
+  </si>
+  <si>
+    <t>Burned residue</t>
+  </si>
+  <si>
+    <t>Percentage of residue that was burned</t>
+  </si>
+  <si>
+    <t>Total residue burned</t>
+  </si>
+  <si>
+    <t>Residue retained on paddocks</t>
+  </si>
+  <si>
+    <t>Cotton</t>
+  </si>
+  <si>
+    <t>Sprinkler irrigation</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <rFont val="Arial"/>
+        <family val="1"/>
+      </rPr>
+      <t>←</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <rFont val="Arial"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Please select</t>
+    </r>
+  </si>
+  <si>
+    <t>Turnout rate</t>
+  </si>
+  <si>
+    <t>Average weight per round module</t>
+  </si>
+  <si>
+    <t>kg / round module</t>
+  </si>
+  <si>
+    <t>round modules</t>
+  </si>
+  <si>
+    <t>Average amount of cottonseed produced per round module</t>
+  </si>
+  <si>
+    <t>lint bales / round module</t>
+  </si>
+  <si>
+    <t>Average weight per lint bale</t>
+  </si>
+  <si>
+    <t>kg / lint bale</t>
+  </si>
+  <si>
+    <t>Total number of round modules</t>
+  </si>
+  <si>
+    <t>round modules / ha</t>
+  </si>
+  <si>
+    <t>Round modules produced per hectare</t>
+  </si>
+  <si>
+    <t>Number of lint bales per round module</t>
+  </si>
+  <si>
+    <t>Residue:crop ratio</t>
+  </si>
+  <si>
+    <t>Tonnes</t>
+  </si>
+  <si>
+    <t>Percent</t>
+  </si>
+  <si>
+    <t>Kilograms</t>
+  </si>
+  <si>
+    <t>Bales</t>
+  </si>
+  <si>
+    <t>hectares</t>
+  </si>
+  <si>
+    <t>Total lint yield</t>
+  </si>
+  <si>
+    <t>Total unprocessed cotton yield (excluding trash)</t>
+  </si>
+  <si>
+    <t>Total cottonseed produced</t>
   </si>
 </sst>
 </file>
@@ -1289,108 +1429,106 @@
   </numFmts>
   <fonts count="55" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14996795556505021"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF533001"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
       <strike/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
       <i/>
       <strike/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
@@ -1401,219 +1539,217 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF008000"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1" tint="0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0" tint="-4.9989318521683403E-2"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1" tint="0.14996795556505021"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC44340"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="0" tint="-4.9989318521683403E-2"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="1" tint="0.14996795556505021"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFC44340"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF008000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
+      <sz val="10"/>
+      <color rgb="FFCC6600"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <u/>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <i/>
+      <sz val="9"/>
+      <color theme="6" tint="-0.499984740745262"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <i/>
+      <sz val="9"/>
+      <color theme="5" tint="-0.499984740745262"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="10"/>
-      <color theme="6" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="5" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
+      <sz val="9"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF242424"/>
       <name val="Consolas"/>
       <family val="3"/>
@@ -1621,34 +1757,34 @@
     <font>
       <sz val="9"/>
       <color rgb="FF404040"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FF0C769E"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
   </fonts>
@@ -2137,7 +2273,7 @@
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="8">
       <alignment horizontal="left" vertical="center"/>
@@ -2417,6 +2553,15 @@
     <xf numFmtId="170" fontId="27" fillId="4" borderId="0" xfId="8" applyNumberFormat="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="2" xfId="17">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="4" borderId="2" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="2" xfId="16" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="69">
     <cellStyle name="Alert" xfId="59" xr:uid="{34EFE908-8095-4010-8F93-8CFE88055637}"/>
@@ -2489,7 +2634,17 @@
     <cellStyle name="Variable type input" xfId="65" xr:uid="{69904D21-1566-4CAB-9A42-C86AC6535120}"/>
     <cellStyle name="Variable type other" xfId="64" xr:uid="{105BD9DE-B567-4DA0-87E6-C60A0ECC1C65}"/>
   </cellStyles>
-  <dxfs count="65">
+  <dxfs count="66">
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2501,11 +2656,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2525,11 +2679,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2549,11 +2702,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2573,11 +2725,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2597,11 +2748,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2621,11 +2771,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2645,11 +2794,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2669,11 +2817,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2693,11 +2840,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2717,11 +2863,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2741,11 +2886,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2765,11 +2909,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2789,11 +2932,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2813,11 +2955,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2837,11 +2978,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2861,11 +3001,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2885,11 +3024,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2909,11 +3047,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2933,11 +3070,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2957,11 +3093,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2981,11 +3116,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3005,11 +3139,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3029,11 +3162,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3053,11 +3185,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3077,11 +3208,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3101,11 +3231,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3125,11 +3254,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3149,11 +3277,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3173,11 +3300,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3197,11 +3323,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3221,11 +3346,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3245,11 +3369,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3269,11 +3392,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3293,11 +3415,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3317,11 +3438,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3341,11 +3461,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3365,11 +3484,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3389,11 +3507,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3413,11 +3530,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3437,11 +3553,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3461,11 +3576,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3712,20 +3826,20 @@
   </dxfs>
   <tableStyles count="3" defaultTableStyle="Equation table" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Editable table" pivot="0" count="6" xr9:uid="{8C498A1C-5864-4BF8-8739-A3055FE117E0}">
-      <tableStyleElement type="wholeTable" dxfId="64"/>
-      <tableStyleElement type="headerRow" dxfId="63"/>
-      <tableStyleElement type="totalRow" dxfId="62"/>
-      <tableStyleElement type="firstColumn" dxfId="61"/>
-      <tableStyleElement type="firstRowStripe" dxfId="60"/>
-      <tableStyleElement type="secondRowStripe" dxfId="59"/>
+      <tableStyleElement type="wholeTable" dxfId="65"/>
+      <tableStyleElement type="headerRow" dxfId="64"/>
+      <tableStyleElement type="totalRow" dxfId="63"/>
+      <tableStyleElement type="firstColumn" dxfId="62"/>
+      <tableStyleElement type="firstRowStripe" dxfId="61"/>
+      <tableStyleElement type="secondRowStripe" dxfId="60"/>
     </tableStyle>
     <tableStyle name="Equation table" pivot="0" count="6" xr9:uid="{B247698E-E41D-4CCD-AA0A-C14817E9DE65}">
-      <tableStyleElement type="wholeTable" dxfId="58"/>
-      <tableStyleElement type="headerRow" dxfId="57"/>
-      <tableStyleElement type="totalRow" dxfId="56"/>
-      <tableStyleElement type="firstColumn" dxfId="55"/>
-      <tableStyleElement type="firstRowStripe" dxfId="54"/>
-      <tableStyleElement type="secondRowStripe" dxfId="53"/>
+      <tableStyleElement type="wholeTable" dxfId="59"/>
+      <tableStyleElement type="headerRow" dxfId="58"/>
+      <tableStyleElement type="totalRow" dxfId="57"/>
+      <tableStyleElement type="firstColumn" dxfId="56"/>
+      <tableStyleElement type="firstRowStripe" dxfId="55"/>
+      <tableStyleElement type="secondRowStripe" dxfId="54"/>
     </tableStyle>
     <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{97B370DB-5463-4A31-9160-5A96BD6A559D}"/>
   </tableStyles>
@@ -3775,7 +3889,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -4437,7 +4551,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -4674,7 +4788,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -4811,7 +4925,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -6216,24 +6330,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{6496CA75-FED4-4E21-A81D-BDC20736B7B5}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6297,24 +6411,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{1A778010-8EF6-4986-9F7A-ED1F5F66D6A5}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6378,24 +6492,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{7DC837A9-60D0-4FEE-9D60-F5F33C8747DB}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6459,24 +6573,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{A1C4261C-1106-48B4-9C10-E82D60412011}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6540,24 +6654,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{AE965B10-5BD0-44CC-8118-41596A6F15E2}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6621,24 +6735,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{304D704D-8D75-4B25-B661-1CD4BF80A14D}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6701,16 +6815,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -6776,36 +6890,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -6871,18 +6985,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -6950,7 +7064,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1600">
+            <a:rPr lang="en-AU" sz="1400">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
@@ -7068,16 +7182,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -7143,36 +7257,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -7238,18 +7352,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 2</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -7417,16 +7531,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -7492,36 +7606,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -7587,18 +7701,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -7660,7 +7774,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -7684,7 +7798,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -7752,7 +7866,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1600">
+            <a:rPr lang="en-AU" sz="1400">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
@@ -7875,16 +7989,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -7950,36 +8064,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -8045,18 +8159,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 2</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8228,7 +8342,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8252,7 +8366,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8314,7 +8428,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8338,7 +8452,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8400,7 +8514,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8424,7 +8538,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8486,7 +8600,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8510,7 +8624,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8572,7 +8686,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8596,7 +8710,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8658,7 +8772,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8682,7 +8796,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8744,7 +8858,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8768,7 +8882,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8837,24 +8951,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{325659CC-BF18-4027-9C39-6B59F0E2F578}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -8918,24 +9032,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{A9E71E38-28CF-40B4-A787-CD2A933BF092}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -8999,24 +9113,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{FBAAA7CE-3F73-42A7-B887-E644937F7159}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -9080,24 +9194,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{E266E2BA-6A96-4903-9E52-5C6BCFEF9FF1}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -9161,24 +9275,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{F8F36783-2D83-448C-9BE3-D1653ADA37CE}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -9242,24 +9356,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{9792A2EE-0599-40C6-BEC6-FB928C51F2CA}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -9323,24 +9437,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{9FBD39D1-A40C-4D41-815F-1614BABEEB25}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -9404,24 +9518,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{48E1D669-5050-474F-B029-B219812AC417}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -9484,16 +9598,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -9559,36 +9673,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -9654,18 +9768,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -9733,7 +9847,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1600">
+            <a:rPr lang="en-AU" sz="1400">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
@@ -9851,16 +9965,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -9926,36 +10040,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -10021,18 +10135,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 2</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -10200,16 +10314,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -10275,36 +10389,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -10370,18 +10484,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -10443,7 +10557,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -10467,7 +10581,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -10535,7 +10649,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1600">
+            <a:rPr lang="en-AU" sz="1400">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
@@ -10658,16 +10772,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -10733,18 +10847,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 2</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -10916,7 +11030,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -10940,7 +11054,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -11002,7 +11116,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11026,7 +11140,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -11088,7 +11202,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11112,7 +11226,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -11174,7 +11288,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11198,7 +11312,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -11260,7 +11374,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11284,7 +11398,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -11346,7 +11460,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11370,7 +11484,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -11432,7 +11546,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11456,7 +11570,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -11525,24 +11639,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{B945A79A-D657-45FF-8794-B3F7FE79A7B2}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -11606,24 +11720,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{A0887E06-5564-4610-905A-7D5E4A0E50F4}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -11686,7 +11800,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="2000"/>
+            <a:rPr lang="en-AU" sz="1800"/>
             <a:t>Grain sold</a:t>
           </a:r>
         </a:p>
@@ -11823,7 +11937,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="2000"/>
+            <a:rPr lang="en-AU" sz="1800"/>
             <a:t>Baled hay/silage sold</a:t>
           </a:r>
         </a:p>
@@ -11943,6 +12057,92 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Overview"/>
+      <sheetName val="Results"/>
+      <sheetName val="Input - Site"/>
+      <sheetName val="Input - Crop"/>
+      <sheetName val="Input - Pasture"/>
+      <sheetName val="6.1.1.1-2 Crop residue N2O"/>
+      <sheetName val="6.2.1.1-2 Pasture residue N2O"/>
+      <sheetName val="6.3.1.1-2 Leaching and runoff"/>
+      <sheetName val="6.3.1.1-2 Leach runoff crop"/>
+      <sheetName val="6.3.1.1-2 Leach runoff pasture"/>
+      <sheetName val="6.4.1.1-2 Residue burning"/>
+      <sheetName val="Constants - Ag Residue"/>
+      <sheetName val="Constants - Common"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12">
+        <row r="8">
+          <cell r="D8" t="str">
+            <v>Cash grain crop</v>
+          </cell>
+          <cell r="E8" t="str">
+            <v>grain</v>
+          </cell>
+          <cell r="F8" t="str">
+            <v>yield</v>
+          </cell>
+          <cell r="G8" t="str">
+            <v>harvest</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="D9" t="str">
+            <v>Cash crop for hay/silage</v>
+          </cell>
+          <cell r="E9" t="str">
+            <v>above ground biomass</v>
+          </cell>
+          <cell r="F9" t="str">
+            <v>yield</v>
+          </cell>
+          <cell r="G9" t="str">
+            <v>harvest</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="D10" t="str">
+            <v>Cover crop</v>
+          </cell>
+          <cell r="E10" t="str">
+            <v>above ground biomass</v>
+          </cell>
+          <cell r="F10" t="str">
+            <v>mass</v>
+          </cell>
+          <cell r="G10" t="str">
+            <v>end of crop cycle</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="13" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12096,49 +12296,49 @@
     <tableColumn id="1" xr3:uid="{C292125F-3A0F-4FB3-9096-9A6C09064CE7}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{FD91884A-B7CC-43A5-89E2-EB9ADAD79B74}" name="MAT" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{FD91884A-B7CC-43A5-89E2-EB9ADAD79B74}" name="MAT" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B580D36E-E641-4419-A5E9-56AD94FD9711}" name="MAP" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{B580D36E-E641-4419-A5E9-56AD94FD9711}" name="MAP" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{0CE926DB-8FBB-46DD-B2F5-74DB63757391}" name="Frost days per year" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{0CE926DB-8FBB-46DD-B2F5-74DB63757391}" name="Frost days per year" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{47751D32-289E-4A5A-90B8-231DD67C9832}" name="Elevation" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{47751D32-289E-4A5A-90B8-231DD67C9832}" name="Elevation" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4F949F03-6B35-4E94-829B-0336C4645775}" name="MAP:PET" totalsRowDxfId="36" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{4F949F03-6B35-4E94-829B-0336C4645775}" name="MAP:PET" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3FBCB33B-842D-41D5-AD5F-83D615C11114}" name="Min temp" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{3FBCB33B-842D-41D5-AD5F-83D615C11114}" name="Min temp" totalsRowDxfId="36" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{C2619C9C-0794-4F06-A862-63A4C3CA66EC}" name="Max temp" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{C2619C9C-0794-4F06-A862-63A4C3CA66EC}" name="Max temp" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{FAF7977F-60AC-4F2F-AA73-CCFEA07FF532}" name="Min rainfall" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{FAF7977F-60AC-4F2F-AA73-CCFEA07FF532}" name="Min rainfall" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{D90DF110-8E64-41CE-9DF1-5AD24AE94500}" name="Max rainfall" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{D90DF110-8E64-41CE-9DF1-5AD24AE94500}" name="Max rainfall" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{1226E44E-433A-4C43-A126-43AC4AD90613}" name="Min frost days" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{1226E44E-433A-4C43-A126-43AC4AD90613}" name="Min frost days" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{39232AE3-3382-4B1D-A883-69EAEC386BCA}" name="Max frost days" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{39232AE3-3382-4B1D-A883-69EAEC386BCA}" name="Max frost days" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{59F4DDE6-C7E7-4BB5-BB18-F669A3EE8FF3}" name="Min elevation" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{59F4DDE6-C7E7-4BB5-BB18-F669A3EE8FF3}" name="Min elevation" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{72A56AAE-52D9-45B2-A13B-93D81D4FB64C}" name="Max elevation" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{72A56AAE-52D9-45B2-A13B-93D81D4FB64C}" name="Max elevation" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{EE7B4570-E79C-43AD-A951-1CDFABFAAADA}" name="Min MAP:PET" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{EE7B4570-E79C-43AD-A951-1CDFABFAAADA}" name="Min MAP:PET" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{A609D4ED-0384-43E1-9D16-AE8544F53232}" name="Max MAP:PET" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{A609D4ED-0384-43E1-9D16-AE8544F53232}" name="Max MAP:PET" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12156,7 +12356,7 @@
     <tableColumn id="1" xr3:uid="{4CF489C9-0C88-4CCB-A29C-4C5E0A706490}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{15DEBDB4-D8D7-40B9-83B3-DA303173B97A}" name="Wet or Dry Zone" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{15DEBDB4-D8D7-40B9-83B3-DA303173B97A}" name="Wet or Dry Zone" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12262,7 +12462,7 @@
     <tableColumn id="1" xr3:uid="{22C2C6AE-DA6F-4ADB-859F-88523E4E47DC}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{961AE704-9742-40C1-9D0C-522CDADB57B4}" name="FracWET" dataDxfId="24">
+    <tableColumn id="2" xr3:uid="{961AE704-9742-40C1-9D0C-522CDADB57B4}" name="FracWET" dataDxfId="25">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12308,8 +12508,8 @@
     <tableColumn id="2" xr3:uid="{8628A244-7FCA-4923-B809-B69CE86B5CDE}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{FAD9C63D-6E32-48F0-8A23-222E15F46B11}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{5EDBE82F-7B3C-458A-8638-8F86879CF287}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{58811FFB-FE3A-4DD8-BE53-E8CB588BCB77}" name="Notes" dataDxfId="52"/>
-    <tableColumn id="6" xr3:uid="{1219F6AC-7C79-4EDD-8C55-F7A78277AE3F}" name="Evidence files" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{58811FFB-FE3A-4DD8-BE53-E8CB588BCB77}" name="Notes" dataDxfId="53"/>
+    <tableColumn id="6" xr3:uid="{1219F6AC-7C79-4EDD-8C55-F7A78277AE3F}" name="Evidence files" dataDxfId="52"/>
     <tableColumn id="7" xr3:uid="{A201D4C4-5F18-4228-8444-52A30734BB16}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_Enterprise[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_Enterprise[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_Enterprise[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -12328,7 +12528,7 @@
     <tableColumn id="1" xr3:uid="{89B8C9C0-487C-456F-A38C-2227312F423D}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{76FEBB52-4BA8-4878-ABD5-A1D385C9CBB2}" name="FracWET" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{76FEBB52-4BA8-4878-ABD5-A1D385C9CBB2}" name="FracWET" dataDxfId="24" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12346,7 +12546,7 @@
     <tableColumn id="1" xr3:uid="{B3194017-8420-4A75-BF58-D94E8E366FA5}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DB7689A4-5F79-4DC6-AEDA-BD27AA7735DE}" name="EFPRP" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{DB7689A4-5F79-4DC6-AEDA-BD27AA7735DE}" name="EFPRP" dataDxfId="23" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12364,7 +12564,7 @@
     <tableColumn id="1" xr3:uid="{CFA27088-5584-4432-9EBF-9CC908BB3F73}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{562A242E-2C18-4700-B87C-BF0E6D72E55D}" name="Season" dataDxfId="21" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{562A242E-2C18-4700-B87C-BF0E6D72E55D}" name="Season" dataDxfId="22" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12396,49 +12596,49 @@
     <tableColumn id="1" xr3:uid="{B9C03558-7821-48FC-BA43-9E83FD9DD214}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AE651B1E-905B-4999-A25B-F342CDE64E0F}" name="MAT (ºC)" dataDxfId="20" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{AE651B1E-905B-4999-A25B-F342CDE64E0F}" name="MAT (ºC)" dataDxfId="21" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DB270A2A-6E0B-40B1-8BF5-FD175022D5E5}" name="Anaerobic lagoon" dataDxfId="19" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{DB270A2A-6E0B-40B1-8BF5-FD175022D5E5}" name="Anaerobic lagoon" dataDxfId="20" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{21E38317-525E-4A5B-86A6-35AD41B903A1}" name="Digester / covered lagoons" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{21E38317-525E-4A5B-86A6-35AD41B903A1}" name="Digester / covered lagoons" dataDxfId="19" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{017EAE1F-F1D4-4ECA-B2BF-27F27C0B710C}" name="Liquid systems" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{017EAE1F-F1D4-4ECA-B2BF-27F27C0B710C}" name="Liquid systems" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{8D7C0588-F29D-41D2-A4F1-2B6AE80CCB2F}" name="Daily spread" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{8D7C0588-F29D-41D2-A4F1-2B6AE80CCB2F}" name="Daily spread" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{2D7D514E-D604-458B-8BB0-C81C5E0B188D}" name="Composting (passive windrow)" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{2D7D514E-D604-458B-8BB0-C81C5E0B188D}" name="Composting (passive windrow)" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{F7536CDB-8030-4364-AAA8-EF005F5E86F7}" name="Solid storage" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{F7536CDB-8030-4364-AAA8-EF005F5E86F7}" name="Solid storage" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{9C345CB6-1C20-4DB9-BB29-CB0010CAD450}" name="Pit storage" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{9C345CB6-1C20-4DB9-BB29-CB0010CAD450}" name="Pit storage" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{124CEA8D-4055-4FCC-9831-B9F593B59067}" name="Deep litter" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{124CEA8D-4055-4FCC-9831-B9F593B59067}" name="Deep litter" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{BE546694-46BB-4C32-9C9E-789A7FB89886}" name="Poultry manure with bedding" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{BE546694-46BB-4C32-9C9E-789A7FB89886}" name="Poultry manure with bedding" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{12DFD68D-580C-4C50-B683-5DD09E98F6BA}" name="Poultry manure without bedding" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{12DFD68D-580C-4C50-B683-5DD09E98F6BA}" name="Poultry manure without bedding" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E5502853-37BF-4EF6-8B81-BFA61AB1A883}" name="Direct processing" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{E5502853-37BF-4EF6-8B81-BFA61AB1A883}" name="Direct processing" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{E4B91790-27EC-4CF9-8F1E-156D88349580}" name="Direct application" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{E4B91790-27EC-4CF9-8F1E-156D88349580}" name="Direct application" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{7B2BAB32-A63B-41E1-BE03-B2A6435DA45E}" name="Pasture range and paddock" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{7B2BAB32-A63B-41E1-BE03-B2A6435DA45E}" name="Pasture range and paddock" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{B52E7C0B-2A2F-4D94-B3EE-F55684FCD251}" name="MAT raw" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{B52E7C0B-2A2F-4D94-B3EE-F55684FCD251}" name="MAT raw" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12456,7 +12656,7 @@
     <tableColumn id="1" xr3:uid="{672554FB-5647-43EE-81BE-BD170F3983CE}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E3B7306-38E5-41D5-9D76-8FDBDD9AE302}" name="EFNi &amp; EFN2Oi" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{9E3B7306-38E5-41D5-9D76-8FDBDD9AE302}" name="EFNi &amp; EFN2Oi" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12473,8 +12673,8 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{67CB5F21-5858-42C0-820C-FA4341C92233}" name="User friendly description" dataDxfId="4" dataCellStyle="Content normal"/>
-    <tableColumn id="2" xr3:uid="{A467D3D2-FAE8-4B4F-AD2F-273B449008EF}" name="Description" dataDxfId="3" dataCellStyle="Content normal"/>
+    <tableColumn id="4" xr3:uid="{67CB5F21-5858-42C0-820C-FA4341C92233}" name="User friendly description" dataDxfId="5" dataCellStyle="Content normal"/>
+    <tableColumn id="2" xr3:uid="{A467D3D2-FAE8-4B4F-AD2F-273B449008EF}" name="Description" dataDxfId="4" dataCellStyle="Content normal"/>
     <tableColumn id="1" xr3:uid="{0177D8A5-3CAD-4019-91CC-E9E92C7CD148}" name="ID"/>
     <tableColumn id="3" xr3:uid="{D129B7D0-4F30-40BA-A6A7-54FEE1CB39A7}" name="Score"/>
   </tableColumns>
@@ -12491,7 +12691,7 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{E3087997-1A71-41E6-95DA-00D25217CB77}" name="User friendly description" dataDxfId="2" dataCellStyle="Content normal"/>
+    <tableColumn id="4" xr3:uid="{E3087997-1A71-41E6-95DA-00D25217CB77}" name="User friendly description" dataDxfId="3" dataCellStyle="Content normal"/>
     <tableColumn id="1" xr3:uid="{76CE025C-B272-4023-B793-440DED678242}" name="Description"/>
     <tableColumn id="2" xr3:uid="{7F57D207-1D4F-4A28-8836-C5DC431E1625}" name="ID"/>
     <tableColumn id="3" xr3:uid="{559F6435-AB23-47A3-B30E-D5E467BA68A8}" name="Score"/>
@@ -12509,7 +12709,7 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{DF638216-436F-4C10-B75A-DAAFFCC99904}" name="User friendly description" dataDxfId="1" dataCellStyle="Content normal"/>
+    <tableColumn id="4" xr3:uid="{DF638216-436F-4C10-B75A-DAAFFCC99904}" name="User friendly description" dataDxfId="2" dataCellStyle="Content normal"/>
     <tableColumn id="1" xr3:uid="{349901AD-9801-4819-B144-89B773FED959}" name="Description"/>
     <tableColumn id="2" xr3:uid="{BBC89306-46D2-4929-8947-68EE38366C09}" name="ID"/>
     <tableColumn id="3" xr3:uid="{865818AA-73D1-46C8-89D3-B389E9CADD7C}" name="Score"/>
@@ -12527,7 +12727,7 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{BA23F989-3F7E-4E10-B48D-200333055957}" name="User friendly description" dataDxfId="0" dataCellStyle="Content normal"/>
+    <tableColumn id="4" xr3:uid="{BA23F989-3F7E-4E10-B48D-200333055957}" name="User friendly description" dataDxfId="1" dataCellStyle="Content normal"/>
     <tableColumn id="1" xr3:uid="{55A1F1EC-210E-48D2-BED8-03D5FB58A9A5}" name="Description"/>
     <tableColumn id="2" xr3:uid="{4F17639D-3869-4472-8F9F-1819280657B0}" name="ID"/>
     <tableColumn id="3" xr3:uid="{77FE4131-90F7-4C8B-929C-08DA8DF35F1C}" name="Score"/>
@@ -12544,8 +12744,8 @@
     <tableColumn id="2" xr3:uid="{0E7A6865-A484-4EA8-BE54-5D641629A627}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{3E8C7762-D226-4D20-9E9C-87D78E3C44EB}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{4BFD5FBC-8263-4629-836C-DDA0F8DB50DF}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{E8075AB8-A4A6-48D2-A746-36F9CD68017F}" name="Notes" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{73F97399-8A3B-4EFB-9481-CBD7CB1C44EB}" name="Evidence files" dataDxfId="49"/>
+    <tableColumn id="5" xr3:uid="{E8075AB8-A4A6-48D2-A746-36F9CD68017F}" name="Notes" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{73F97399-8A3B-4EFB-9481-CBD7CB1C44EB}" name="Evidence files" dataDxfId="50"/>
     <tableColumn id="7" xr3:uid="{5C3D4C29-1D29-4869-8E15-91152F19AFCD}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_Site[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_Site[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_Site[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -12562,8 +12762,8 @@
     <tableColumn id="2" xr3:uid="{F15C1AF3-5D79-4EFF-A7BC-85CD71AF8BCF}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{E627CA70-3484-4F31-AEDF-45A8D9B88D5B}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{17EAABE4-C534-43AF-A841-58EDEBD26AB6}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{179CA6A6-4732-423D-BA28-31ED41FEC488}" name="Notes" dataDxfId="48"/>
-    <tableColumn id="6" xr3:uid="{865FA280-4A36-4101-BD09-20356916B4D5}" name="Evidence files" dataDxfId="47"/>
+    <tableColumn id="5" xr3:uid="{179CA6A6-4732-423D-BA28-31ED41FEC488}" name="Notes" dataDxfId="49"/>
+    <tableColumn id="6" xr3:uid="{865FA280-4A36-4101-BD09-20356916B4D5}" name="Evidence files" dataDxfId="48"/>
     <tableColumn id="7" xr3:uid="{399918FC-2F3F-431B-90D1-3CF016CF6FB7}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_PastureManagement[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_PastureManagement[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_PastureManagement[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -12580,8 +12780,8 @@
     <tableColumn id="2" xr3:uid="{D6C96F63-36E8-4824-8C95-BC4F6A076292}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{6D6CAE5E-4461-40B3-B8DC-047E72C1E057}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{1CF6EB6B-3987-44BA-AF58-FE9F4194D42F}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{2217AC95-A768-492F-A36E-74569D5596D4}" name="Notes" dataDxfId="46"/>
-    <tableColumn id="6" xr3:uid="{410620E5-5948-4B74-B5C6-B017CD8C09FE}" name="Evidence files" dataDxfId="45"/>
+    <tableColumn id="5" xr3:uid="{2217AC95-A768-492F-A36E-74569D5596D4}" name="Notes" dataDxfId="47"/>
+    <tableColumn id="6" xr3:uid="{410620E5-5948-4B74-B5C6-B017CD8C09FE}" name="Evidence files" dataDxfId="46"/>
     <tableColumn id="7" xr3:uid="{D000D4F8-1A71-478C-A273-A9B02C735D2D}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_FertiliserApplications[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FertiliserApplications[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FertiliserApplications[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -12598,8 +12798,8 @@
     <tableColumn id="2" xr3:uid="{BC53EBA0-F074-453F-8CEB-CA1F6ECC908D}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{443C80E7-5900-4A26-A586-B5571F50B9F7}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{C01B1081-DB35-4821-8766-E86DBB122E80}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{A1104D67-6CCD-4845-87B4-822F83200DD9}" name="Notes" dataDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{690D112F-6792-478E-99EE-B77B520B2164}" name="Evidence files" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{A1104D67-6CCD-4845-87B4-822F83200DD9}" name="Notes" dataDxfId="45"/>
+    <tableColumn id="6" xr3:uid="{690D112F-6792-478E-99EE-B77B520B2164}" name="Evidence files" dataDxfId="44"/>
     <tableColumn id="7" xr3:uid="{6CAA4E36-3A57-4A0B-8F59-4A9A9900E954}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_FuelElectricity[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FuelElectricity[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FuelElectricity[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -12616,8 +12816,8 @@
     <tableColumn id="2" xr3:uid="{4E3BAE35-86E5-4F71-98DC-491AD05B9B47}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{27B2AE81-8632-4140-9460-9C99650189CD}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{9C973ECC-975D-44BC-8B9B-BFC0C605F944}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{F255A018-D1E3-4FA7-9B50-4726EC2E2E56}" name="Notes" dataDxfId="42"/>
-    <tableColumn id="6" xr3:uid="{16D79CDB-80AA-4F28-B5E0-282205F97C41}" name="Evidence files" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{F255A018-D1E3-4FA7-9B50-4726EC2E2E56}" name="Notes" dataDxfId="43"/>
+    <tableColumn id="6" xr3:uid="{16D79CDB-80AA-4F28-B5E0-282205F97C41}" name="Evidence files" dataDxfId="42"/>
     <tableColumn id="7" xr3:uid="{73A8FFE4-648C-4FC3-BBE0-724E1B5D1A5A}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_FarmInputsFreightWaste[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FarmInputsFreightWaste[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FarmInputsFreightWaste[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -12705,12 +12905,12 @@
     </a:clrScheme>
     <a:fontScheme name="Custom 1">
       <a:majorFont>
-        <a:latin typeface="Times New Roman"/>
+        <a:latin typeface="Arial"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Times New Roman"/>
+        <a:latin typeface="Arial"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -12921,31 +13121,31 @@
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25" ht="30" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A3" s="82" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A6" s="83" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A7" s="5" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -12963,7 +13163,7 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:K87"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="2.7109375" customWidth="1"/>
@@ -12991,7 +13191,7 @@
       <c r="J1" s="93"/>
       <c r="K1" s="93"/>
     </row>
-    <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -13003,7 +13203,7 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -13018,7 +13218,7 @@
       <c r="J3" s="94"/>
       <c r="K3" s="94"/>
     </row>
-    <row r="4" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -13028,10 +13228,10 @@
         <v>Emissions breakdown for activities running between 01 January 2025 and 31 December 2025</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
     </row>
-    <row r="6" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>1</v>
       </c>
@@ -13039,13 +13239,13 @@
         <v>272</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Input - Pasture Beef'!A1", "Pasture Beef")</f>
         <v>Pasture Beef</v>
@@ -13070,7 +13270,7 @@
       </c>
       <c r="J8" s="12"/>
     </row>
-    <row r="9" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="D9" s="1" t="s">
         <v>134</v>
@@ -13098,7 +13298,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
@@ -13128,7 +13328,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.1-2 Methane'!A1", "4.2.1.1-2 Methane")</f>
         <v>4.2.1.1-2 Methane</v>
@@ -13159,7 +13359,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.3-4 Soil direct N2O'!A1", "4.2.1.3-4 Soil direct N2O")</f>
         <v>4.2.1.3-4 Soil direct N2O</v>
@@ -13190,7 +13390,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.5-6 Soil Atmos Dep'!A1", "4.2.1.5-6 Soil atm. deposition")</f>
         <v>4.2.1.5-6 Soil atm. deposition</v>
@@ -13221,7 +13421,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.7-8 Soil leach runoff'!A1", "4.2.1.7-8 Soil leach &amp; runoff")</f>
         <v>4.2.1.7-8 Soil leach &amp; runoff</v>
@@ -13252,7 +13452,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="D15" s="1" t="s">
         <v>174</v>
@@ -13280,7 +13480,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>2</v>
       </c>
@@ -13310,7 +13510,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="str">
         <f>HYPERLINK("#'Constants - Pasture Beef'!A1", "Constants - Pasture Beef")</f>
         <v>Constants - Pasture Beef</v>
@@ -13341,7 +13541,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="str">
         <f>HYPERLINK("#'Constants - Livestock'!A1", "Constants - Livestock")</f>
         <v>Constants - Livestock</v>
@@ -13372,7 +13572,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -13403,7 +13603,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -13434,7 +13634,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="1" t="s">
         <v>141</v>
       </c>
@@ -13461,7 +13661,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="D22" s="1" t="s">
         <v>143</v>
@@ -13489,7 +13689,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="D23" s="1" t="s">
         <v>144</v>
@@ -13517,7 +13717,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="D24" s="1" t="s">
         <v>145</v>
@@ -13545,7 +13745,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="1" t="s">
         <v>146</v>
       </c>
@@ -13572,7 +13772,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="1" t="s">
         <v>147</v>
       </c>
@@ -13599,7 +13799,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="88" t="s">
         <v>5</v>
       </c>
@@ -13618,15 +13818,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="80" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D32" s="12" t="s">
         <v>274</v>
       </c>
@@ -13647,7 +13847,7 @@
       </c>
       <c r="J32" s="12"/>
     </row>
-    <row r="33" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D33" s="1" t="e" cm="1">
         <f t="array" ref="D33">"14.1.1-2 Purchased electricity " &amp; IF(X_Cell_Electricity_CalculationMethod="Location-based (simpler)", "(Location-based)", "(Market-based)")</f>
         <v>#NAME?</v>
@@ -13675,7 +13875,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D34" s="88" t="s">
         <v>275</v>
       </c>
@@ -13694,15 +13894,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D37" s="80" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="38" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D39" s="12" t="s">
         <v>277</v>
       </c>
@@ -13723,7 +13923,7 @@
       </c>
       <c r="J39" s="12"/>
     </row>
-    <row r="40" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D40" s="1" t="s">
         <v>278</v>
       </c>
@@ -13750,7 +13950,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" s="1" t="s">
         <v>279</v>
       </c>
@@ -13777,7 +13977,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="1" t="s">
         <v>280</v>
       </c>
@@ -13804,7 +14004,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="1" t="s">
         <v>281</v>
       </c>
@@ -13831,7 +14031,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" s="1" t="s">
         <v>282</v>
       </c>
@@ -13858,7 +14058,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="1" t="s">
         <v>283</v>
       </c>
@@ -13885,7 +14085,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" s="1" t="s">
         <v>284</v>
       </c>
@@ -13912,7 +14112,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="1" t="e" cm="1">
         <f t="array" ref="D47">"15.12.1.1 Purchased electricity " &amp; IF(X_Cell_Electricity_CalculationMethod="Location-based (simpler)", "(Location-based)", "(Market-based)")</f>
         <v>#NAME?</v>
@@ -13940,7 +14140,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D48" s="1" t="s">
         <v>285</v>
       </c>
@@ -13967,7 +14167,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D49" s="1" t="s">
         <v>286</v>
       </c>
@@ -13994,7 +14194,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D50" s="1" t="s">
         <v>287</v>
       </c>
@@ -14021,7 +14221,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D51" s="88" t="s">
         <v>288</v>
       </c>
@@ -14040,16 +14240,16 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D54" s="80" t="str">
         <f>"Carbon removals from plantings for the activity period " &amp; TEXT(X_Cell_Site_StartDate, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Site_EndDate, "d mmmm yyyy")</f>
         <v>Carbon removals from plantings for the activity period 1 January 2025 and 31 December 2025</v>
       </c>
     </row>
-    <row r="55" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D56" s="88" t="s">
         <v>289</v>
       </c>
@@ -14061,16 +14261,16 @@
         <v>128</v>
       </c>
     </row>
-    <row r="57" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D59" s="80" t="str">
         <f>"Net emissions for the activity period " &amp; TEXT(X_Cell_Site_StartDate, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Site_EndDate, "d mmmm yyyy")</f>
         <v>Net emissions for the activity period 1 January 2025 and 31 December 2025</v>
       </c>
     </row>
-    <row r="60" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D61" s="12"/>
       <c r="E61" s="12" t="s">
         <v>131</v>
@@ -14080,7 +14280,7 @@
       </c>
       <c r="G61" s="12"/>
     </row>
-    <row r="62" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D62" s="97" t="s">
         <v>290</v>
       </c>
@@ -14096,7 +14296,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="63" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D63" s="97" t="s">
         <v>292</v>
       </c>
@@ -14112,30 +14312,30 @@
         <v>291</v>
       </c>
     </row>
-    <row r="64" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -14149,7 +14349,7 @@
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
   <dimension ref="A1:N58"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -14159,7 +14359,7 @@
     <col min="14" max="14" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="93" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" s="93" customFormat="1" ht="30" x14ac:dyDescent="0.35" customHeight="1">
       <c r="A1" s="11" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
@@ -14167,8 +14367,8 @@
         <v>295</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25" ht="20" customHeight="1"/>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C3" s="94"/>
       <c r="D3" s="94"/>
       <c r="E3" s="94"/>
@@ -14182,13 +14382,13 @@
       <c r="M3" s="94"/>
       <c r="N3" s="94"/>
     </row>
-    <row r="32" spans="4:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:4" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D32" s="2" t="str">
         <f>"Emissions for whole production cycle running between " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Emissions for whole production cycle running between 1 November 2025 and 31 March 2026</v>
       </c>
     </row>
-    <row r="35" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D35" s="12"/>
       <c r="E35" s="12" t="s">
         <v>131</v>
@@ -14198,7 +14398,7 @@
       </c>
       <c r="G35" s="12"/>
     </row>
-    <row r="36" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D36" s="78" t="s">
         <v>293</v>
       </c>
@@ -14214,7 +14414,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D37" s="78" t="s">
         <v>294</v>
       </c>
@@ -14230,18 +14430,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D39" s="2" t="str">
         <f>"Product emissions intensity for whole production cycle running between " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Product emissions intensity for whole production cycle running between 1 November 2025 and 31 March 2026</v>
       </c>
     </row>
-    <row r="42" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D42" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="43" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D43" s="12" t="s">
         <v>133</v>
       </c>
@@ -14264,20 +14464,20 @@
         <v>119</v>
       </c>
     </row>
-    <row r="44" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D44" s="1" t="s">
         <v>169</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F44" s="1" t="e">
+      <c r="F44" s="1">
         <f>X_Cell_Enterprise_GrainYield*X_Cell_Enterprise_PercentGrainSold</f>
-        <v>#NAME?</v>
+        <v>0</v>
       </c>
       <c r="G44" s="1" t="e">
         <f>F44/(F44+F47)</f>
-        <v>#NAME?</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H44" s="1" t="e">
         <f>(E36/F44)*G44</f>
@@ -14291,20 +14491,20 @@
         <v>161</v>
       </c>
     </row>
-    <row r="45" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D45" s="1" t="s">
         <v>170</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F45" s="1" t="e">
+      <c r="F45" s="1">
         <f>F44</f>
-        <v>#NAME?</v>
+        <v>0</v>
       </c>
       <c r="G45" s="1" t="e">
         <f>G44</f>
-        <v>#NAME?</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H45" s="1" t="e">
         <f>(E37/F45)*G45</f>
@@ -14318,16 +14518,16 @@
         <v>161</v>
       </c>
     </row>
-    <row r="46" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D46" s="1" t="s">
         <v>159</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F46" s="1" t="e">
+      <c r="F46" s="1">
         <f>X_Cell_Enterprise_GrainYield*X_Cell_Enterprise_PercentGrainUsedAsFeed</f>
-        <v>#NAME?</v>
+        <v>0</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>125</v>
@@ -14340,20 +14540,20 @@
       </c>
       <c r="J46" s="10"/>
     </row>
-    <row r="47" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D47" s="1" t="s">
         <v>171</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F47" s="1" t="e">
+      <c r="F47" s="1">
         <f>X_Cell_BaledHayYield*X_Cell_PercentBaledHaySold</f>
-        <v>#NAME?</v>
+        <v>0</v>
       </c>
       <c r="G47" s="1" t="e">
         <f>F47/(F44+F47)</f>
-        <v>#NAME?</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H47" s="1" t="e">
         <f>(E36/F47)*G47</f>
@@ -14367,20 +14567,20 @@
         <v>162</v>
       </c>
     </row>
-    <row r="48" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D48" s="1" t="s">
         <v>172</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F48" s="1" t="e">
+      <c r="F48" s="1">
         <f>F47</f>
-        <v>#NAME?</v>
+        <v>0</v>
       </c>
       <c r="G48" s="1" t="e">
         <f>G47</f>
-        <v>#NAME?</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H48" s="99" t="e">
         <f>(E37/F48)*G48</f>
@@ -14394,16 +14594,16 @@
         <v>162</v>
       </c>
     </row>
-    <row r="49" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D49" s="1" t="s">
         <v>160</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F49" s="1" t="e">
+      <c r="F49" s="1">
         <f>X_Cell_BaledHayYield*X_Cell_PercentBaledHayUsedOnFarm</f>
-        <v>#NAME?</v>
+        <v>0</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>125</v>
@@ -14416,12 +14616,12 @@
       </c>
       <c r="J49" s="10"/>
     </row>
-    <row r="51" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D51" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="52" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D52" s="12" t="s">
         <v>133</v>
       </c>
@@ -14444,16 +14644,16 @@
         <v>119</v>
       </c>
     </row>
-    <row r="53" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D53" s="1" t="s">
         <v>169</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F53" s="1" t="e">
+      <c r="F53" s="1">
         <f>X_Cell_Enterprise_GrainYield*X_Cell_Enterprise_PercentGrainSold</f>
-        <v>#NAME?</v>
+        <v>0</v>
       </c>
       <c r="G53" s="1">
         <f>X_Cell_Enterprise_PercentIncomeFromGrain</f>
@@ -14471,16 +14671,16 @@
         <v>161</v>
       </c>
     </row>
-    <row r="54" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D54" s="1" t="s">
         <v>170</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F54" s="1" t="e">
+      <c r="F54" s="1">
         <f>F53</f>
-        <v>#NAME?</v>
+        <v>0</v>
       </c>
       <c r="G54" s="1">
         <f>G53</f>
@@ -14498,16 +14698,16 @@
         <v>161</v>
       </c>
     </row>
-    <row r="55" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D55" s="1" t="s">
         <v>159</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F55" s="1" t="e">
+      <c r="F55" s="1">
         <f>X_Cell_Enterprise_GrainYield*X_Cell_Enterprise_PercentGrainUsedAsFeed</f>
-        <v>#NAME?</v>
+        <v>0</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>125</v>
@@ -14520,16 +14720,16 @@
       </c>
       <c r="J55" s="10"/>
     </row>
-    <row r="56" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D56" s="1" t="s">
         <v>171</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F56" s="1" t="e">
+      <c r="F56" s="1">
         <f>X_Cell_BaledHayYield*X_Cell_PercentBaledHaySold</f>
-        <v>#NAME?</v>
+        <v>0</v>
       </c>
       <c r="G56" s="1">
         <f>X_Cell_Enterprise_PercentIncomeFromGrain</f>
@@ -14547,16 +14747,16 @@
         <v>162</v>
       </c>
     </row>
-    <row r="57" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D57" s="1" t="s">
         <v>172</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F57" s="1" t="e">
+      <c r="F57" s="1">
         <f>F56</f>
-        <v>#NAME?</v>
+        <v>0</v>
       </c>
       <c r="G57" s="1">
         <f>G56</f>
@@ -14574,16 +14774,16 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D58" s="1" t="s">
         <v>160</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F58" s="1" t="e">
+      <c r="F58" s="1">
         <f>X_Cell_BaledHayYield*X_Cell_PercentBaledHayUsedOnFarm</f>
-        <v>#NAME?</v>
+        <v>0</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>125</v>
@@ -14609,7 +14809,7 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:AA115"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="4" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" style="23" customWidth="1"/>
@@ -14630,7 +14830,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:24" s="23" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="23" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -14641,7 +14841,7 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -14668,7 +14868,7 @@
       <c r="W3" s="25"/>
       <c r="X3" s="25"/>
     </row>
-    <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -14683,19 +14883,19 @@
       <c r="J4" s="31"/>
       <c r="K4" s="31"/>
     </row>
-    <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D5" s="2" t="s">
         <v>96</v>
       </c>
       <c r="N5" s="32"/>
     </row>
-    <row r="6" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>1</v>
       </c>
       <c r="N6" s="34"/>
     </row>
-    <row r="7" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
@@ -14707,7 +14907,7 @@
       <c r="F7" s="45"/>
       <c r="G7" s="46"/>
     </row>
-    <row r="8" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Input - Pasture Beef'!A1", "Pasture Beef")</f>
         <v>Pasture Beef</v>
@@ -14719,14 +14919,14 @@
       <c r="F8" s="48"/>
       <c r="G8" s="49"/>
     </row>
-    <row r="9" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="D9" s="1"/>
       <c r="E9" s="50"/>
       <c r="F9" s="17"/>
       <c r="N9" s="36"/>
     </row>
-    <row r="10" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
@@ -14741,7 +14941,7 @@
       </c>
       <c r="N10" s="36"/>
     </row>
-    <row r="11" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.1-2 Methane'!A1", "4.2.1.1-2 Methane")</f>
         <v>4.2.1.1-2 Methane</v>
@@ -14758,7 +14958,7 @@
       <c r="G11" s="1"/>
       <c r="N11" s="41"/>
     </row>
-    <row r="12" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.3-4 Soil direct N2O'!A1", "4.2.1.3-4 Soil direct N2O")</f>
         <v>4.2.1.3-4 Soil direct N2O</v>
@@ -14773,7 +14973,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.5-6 Soil Atmos Dep'!A1", "4.2.1.5-6 Soil atm. deposition")</f>
         <v>4.2.1.5-6 Soil atm. deposition</v>
@@ -14790,7 +14990,7 @@
       <c r="N13" s="43"/>
       <c r="O13" s="43"/>
     </row>
-    <row r="14" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.7-8 Soil leach runoff'!A1", "4.2.1.7-8 Soil leach &amp; runoff")</f>
         <v>4.2.1.7-8 Soil leach &amp; runoff</v>
@@ -14807,7 +15007,7 @@
       <c r="N14" s="43"/>
       <c r="O14" s="43"/>
     </row>
-    <row r="15" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="D15" s="1" t="s">
         <v>109</v>
@@ -14821,7 +15021,7 @@
       <c r="N15" s="43"/>
       <c r="O15" s="43"/>
     </row>
-    <row r="16" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>2</v>
       </c>
@@ -14837,7 +15037,7 @@
       <c r="N16" s="43"/>
       <c r="O16" s="43"/>
     </row>
-    <row r="17" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="str">
         <f>HYPERLINK("#'Constants - Pasture Beef'!A1", "Constants - Pasture Beef")</f>
         <v>Constants - Pasture Beef</v>
@@ -14852,7 +15052,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="str">
         <f>HYPERLINK("#'Constants - Livestock'!A1", "Constants - Livestock")</f>
         <v>Constants - Livestock</v>
@@ -14866,7 +15066,7 @@
       </c>
       <c r="F18" s="17"/>
     </row>
-    <row r="19" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -14881,7 +15081,7 @@
       <c r="G19" s="51"/>
       <c r="N19" s="32"/>
     </row>
-    <row r="20" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -14897,7 +15097,7 @@
       <c r="G20" s="50"/>
       <c r="N20" s="34"/>
     </row>
-    <row r="21" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="D21" s="1" t="s">
         <v>115</v>
@@ -14909,7 +15109,7 @@
       <c r="F21" s="1"/>
       <c r="G21" s="50"/>
     </row>
-    <row r="22" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="D22" s="1" t="s">
         <v>69</v>
@@ -14920,29 +15120,29 @@
       </c>
       <c r="G22" s="54"/>
     </row>
-    <row r="23" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
       <c r="N25" s="34"/>
     </row>
-    <row r="26" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
     </row>
-    <row r="27" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
     </row>
-    <row r="28" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
     </row>
-    <row r="29" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29"/>
     </row>
-    <row r="30" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
       <c r="L30" s="52"/>
       <c r="M30" s="52"/>
@@ -14959,7 +15159,7 @@
       <c r="X30" s="52"/>
       <c r="Y30" s="52"/>
     </row>
-    <row r="31" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31"/>
       <c r="L31" s="53"/>
       <c r="M31" s="53"/>
@@ -14976,7 +15176,7 @@
       <c r="X31" s="53"/>
       <c r="Y31" s="53"/>
     </row>
-    <row r="32" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32"/>
       <c r="L32" s="53"/>
       <c r="M32" s="53"/>
@@ -14993,7 +15193,7 @@
       <c r="X32" s="53"/>
       <c r="Y32" s="53"/>
     </row>
-    <row r="33" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33"/>
       <c r="L33" s="53"/>
       <c r="M33" s="53"/>
@@ -15010,7 +15210,7 @@
       <c r="X33" s="53"/>
       <c r="Y33" s="53"/>
     </row>
-    <row r="34" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34"/>
       <c r="J34" s="55"/>
       <c r="K34" s="56"/>
@@ -15029,7 +15229,7 @@
       <c r="X34" s="53"/>
       <c r="Y34" s="53"/>
     </row>
-    <row r="35" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35"/>
       <c r="J35" s="55"/>
       <c r="K35" s="56"/>
@@ -15048,7 +15248,7 @@
       <c r="X35" s="53"/>
       <c r="Y35" s="53"/>
     </row>
-    <row r="36" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
       <c r="D36" s="57"/>
       <c r="E36" s="57"/>
@@ -15073,7 +15273,7 @@
       <c r="X36" s="53"/>
       <c r="Y36" s="53"/>
     </row>
-    <row r="37" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="D37" s="57"/>
       <c r="E37" s="57"/>
@@ -15098,7 +15298,7 @@
       <c r="X37" s="53"/>
       <c r="Y37" s="53"/>
     </row>
-    <row r="38" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
       <c r="D38" s="57"/>
       <c r="E38" s="57"/>
@@ -15123,7 +15323,7 @@
       <c r="X38" s="53"/>
       <c r="Y38" s="53"/>
     </row>
-    <row r="39" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
       <c r="D39" s="57"/>
       <c r="E39" s="57"/>
@@ -15148,7 +15348,7 @@
       <c r="X39" s="53"/>
       <c r="Y39" s="53"/>
     </row>
-    <row r="40" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="D40" s="60"/>
       <c r="E40" s="60"/>
@@ -15173,104 +15373,104 @@
       <c r="X40" s="63"/>
       <c r="Y40" s="63"/>
     </row>
-    <row r="41" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
     </row>
-    <row r="42" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42"/>
     </row>
-    <row r="43" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43"/>
     </row>
-    <row r="44" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="2"/>
     </row>
-    <row r="46" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="64"/>
       <c r="E47" s="64"/>
       <c r="F47" s="64"/>
       <c r="G47" s="64"/>
       <c r="H47" s="64"/>
     </row>
-    <row r="48" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D48" s="65"/>
       <c r="E48" s="65"/>
       <c r="F48" s="66"/>
       <c r="G48" s="66"/>
       <c r="H48" s="65"/>
     </row>
-    <row r="49" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D49" s="65"/>
       <c r="E49" s="65"/>
       <c r="F49" s="66"/>
       <c r="G49" s="66"/>
       <c r="H49" s="65"/>
     </row>
-    <row r="50" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D50" s="65"/>
       <c r="E50" s="65"/>
       <c r="F50" s="66"/>
       <c r="G50" s="66"/>
       <c r="H50" s="65"/>
     </row>
-    <row r="51" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D51" s="67"/>
       <c r="E51" s="68"/>
       <c r="F51" s="68"/>
       <c r="G51" s="68"/>
       <c r="H51" s="69"/>
     </row>
-    <row r="52" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G54" s="70"/>
     </row>
-    <row r="55" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D55" s="2"/>
     </row>
-    <row r="56" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D57" s="71"/>
       <c r="F57" s="72"/>
     </row>
-    <row r="58" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D58" s="1"/>
       <c r="E58" s="73"/>
     </row>
-    <row r="59" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D59" s="1"/>
       <c r="E59" s="73"/>
     </row>
-    <row r="60" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D60" s="1"/>
       <c r="E60" s="74"/>
     </row>
-    <row r="61" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D61" s="1"/>
     </row>
-    <row r="62" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D63" s="71"/>
     </row>
-    <row r="64" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D64" s="1"/>
       <c r="E64" s="73"/>
     </row>
-    <row r="65" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D65" s="1"/>
       <c r="E65" s="73"/>
     </row>
-    <row r="66" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D66" s="1"/>
       <c r="E66" s="74"/>
     </row>
-    <row r="67" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D69" s="75"/>
       <c r="E69" s="75"/>
       <c r="F69" s="75"/>
@@ -15278,7 +15478,7 @@
       <c r="H69" s="75"/>
       <c r="I69" s="75"/>
     </row>
-    <row r="70" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D70" s="75"/>
       <c r="E70" s="75"/>
       <c r="F70" s="75"/>
@@ -15286,7 +15486,7 @@
       <c r="H70" s="75"/>
       <c r="I70" s="75"/>
     </row>
-    <row r="71" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D71" s="75"/>
       <c r="E71" s="75"/>
       <c r="F71" s="75"/>
@@ -15294,7 +15494,7 @@
       <c r="H71" s="75"/>
       <c r="I71" s="75"/>
     </row>
-    <row r="72" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D72" s="75"/>
       <c r="E72" s="75"/>
       <c r="F72" s="75"/>
@@ -15302,59 +15502,59 @@
       <c r="H72" s="75"/>
       <c r="I72" s="75"/>
     </row>
-    <row r="73" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D78" s="76"/>
     </row>
-    <row r="79" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D79" s="76"/>
     </row>
-    <row r="80" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D80" s="76"/>
     </row>
-    <row r="81" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D81" s="76"/>
     </row>
-    <row r="82" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D82" s="76"/>
     </row>
-    <row r="83" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E12" xr:uid="{620909BD-05B7-4260-BB85-4888DFAEE1F3}">
@@ -15380,7 +15580,7 @@
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
   <dimension ref="C1:J83"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -15391,7 +15591,7 @@
     <col min="11" max="11" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:10" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="3:10" ht="30" x14ac:dyDescent="0.35" customHeight="1">
       <c r="C1" s="29" t="s">
         <v>148</v>
       </c>
@@ -15403,7 +15603,7 @@
       <c r="I1" s="23"/>
       <c r="J1" s="23"/>
     </row>
-    <row r="2" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -15413,7 +15613,7 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="3:10" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C3" s="30"/>
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
@@ -15423,7 +15623,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="5" spans="3:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D5" s="2" t="s">
         <v>88</v>
       </c>
@@ -15431,13 +15631,13 @@
       <c r="F5" s="26"/>
       <c r="G5" s="26"/>
     </row>
-    <row r="6" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D6" s="33"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
       <c r="G6" s="26"/>
     </row>
-    <row r="7" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D7" s="1" t="s">
         <v>89</v>
       </c>
@@ -15447,7 +15647,7 @@
       <c r="F7" s="17"/>
       <c r="G7" s="26"/>
     </row>
-    <row r="8" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D8" s="13" t="s">
         <v>91</v>
       </c>
@@ -15457,13 +15657,13 @@
       <c r="F8" s="26"/>
       <c r="G8" s="26"/>
     </row>
-    <row r="9" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D9" s="26"/>
       <c r="E9" s="26"/>
       <c r="F9" s="26"/>
       <c r="G9" s="26"/>
     </row>
-    <row r="10" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D10" s="37" t="s">
         <v>93</v>
       </c>
@@ -15471,13 +15671,13 @@
       <c r="F10" s="39"/>
       <c r="G10" s="40"/>
     </row>
-    <row r="11" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D11" s="26"/>
       <c r="E11" s="26"/>
       <c r="F11" s="26"/>
       <c r="G11" s="26"/>
     </row>
-    <row r="12" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D12" s="13" t="s">
         <v>17</v>
       </c>
@@ -15489,7 +15689,7 @@
       </c>
       <c r="G12" s="26"/>
     </row>
-    <row r="13" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D13" s="13" t="s">
         <v>18</v>
       </c>
@@ -15502,16 +15702,16 @@
       </c>
       <c r="G13" s="26"/>
     </row>
-    <row r="14" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="F14" s="26"/>
       <c r="G14" s="26"/>
     </row>
-    <row r="16" spans="3:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D16" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D18" s="1" t="s">
         <v>14</v>
       </c>
@@ -15522,7 +15722,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D19" s="1" t="s">
         <v>15</v>
       </c>
@@ -15533,7 +15733,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="20" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D20" s="1" t="s">
         <v>16</v>
       </c>
@@ -15545,19 +15745,19 @@
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D22" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E22" s="79" t="e" cm="1">
+      <c r="E22" s="79" cm="1">
         <f t="array" ref="E22">IF(X_Cell_Crop_CropPurpose = "Cash grain crop", X_Cell_Crop_TotalProductionOfCrop, 0)</f>
-        <v>#NAME?</v>
+        <v>0</v>
       </c>
       <c r="F22" s="17" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D23" s="1" t="s">
         <v>154</v>
       </c>
@@ -15568,7 +15768,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="24" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D24" s="1" t="s">
         <v>155</v>
       </c>
@@ -15579,7 +15779,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="25" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D25" s="1" t="s">
         <v>156</v>
       </c>
@@ -15591,19 +15791,19 @@
         <v>149</v>
       </c>
     </row>
-    <row r="27" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D27" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="E27" s="79" t="e" cm="1">
+      <c r="E27" s="79" cm="1">
         <f t="array" ref="E27">X_Cell_Crop_TotalResidueBaled</f>
-        <v>#NAME?</v>
+        <v>0</v>
       </c>
       <c r="F27" s="17" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D28" s="1" t="s">
         <v>157</v>
       </c>
@@ -15614,7 +15814,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="29" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D29" s="1" t="s">
         <v>158</v>
       </c>
@@ -15625,7 +15825,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="30" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D30" s="1" t="s">
         <v>156</v>
       </c>
@@ -15637,7 +15837,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="32" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D32" s="1" t="s">
         <v>151</v>
       </c>
@@ -15648,7 +15848,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="33" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D33" s="1" t="s">
         <v>153</v>
       </c>
@@ -15659,18 +15859,18 @@
         <v>149</v>
       </c>
     </row>
-    <row r="36" spans="4:7" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D36" s="2" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="39" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D39" s="80" t="str">
         <f>"Carbon captured from " &amp; TEXT(X_Cell_Site_StartDate, "d mmmm yyyy") &amp; " to " &amp; TEXT(X_Cell_Site_EndDate, "d, mmmm, yyyy") &amp; " from environmental plantings"</f>
         <v>Carbon captured from 1 January 2025 to 31, December, 2025 from environmental plantings</v>
       </c>
     </row>
-    <row r="41" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D41" s="21" t="s">
         <v>266</v>
       </c>
@@ -15684,7 +15884,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="42" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D42" s="35"/>
       <c r="E42" s="77"/>
       <c r="F42" s="19"/>
@@ -15693,29 +15893,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="4:7" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D46" s="2" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="48" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D48" s="80" t="str">
         <f>"Gross emissions from other activity periods in the production timeframe " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " to " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Gross emissions from other activity periods in the production timeframe 1 November 2025 to 31 March 2026</v>
       </c>
     </row>
-    <row r="50" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D50" s="90" t="str" cm="1">
         <f t="array" ref="D50">"There are " &amp; Common_InputFunctions.getOverlappingReportingCycles(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate) &amp; " emissions calculation periods that need to be completed before total product emissions can be determined."</f>
         <v>There are 2 emissions calculation periods that need to be completed before total product emissions can be determined.</v>
       </c>
     </row>
-    <row r="51" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D51" s="1" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="53" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D53" s="81" t="s">
         <v>116</v>
       </c>
@@ -15726,7 +15926,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D54" s="1" t="str" cm="1">
         <f t="array" ref="D54:D55">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
         <v>01 Jan 2025 to 31 Dec 2025 (This reporting cycle)</v>
@@ -15743,7 +15943,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D55" s="1" t="str">
         <v>01 Jan 2026 to 31 Dec 2026</v>
       </c>
@@ -15759,7 +15959,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E56" s="77">
         <f>IF(ISBLANK($D56), 0, IF(ISNUMBER(SEARCH("reporting", $D56)), Result_Enterprise_Gross_Method1, "Enter value"))</f>
         <v>0</v>
@@ -15772,7 +15972,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E57" s="77">
         <f>IF(ISBLANK($D57), 0, IF(ISNUMBER(SEARCH("reporting", $D57)), Result_Enterprise_Gross_Method1, "Enter value"))</f>
         <v>0</v>
@@ -15785,7 +15985,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E58" s="77">
         <f>IF(ISBLANK($D58), 0, IF(ISNUMBER(SEARCH("reporting", $D58)), Result_Enterprise_Gross_Method1, "Enter value"))</f>
         <v>0</v>
@@ -15798,7 +15998,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D59" s="91" t="s">
         <v>129</v>
       </c>
@@ -15814,13 +16014,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D64" s="80" t="str">
         <f>"Carbon removals from environmental plantings for whole production cycle running between " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Carbon removals from environmental plantings for whole production cycle running between 1 November 2025 and 31 March 2026</v>
       </c>
     </row>
-    <row r="66" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D66" s="81" t="s">
         <v>116</v>
       </c>
@@ -15829,7 +16029,7 @@
       </c>
       <c r="F66" s="81"/>
     </row>
-    <row r="67" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D67" s="1" t="str" cm="1">
         <f t="array" ref="D67:D68">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
         <v>01 Jan 2025 to 31 Dec 2025 (This reporting cycle)</v>
@@ -15842,7 +16042,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="68" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D68" s="1" t="str">
         <v>01 Jan 2026 to 31 Dec 2026</v>
       </c>
@@ -15854,7 +16054,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="69" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E69" s="77">
         <f>IF(ISBLANK($D69), 0, IF(ISNUMBER(SEARCH("reporting", $D69)), SUM(Table_Input_Enterprise_PlantingRemovals[Removal allocated to this enterprise]), "Enter value"))</f>
         <v>0</v>
@@ -15863,7 +16063,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="70" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E70" s="77">
         <f>IF(ISBLANK($D70), 0, IF(ISNUMBER(SEARCH("reporting", $D70)), SUM(Table_Input_Enterprise_PlantingRemovals[Removal allocated to this enterprise]), "Enter value"))</f>
         <v>0</v>
@@ -15872,7 +16072,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="71" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E71" s="77">
         <f>IF(ISBLANK($D71), 0, IF(ISNUMBER(SEARCH("reporting", $D71)), SUM(Table_Input_Enterprise_PlantingRemovals[Removal allocated to this enterprise]), "Enter value"))</f>
         <v>0</v>
@@ -15881,7 +16081,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="72" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D72" s="91" t="s">
         <v>130</v>
       </c>
@@ -15893,13 +16093,13 @@
         <v>128</v>
       </c>
     </row>
-    <row r="75" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D75" s="80" t="str">
         <f>"Net emissions from other activity periods in the production timeframe " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " to " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Net emissions from other activity periods in the production timeframe 1 November 2025 to 31 March 2026</v>
       </c>
     </row>
-    <row r="77" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D77" s="81" t="s">
         <v>116</v>
       </c>
@@ -15910,7 +16110,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D78" s="1" t="str" cm="1">
         <f t="array" ref="D78:D79">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
         <v>01 Jan 2025 to 31 Dec 2025 (This reporting cycle)</v>
@@ -15927,7 +16127,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D79" s="1" t="str">
         <v>01 Jan 2026 to 31 Dec 2026</v>
       </c>
@@ -15943,7 +16143,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E80" s="77">
         <f>IF(ISBLANK($D80), 0, IF(ISNUMBER(SEARCH("reporting", $D80)), E56-$E$69, "Enter value"))</f>
         <v>0</v>
@@ -15956,7 +16156,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E81" s="77">
         <f>IF(ISBLANK($D81), 0, IF(ISNUMBER(SEARCH("reporting", $D81)), E57-$E$70, "Enter value"))</f>
         <v>0</v>
@@ -15969,7 +16169,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E82" s="77">
         <f>IF(ISBLANK($D82), 0, IF(ISNUMBER(SEARCH("reporting", $D82)), E58-$E$71, "Enter value"))</f>
         <v>0</v>
@@ -15982,7 +16182,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D83" s="91" t="s">
         <v>129</v>
       </c>
@@ -16007,30 +16207,25 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECD198B5-7ECE-40EA-8499-B24C208F76C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B55358B0-3547-450A-B366-699B2B08FF33}">
   <sheetPr>
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="C1:K59"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" style="1" customWidth="1"/>
-    <col min="4" max="10" width="30.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="59.5703125" style="1" customWidth="1"/>
+    <col min="5" max="10" width="30.7109375" style="1" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="11" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:11" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="3:11" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.35" customHeight="1"/>
+    <row r="2" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="30"/>
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
@@ -16041,7 +16236,371 @@
       <c r="J3" s="30"/>
       <c r="K3" s="30"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D5" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="6" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D7" s="71" t="s">
+        <v>299</v>
+      </c>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+    </row>
+    <row r="8" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D9" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="10" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D10" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="11" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D12" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E12" s="100">
+        <v>1000</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="13" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D14" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="15" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D16" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="E16" s="77">
+        <v>2</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="17" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D17" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E17" s="16">
+        <f>X_Cell_Crop_AreaUnderCropping*E16</f>
+        <v>2000</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="18" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D18" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="E18" s="77">
+        <v>4.41</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="19" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D19" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="E19" s="77">
+        <v>227</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="20" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D20" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E20" s="16">
+        <f>(E17*E18)*E19*10^-3</f>
+        <v>2002.14</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D21" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="E21" s="102">
+        <v>0.41839999999999999</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="22" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D22" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E22" s="16">
+        <f>(E19*E18)/E21</f>
+        <v>2392.6147227533461</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="23" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D24" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E24" s="77">
+        <v>250</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="25" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D25" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E25" s="16">
+        <f>E24*E17*10^-3</f>
+        <v>500</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D27" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="28" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D28" s="78"/>
+    </row>
+    <row r="29" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D29" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="E29" s="16" cm="1">
+        <f t="array" ref="E29">Common_InputFunctions.Utility_LookupValueInTableNumber(X_Cell_Crop_CropType, [1]!Table_SourceData_CropAttributes[Crop type],[1]!Table_SourceData_CropAttributes[Residue: Crop ratio])</f>
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="30" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D30" s="90"/>
+    </row>
+    <row r="31" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D31" s="90"/>
+    </row>
+    <row r="32" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D33" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="34" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D35" s="1" t="e">
+        <f>"Residue after " &amp; VLOOKUP(X_Cell_Crop_CropPurpose,'[1]Constants - Ag Residue'!D8:G10, 4, FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E35" s="16">
+        <f>E29*X_Cell_Crop_AreaUnderCropping</f>
+        <v>1900</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="36" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D37" s="80" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="38" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D38" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="E38" s="16">
+        <f>E28*X_Cell_Crop_AreaUnderCropping</f>
+        <v>0</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="39" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D39" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="F39" s="17" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="40" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D40" s="78" t="s">
+        <v>305</v>
+      </c>
+      <c r="F40" s="17" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="41" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D41" s="78" t="s">
+        <v>306</v>
+      </c>
+      <c r="E41" s="19">
+        <v>0.11</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="42" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E42" s="77">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D43" s="80" t="s">
+        <v>307</v>
+      </c>
+      <c r="E43" s="101">
+        <f>IFERROR((X_Cell_Crop_TotalResidueBaled*10^3)/X_Cell_Crop_AverageWeightPerBale, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D44" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E44" s="16">
+        <f>E38*X_Cell_Crop_PercentResidueBaled</f>
+        <v>0</v>
+      </c>
+      <c r="F44" s="17" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="45" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D45" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="46" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D47" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="E47" s="19">
+        <v>0.3</v>
+      </c>
+      <c r="F47" s="17" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="48" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E48" s="16">
+        <f>E38*X_Cell_Crop_PercentResidueBurned</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="5:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="5:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E50" s="16">
+        <f>E38-X_Cell_Crop_TotalResidueBaled-E48</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="5:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="5:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="5:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="5:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="5:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="5:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="5:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="5:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="5:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <conditionalFormatting sqref="F47">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10" xr:uid="{17671CC9-537C-4730-851C-300987B94431}">
+      <formula1>INDIRECT("Table_SourceData_Fertiliser_IrrigationMethods[Irrigation method]")</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECD198B5-7ECE-40EA-8499-B24C208F76C0}">
+  <sheetPr>
+    <tabColor rgb="FFCC6600"/>
+  </sheetPr>
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" style="1" customWidth="1"/>
+    <col min="4" max="10" width="30.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.35" customHeight="1">
+      <c r="A1" s="11" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25" ht="20" customHeight="1"/>
+    <row r="3" spans="1:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D5" s="71" t="s">
         <v>182</v>
       </c>
@@ -16049,10 +16608,10 @@
       <c r="F5" s="71"/>
       <c r="G5" s="71"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="F6" s="17"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D7" s="1" t="s">
         <v>178</v>
       </c>
@@ -16061,17 +16620,17 @@
       </c>
       <c r="F7" s="17"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D8" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E8" s="16" t="e" cm="1">
+      <c r="E8" s="16" t="str" cm="1">
         <f t="array" ref="E8">_xlfn.IFS(X_Cell_Crop_CropType="Maize", "Maize", X_Cell_Crop_CropType="Cotton", "Cotton", TRUE, "Grains")</f>
-        <v>#NAME?</v>
+        <v>Cotton</v>
       </c>
       <c r="F8" s="17"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D9" s="1" t="s">
         <v>64</v>
       </c>
@@ -16080,13 +16639,13 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D10" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E10" s="16" t="e" cm="1">
+      <c r="E10" s="16" cm="1">
         <f t="array" ref="E10">X_Cell_Crop_AreaUnderCropping</f>
-        <v>#NAME?</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -16094,13 +16653,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{790A6CAE-AEA5-40D0-AB61-E3C60BCDF82A}">
   <sheetPr>
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
   <dimension ref="C1:M65"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -16113,13 +16672,13 @@
     <col min="14" max="14" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:13" s="11" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="3:13" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.35" customHeight="1">
       <c r="C1" s="11" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="2" spans="3:13" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="3:13" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:13" s="3" customFormat="1" x14ac:dyDescent="0.25" ht="20" customHeight="1"/>
+    <row r="3" spans="3:13" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C3" s="30"/>
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
@@ -16132,12 +16691,12 @@
       <c r="L3" s="30"/>
       <c r="M3" s="30"/>
     </row>
-    <row r="5" spans="3:13" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:13" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D5" s="2" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="7" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D7" s="81" t="s">
         <v>256</v>
       </c>
@@ -16160,7 +16719,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="8" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D8" s="1" t="str">
         <f>"Unprocessed cotton yield"</f>
         <v>Unprocessed cotton yield</v>
@@ -16181,7 +16740,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D9" s="1" t="str">
         <f>"Processed cotton lint yield"</f>
         <v>Processed cotton lint yield</v>
@@ -16196,7 +16755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D10" s="1" t="str">
         <f>"Cottonseed yield"</f>
         <v>Cottonseed yield</v>
@@ -16211,7 +16770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D11" s="1" t="str">
         <f>"Cotton lint sold"</f>
         <v>Cotton lint sold</v>
@@ -16232,7 +16791,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D12" s="1" t="str">
         <f>"Cottonseed sold"</f>
         <v>Cottonseed sold</v>
@@ -16253,7 +16812,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D13" s="1" t="str">
         <f>"Percent income from cotton lint sold"</f>
         <v>Percent income from cotton lint sold</v>
@@ -16274,13 +16833,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D14" s="1" t="str">
         <f>"Percent income from cotton seed sold"</f>
         <v>Percent income from cotton seed sold</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F14" s="14" t="s">
         <v>241</v>
@@ -16292,21 +16851,21 @@
       <c r="I14" s="85"/>
       <c r="J14" s="16">
         <f>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_Enterprise[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_Enterprise[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_Enterprise[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="3:13" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J16" s="86">
         <f>SUM(Table_Input_DataQuality_Enterprise[Score])</f>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D17" s="2" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="19" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D19" s="81" t="s">
         <v>256</v>
       </c>
@@ -16329,7 +16888,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="20" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D20" s="1" t="str">
         <f>"Leaching zone"</f>
         <v>Leaching zone</v>
@@ -16350,7 +16909,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D21" s="1" t="str">
         <f>"Elevation"</f>
         <v>Elevation</v>
@@ -16371,7 +16930,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D22" s="1" t="str">
         <f>"Average temperature for reporting period"</f>
         <v>Average temperature for reporting period</v>
@@ -16392,7 +16951,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D23" s="1" t="str">
         <f>"Total rainfall for reporting period"</f>
         <v>Total rainfall for reporting period</v>
@@ -16413,7 +16972,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D24" s="1" t="str">
         <f>"Potential evapotranspiration for reporting period"</f>
         <v>Potential evapotranspiration for reporting period</v>
@@ -16434,7 +16993,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D25" s="1" t="str">
         <f>"Number of frost days for reporting period"</f>
         <v>Number of frost days for reporting period</v>
@@ -16455,18 +17014,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J27" s="86">
         <f>SUM(Table_Input_DataQuality_Site[Score])</f>
         <v>73</v>
       </c>
     </row>
-    <row r="28" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D28" s="2" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="30" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D30" s="81" t="s">
         <v>256</v>
       </c>
@@ -16489,7 +17048,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="31" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D31" s="1" t="str">
         <f>"Irrigation method"</f>
         <v>Irrigation method</v>
@@ -16510,7 +17069,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D32" s="1" t="str">
         <f>"Area under cropping"</f>
         <v>Area under cropping</v>
@@ -16531,7 +17090,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D33" s="1" t="str">
         <f>"Residue management"</f>
         <v>Residue management</v>
@@ -16552,18 +17111,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J35" s="86">
         <f>SUM(Table_Input_DataQuality_PastureManagement[Score])</f>
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D36" s="2" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="38" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D38" s="81" t="s">
         <v>256</v>
       </c>
@@ -16586,7 +17145,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="39" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D39" s="1" t="str">
         <f>"Branded inorganic fertiliser applications"</f>
         <v>Branded inorganic fertiliser applications</v>
@@ -16607,7 +17166,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D40" s="1" t="str">
         <f>"Custom inorganic fertiliser blend applications"</f>
         <v>Custom inorganic fertiliser blend applications</v>
@@ -16628,7 +17187,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D41" s="1" t="str">
         <f>"Lime applications"</f>
         <v>Lime applications</v>
@@ -16649,7 +17208,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D42" s="1" t="str">
         <f>"Organic fertiliser applications"</f>
         <v>Organic fertiliser applications</v>
@@ -16670,18 +17229,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J44" s="86">
         <f>SUM(Table_Input_DataQuality_FertiliserApplications[Score])</f>
         <v>55</v>
       </c>
     </row>
-    <row r="45" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D45" s="2" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="47" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D47" s="81" t="s">
         <v>256</v>
       </c>
@@ -16704,7 +17263,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="48" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D48" s="1" t="str">
         <f>"Fuel purchases"</f>
         <v>Fuel purchases</v>
@@ -16725,7 +17284,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D49" s="1" t="str">
         <f>"Fuel consumption"</f>
         <v>Fuel consumption</v>
@@ -16746,7 +17305,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="50" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D50" s="1" t="str">
         <f>"Electricity consumption"</f>
         <v>Electricity consumption</v>
@@ -16767,7 +17326,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D51" s="1" t="str">
         <f>"Electricity generation"</f>
         <v>Electricity generation</v>
@@ -16788,18 +17347,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J53" s="86">
         <f>SUM(Table_Input_DataQuality_FuelElectricity[Score])</f>
         <v>55</v>
       </c>
     </row>
-    <row r="55" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D55" s="2" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="57" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D57" s="81" t="s">
         <v>256</v>
       </c>
@@ -16822,7 +17381,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="58" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D58" s="1" t="str">
         <f>"Farm input purchases"</f>
         <v>Farm input purchases</v>
@@ -16843,7 +17402,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D59" s="1" t="str">
         <f>"Inbound freight use"</f>
         <v>Inbound freight use</v>
@@ -16864,7 +17423,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D60" s="1" t="str">
         <f>"Outbound freight use"</f>
         <v>Outbound freight use</v>
@@ -16885,7 +17444,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D61" s="1" t="str">
         <f>"Solid waste generation and treatment"</f>
         <v>Solid waste generation and treatment</v>
@@ -16906,19 +17465,19 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J63" s="86">
         <f>SUM(Table_Input_DataQuality_FarmInputsFreightWaste[Score])</f>
         <v>55</v>
       </c>
     </row>
-    <row r="65" spans="4:5" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:5" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D65" s="88" t="s">
         <v>264</v>
       </c>
       <c r="E65" s="89" t="str">
         <f>(J16+J27+J35+J44+J53+J63)&amp;" out of "&amp;((COUNT(Table_Input_DataQuality_Enterprise[Score])*15)+(COUNT(Table_Input_DataQuality_Site[Score])*15)+(COUNT(Table_Input_DataQuality_PastureManagement[Score])*15)+(COUNT(Table_Input_DataQuality_FertiliserApplications[Score])*15)+(COUNT(Table_Input_DataQuality_FuelElectricity[Score])*15)+(COUNT(Table_Input_DataQuality_FarmInputsFreightWaste[Score])*15))</f>
-        <v>334 out of 420</v>
+        <v>333 out of 420</v>
       </c>
     </row>
   </sheetData>
@@ -16945,13 +17504,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24D3DE85-228C-483C-8D62-5D3027BF032E}">
   <sheetPr>
     <tabColor theme="2" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:BY297"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="23" customWidth="1"/>
     <col min="2" max="2" width="2.7109375" style="23" customWidth="1"/>
@@ -16984,10 +17543,10 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:65" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -17014,11 +17573,11 @@
       <c r="V3" s="25"/>
       <c r="W3" s="25"/>
     </row>
-    <row r="4" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4"/>
       <c r="BM4" s="26"/>
     </row>
-    <row r="5" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5"/>
       <c r="D5" s="2" t="str" cm="1">
         <f t="array" ref="D5">Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title()</f>
@@ -17026,7 +17585,7 @@
       </c>
       <c r="BM5" s="26"/>
     </row>
-    <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="83" t="s">
         <v>2</v>
       </c>
@@ -17040,7 +17599,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="84" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -17058,7 +17617,7 @@
         <v>NSW</v>
       </c>
     </row>
-    <row r="8" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -17076,7 +17635,7 @@
         <v>ACT</v>
       </c>
     </row>
-    <row r="9" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9"/>
       <c r="D9" s="21" t="str" cm="1">
         <f t="array" ref="D9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -17091,7 +17650,7 @@
         <v>VIC</v>
       </c>
     </row>
-    <row r="10" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10"/>
       <c r="D10" s="21" t="str" cm="1">
         <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -17106,7 +17665,7 @@
         <v>QLD</v>
       </c>
     </row>
-    <row r="11" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11"/>
       <c r="D11" s="21" t="str" cm="1">
         <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -17122,7 +17681,7 @@
       </c>
       <c r="BM11" s="26"/>
     </row>
-    <row r="12" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12"/>
       <c r="D12" s="21" t="str" cm="1">
         <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -17138,7 +17697,7 @@
       </c>
       <c r="BM12" s="26"/>
     </row>
-    <row r="13" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13"/>
       <c r="D13" s="21" t="str" cm="1">
         <f t="array" ref="D13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -17153,7 +17712,7 @@
         <v>TAS</v>
       </c>
     </row>
-    <row r="14" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14"/>
       <c r="D14" s="21" t="str" cm="1">
         <f t="array" ref="D14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -17168,129 +17727,129 @@
         <v>NT</v>
       </c>
     </row>
-    <row r="15" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15"/>
     </row>
-    <row r="16" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16"/>
     </row>
-    <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17"/>
     </row>
-    <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18"/>
       <c r="D18" s="2" t="str" cm="1">
         <f t="array" ref="D18">Common_SourceData.Common_SourceData_WASA4Areas_Title()</f>
         <v>ABS Statistcal Areas Level 4 - Western Australia</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19"/>
       <c r="D19" s="18" t="str" cm="1">
         <f t="array" ref="D19">Common_SourceData.Common_SourceData_WASA4Areas_Source()</f>
         <v>Australian Bureau of Statistics (ABS) - Statistical Areas Level 2 - 2021 - Shapefile</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20"/>
       <c r="D20" s="21" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="D21" s="21" t="str" cm="1">
         <f t="array" ref="D21">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Bunbury</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22"/>
       <c r="D22" s="21" t="str" cm="1">
         <f t="array" ref="D22">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Mandurah</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23"/>
       <c r="D23" s="21" t="str" cm="1">
         <f t="array" ref="D23">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - Inner</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24"/>
       <c r="D24" s="21" t="str" cm="1">
         <f t="array" ref="D24">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North East</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
       <c r="D25" s="21" t="str" cm="1">
         <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North West</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
       <c r="D26" s="21" t="str" cm="1">
         <f t="array" ref="D26">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South East</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
       <c r="D27" s="21" t="str" cm="1">
         <f t="array" ref="D27">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South West</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
       <c r="D28" s="21" t="str" cm="1">
         <f t="array" ref="D28">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Wheat Belt</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29"/>
       <c r="D29" s="21" t="str" cm="1">
         <f t="array" ref="D29">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (North)</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
       <c r="D30" s="21" t="str" cm="1">
         <f t="array" ref="D30">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (South)</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31"/>
     </row>
-    <row r="32" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32"/>
     </row>
-    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33"/>
     </row>
-    <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34"/>
       <c r="D34" s="2" t="str" cm="1">
         <f t="array" ref="D34">Common_SourceData.Common_SourceData_GWP_Title()</f>
         <v>Global warming potential for greenhouse gases</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35"/>
       <c r="D35" s="18" t="str" cm="1">
         <f t="array" ref="D35">Common_SourceData.Common_SourceData_GWP_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
       <c r="D36" s="21" t="s">
         <v>26</v>
@@ -17299,7 +17858,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="D37" s="21" t="str" cm="1">
         <f t="array" ref="D37">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17310,7 +17869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
       <c r="D38" s="21" t="str" cm="1">
         <f t="array" ref="D38">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17321,7 +17880,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
       <c r="D39" s="21" t="str" cm="1">
         <f t="array" ref="D39">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17332,7 +17891,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="D40" s="21" t="str" cm="1">
         <f t="array" ref="D40">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17343,7 +17902,7 @@
         <v>6630</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
       <c r="D41" s="21" t="str" cm="1">
         <f t="array" ref="D41">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17354,7 +17913,7 @@
         <v>12200</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42"/>
       <c r="D42" s="21" t="str" cm="1">
         <f t="array" ref="D42">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17365,7 +17924,7 @@
         <v>22800</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43"/>
       <c r="D43" s="21" t="str" cm="1">
         <f t="array" ref="D43">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17376,24 +17935,24 @@
         <v>17200</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44"/>
     </row>
-    <row r="45" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45"/>
       <c r="D45" s="2" t="str" cm="1">
         <f t="array" ref="D45">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Title()</f>
         <v>Factor to convert elemental mass of gas to molecular mass</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46"/>
       <c r="D46" s="18" t="str" cm="1">
         <f t="array" ref="D46">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47"/>
       <c r="D47" s="21" t="s">
         <v>26</v>
@@ -17411,7 +17970,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48"/>
       <c r="D48" s="21" t="str" cm="1">
         <f t="array" ref="D48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17434,7 +17993,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49"/>
       <c r="D49" s="21" t="str" cm="1">
         <f t="array" ref="D49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17457,7 +18016,7 @@
         <v>1.3333333333333333</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50"/>
       <c r="D50" s="21" t="str" cm="1">
         <f t="array" ref="D50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17480,7 +18039,7 @@
         <v>1.5714285714285714</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51"/>
       <c r="D51" s="21" t="str" cm="1">
         <f t="array" ref="D51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17503,7 +18062,7 @@
         <v>3.2857142857142856</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52"/>
       <c r="D52" s="21" t="str" cm="1">
         <f t="array" ref="D52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17526,7 +18085,7 @@
         <v>2.3333333333333335</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53"/>
       <c r="D53" s="21" t="str" cm="1">
         <f t="array" ref="D53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17549,7 +18108,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54"/>
       <c r="D54" s="21" t="str" cm="1">
         <f t="array" ref="D54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17572,49 +18131,49 @@
         <v>1.1666666666666667</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55"/>
     </row>
-    <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56"/>
     </row>
-    <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57"/>
       <c r="D57" s="2" t="str" cm="1">
         <f t="array" ref="D57">Common_SourceData.Common_SourceData_WetAndDryZones_Title()</f>
         <v>VEERG Australian wet and dry zones</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58"/>
       <c r="D58" s="18" t="str" cm="1">
         <f t="array" ref="D58">Common_SourceData.Common_SourceData_WetAndDryZones_Source()</f>
         <v>VEERG 2026: Table 1.2: Translating climate zones to wet and dry zones</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59"/>
       <c r="D59" s="27" t="str" cm="1">
         <f t="array" ref="D59:D61">"⚠️" &amp; Common_SourceData.Common_SourceData_WetAndDryZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60"/>
       <c r="D60" s="27" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61"/>
       <c r="D61" s="27" t="str">
         <v>⚠️Fixed typo - Changed 'Fry' to 'Dry'.</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62"/>
     </row>
-    <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63"/>
       <c r="D63" s="21" t="s">
         <v>32</v>
@@ -17623,7 +18182,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64"/>
       <c r="D64" s="21" t="str" cm="1">
         <f t="array" ref="D64">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17634,7 +18193,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65"/>
       <c r="D65" s="21" t="str" cm="1">
         <f t="array" ref="D65">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17645,7 +18204,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66"/>
       <c r="D66" s="21" t="str" cm="1">
         <f t="array" ref="D66">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17656,7 +18215,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67"/>
       <c r="D67" s="21" t="str" cm="1">
         <f t="array" ref="D67">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17667,7 +18226,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68"/>
       <c r="D68" s="21" t="str" cm="1">
         <f t="array" ref="D68">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17678,7 +18237,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69"/>
       <c r="D69" s="21" t="str" cm="1">
         <f t="array" ref="D69">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17689,7 +18248,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70"/>
       <c r="D70" s="21" t="str" cm="1">
         <f t="array" ref="D70">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17700,7 +18259,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71"/>
       <c r="D71" s="21" t="str" cm="1">
         <f t="array" ref="D71">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17711,7 +18270,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72"/>
       <c r="D72" s="21" t="str" cm="1">
         <f t="array" ref="D72">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17722,7 +18281,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73"/>
       <c r="D73" s="21" t="str" cm="1">
         <f t="array" ref="D73">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17733,7 +18292,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74"/>
       <c r="D74" s="21" t="str" cm="1">
         <f t="array" ref="D74">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17744,7 +18303,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75"/>
       <c r="D75" s="21" t="str" cm="1">
         <f t="array" ref="D75">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17755,7 +18314,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76"/>
       <c r="D76" s="21" t="str" cm="1">
         <f t="array" ref="D76">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17766,7 +18325,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77"/>
       <c r="D77" s="21" t="str" cm="1">
         <f t="array" ref="D77">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17777,64 +18336,64 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78"/>
     </row>
-    <row r="79" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79"/>
     </row>
-    <row r="80" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80"/>
     </row>
-    <row r="81" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81"/>
       <c r="D81" s="2" t="str" cm="1">
         <f t="array" ref="D81">Common_SourceData.Common_SourceData_ClimateZones_Title()</f>
         <v>VEERG Australian climate zones</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82"/>
       <c r="D82" s="18" t="str" cm="1">
         <f t="array" ref="D82">Common_SourceData.Common_SourceData_ClimateZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83"/>
       <c r="D83" s="27" t="str" cm="1">
         <f t="array" ref="D83:D87">"⚠️" &amp; Common_SourceData.Common_SourceData_ClimateZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84"/>
       <c r="D84" s="27" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85"/>
       <c r="D85" s="27" t="str">
         <v>⚠️Fixed typo in MAT value for warm temperate dry - changed 10 to 11.</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86"/>
       <c r="D86" s="27" t="str">
         <v>⚠️Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87"/>
       <c r="D87" s="27" t="str">
         <v>⚠️GAF accepts rainfall as a proxy for precipitation.</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88"/>
     </row>
-    <row r="89" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89"/>
       <c r="D89" s="21" t="s">
         <v>32</v>
@@ -17886,7 +18445,7 @@
       </c>
       <c r="T89" s="21"/>
     </row>
-    <row r="90" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90"/>
       <c r="D90" s="21" t="str" cm="1">
         <f t="array" ref="D90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17954,7 +18513,7 @@
       </c>
       <c r="T90" s="21"/>
     </row>
-    <row r="91" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91"/>
       <c r="D91" s="21" t="str" cm="1">
         <f t="array" ref="D91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18022,7 +18581,7 @@
       </c>
       <c r="T91" s="21"/>
     </row>
-    <row r="92" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92"/>
       <c r="D92" s="21" t="str" cm="1">
         <f t="array" ref="D92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18090,7 +18649,7 @@
       </c>
       <c r="T92" s="21"/>
     </row>
-    <row r="93" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93"/>
       <c r="D93" s="21" t="str" cm="1">
         <f t="array" ref="D93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18158,7 +18717,7 @@
       </c>
       <c r="T93" s="21"/>
     </row>
-    <row r="94" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94"/>
       <c r="D94" s="21" t="str" cm="1">
         <f t="array" ref="D94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18226,7 +18785,7 @@
       </c>
       <c r="T94" s="21"/>
     </row>
-    <row r="95" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95"/>
       <c r="D95" s="21" t="str" cm="1">
         <f t="array" ref="D95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18294,7 +18853,7 @@
       </c>
       <c r="T95" s="21"/>
     </row>
-    <row r="96" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96"/>
       <c r="D96" s="21" t="str" cm="1">
         <f t="array" ref="D96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18362,7 +18921,7 @@
       </c>
       <c r="T96" s="21"/>
     </row>
-    <row r="97" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97"/>
       <c r="D97" s="21" t="str" cm="1">
         <f t="array" ref="D97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18430,66 +18989,66 @@
       </c>
       <c r="T97" s="21"/>
     </row>
-    <row r="98" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98"/>
     </row>
-    <row r="99" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99"/>
       <c r="D99" s="10" t="str" cm="1">
         <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100"/>
       <c r="D100" s="10" t="str">
         <v>MAT = mean annual temperature</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101"/>
       <c r="D101" s="10" t="str">
         <v>MAP = mean annual precipitation</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102"/>
       <c r="D102" s="10" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="103" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103"/>
       <c r="D103" s="10"/>
     </row>
-    <row r="104" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104"/>
     </row>
-    <row r="105" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105"/>
       <c r="D105" s="2" t="str" cm="1">
         <f t="array" ref="D105">Common_SourceData.Common_SourceData_TemperatureZones_Title()</f>
         <v>VEERG Australian temperature zones</v>
       </c>
     </row>
-    <row r="106" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106"/>
       <c r="D106" s="18" t="str" cm="1">
         <f t="array" ref="D106">Common_SourceData.Common_SourceData_TemperatureZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="107" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107"/>
       <c r="D107" s="27" t="str" cm="1">
         <f t="array" ref="D107">"⚠️" &amp; Common_SourceData.Common_SourceData_TemperatureZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.</v>
       </c>
     </row>
-    <row r="108" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108"/>
     </row>
-    <row r="109" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109"/>
       <c r="D109" s="21" t="s">
         <v>49</v>
@@ -18504,7 +19063,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="110" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110"/>
       <c r="D110" s="21" t="str" cm="1">
         <f t="array" ref="D110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -18523,7 +19082,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="111" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111"/>
       <c r="D111" s="21" t="str" cm="1">
         <f t="array" ref="D111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -18542,7 +19101,7 @@
         <v>25.998999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112"/>
       <c r="D112" s="21" t="str" cm="1">
         <f t="array" ref="D112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -18561,13 +19120,13 @@
         <v>14.999000000000001</v>
       </c>
     </row>
-    <row r="113" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113"/>
     </row>
-    <row r="114" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114"/>
     </row>
-    <row r="115" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115"/>
       <c r="D115" s="2" t="str" cm="1">
         <f t="array" ref="D115">Common_SourceData.Common_SourceData_RainfallZones_Title()</f>
@@ -18575,7 +19134,7 @@
       </c>
       <c r="BN115" s="23"/>
     </row>
-    <row r="116" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116"/>
       <c r="D116" s="18" t="str" cm="1">
         <f t="array" ref="D116">Common_SourceData.Common_SourceData_RainfallZones_Source()</f>
@@ -18583,7 +19142,7 @@
       </c>
       <c r="BN116" s="23"/>
     </row>
-    <row r="117" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117"/>
       <c r="D117" s="27" t="str" cm="1">
         <f t="array" ref="D117">"⚠️" &amp; Common_SourceData.Common_SourceData_RainfallZones_Variation()</f>
@@ -18591,11 +19150,11 @@
       </c>
       <c r="BN117" s="23"/>
     </row>
-    <row r="118" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118"/>
       <c r="BN118" s="23"/>
     </row>
-    <row r="119" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119"/>
       <c r="D119" s="21" t="s">
         <v>52</v>
@@ -18611,7 +19170,7 @@
       </c>
       <c r="BN119" s="23"/>
     </row>
-    <row r="120" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120"/>
       <c r="D120" s="21" t="str" cm="1">
         <f t="array" ref="D120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -18631,7 +19190,7 @@
       </c>
       <c r="BN120" s="23"/>
     </row>
-    <row r="121" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121"/>
       <c r="D121" s="21" t="str" cm="1">
         <f t="array" ref="D121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -18651,31 +19210,31 @@
       </c>
       <c r="BN121" s="23"/>
     </row>
-    <row r="122" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122"/>
       <c r="BN122" s="23"/>
     </row>
-    <row r="123" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123"/>
     </row>
-    <row r="124" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124"/>
       <c r="D124" s="2" t="str" cm="1">
         <f t="array" ref="D124">Common_SourceData.Common_SourceData_LeachingZones_Title()</f>
         <v>VEERG Australian leaching zones</v>
       </c>
     </row>
-    <row r="125" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125"/>
       <c r="D125" s="18" t="str" cm="1">
         <f t="array" ref="D125">Common_SourceData.Common_SourceData_LeachingZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="126" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126"/>
     </row>
-    <row r="127" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127"/>
       <c r="D127" s="21" t="s">
         <v>54</v>
@@ -18684,7 +19243,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="128" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128"/>
       <c r="D128" s="21" t="str" cm="1">
         <f t="array" ref="D128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -18695,7 +19254,7 @@
         <v>Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="129" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129"/>
       <c r="D129" s="21" t="str" cm="1">
         <f t="array" ref="D129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -18706,13 +19265,13 @@
         <v>Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="130" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130"/>
     </row>
-    <row r="131" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131"/>
     </row>
-    <row r="132" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132"/>
       <c r="D132" s="2" t="str" cm="1">
         <f t="array" ref="D132">Common_SourceData.Common_SourceData_FracWET_Title()</f>
@@ -18720,7 +19279,7 @@
       </c>
       <c r="E132" s="9"/>
     </row>
-    <row r="133" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133"/>
       <c r="D133" s="18" t="str" cm="1">
         <f t="array" ref="D133">Common_SourceData.Common_SourceData_FracWET_Source()</f>
@@ -18728,7 +19287,7 @@
       </c>
       <c r="E133" s="9"/>
     </row>
-    <row r="134" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134"/>
       <c r="D134" t="s">
         <v>56</v>
@@ -18737,7 +19296,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="135" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135"/>
       <c r="D135" t="str" cm="1">
         <f t="array" ref="D135">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -18748,7 +19307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136"/>
       <c r="D136" s="1" t="str" cm="1">
         <f t="array" ref="D136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -18759,10 +19318,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137"/>
     </row>
-    <row r="138" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138"/>
       <c r="BN138" s="23"/>
       <c r="BO138" s="23"/>
@@ -18777,7 +19336,7 @@
       <c r="BX138" s="23"/>
       <c r="BY138" s="23"/>
     </row>
-    <row r="139" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139"/>
       <c r="D139" s="2" t="str" cm="1">
         <f t="array" ref="D139">Common_SourceData.Common_SourceData_FracWETIrrigation_Title()</f>
@@ -18796,7 +19355,7 @@
       <c r="BX139" s="23"/>
       <c r="BY139" s="23"/>
     </row>
-    <row r="140" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140"/>
       <c r="D140" s="18" t="str" cm="1">
         <f t="array" ref="D140">Common_SourceData.Common_SourceData_FracWETIrrigation_Source()</f>
@@ -18815,7 +19374,7 @@
       <c r="BX140" s="23"/>
       <c r="BY140" s="23"/>
     </row>
-    <row r="141" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141"/>
       <c r="D141" s="27" t="str" cm="1">
         <f t="array" ref="D141">Common_SourceData.Common_SourceData_FracWETIrrigation_Variation()</f>
@@ -18823,7 +19382,7 @@
       </c>
       <c r="BN141" s="23"/>
     </row>
-    <row r="142" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142"/>
       <c r="D142" s="21" t="s">
         <v>58</v>
@@ -18833,7 +19392,7 @@
       </c>
       <c r="BN142" s="23"/>
     </row>
-    <row r="143" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143"/>
       <c r="D143" s="21" t="str" cm="1">
         <f t="array" ref="D143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18845,7 +19404,7 @@
       </c>
       <c r="BN143" s="23"/>
     </row>
-    <row r="144" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144"/>
       <c r="D144" s="1" t="str" cm="1">
         <f t="array" ref="D144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18857,7 +19416,7 @@
       </c>
       <c r="BN144" s="23"/>
     </row>
-    <row r="145" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145"/>
       <c r="D145" s="1" t="str" cm="1">
         <f t="array" ref="D145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18869,7 +19428,7 @@
       </c>
       <c r="BN145" s="23"/>
     </row>
-    <row r="146" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146"/>
       <c r="D146" s="1" t="str" cm="1">
         <f t="array" ref="D146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18881,7 +19440,7 @@
       </c>
       <c r="BN146" s="23"/>
     </row>
-    <row r="147" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147"/>
       <c r="D147" s="1" t="str" cm="1">
         <f t="array" ref="D147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18893,15 +19452,15 @@
       </c>
       <c r="BN147" s="23"/>
     </row>
-    <row r="148" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148"/>
       <c r="BN148" s="23"/>
     </row>
-    <row r="149" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149"/>
       <c r="BN149" s="23"/>
     </row>
-    <row r="150" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150"/>
       <c r="D150" s="2" t="str" cm="1">
         <f t="array" ref="D150">Common_SourceData.Common_SourceData_DataScores_Scope3_Title()</f>
@@ -18909,7 +19468,7 @@
       </c>
       <c r="BN150" s="23"/>
     </row>
-    <row r="151" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151"/>
       <c r="D151" s="18" t="str" cm="1">
         <f t="array" ref="D151">Common_SourceData.Common_SourceData_DataScores_Scope3_Source()</f>
@@ -18917,11 +19476,11 @@
       </c>
       <c r="BN151" s="23"/>
     </row>
-    <row r="152" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152"/>
       <c r="BN152" s="23"/>
     </row>
-    <row r="153" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153"/>
       <c r="D153" s="21" t="s">
         <v>59</v>
@@ -18941,7 +19500,7 @@
       <c r="BL153" s="26"/>
       <c r="BM153" s="26"/>
     </row>
-    <row r="154" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154"/>
       <c r="D154" s="21" t="str" cm="1">
         <f t="array" ref="D154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -18963,7 +19522,7 @@
       <c r="BL154" s="26"/>
       <c r="BM154" s="26"/>
     </row>
-    <row r="155" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155"/>
       <c r="D155" s="21" t="str" cm="1">
         <f t="array" ref="D155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -18985,7 +19544,7 @@
       <c r="BL155" s="26"/>
       <c r="BM155" s="26"/>
     </row>
-    <row r="156" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156"/>
       <c r="D156" s="21" t="str" cm="1">
         <f t="array" ref="D156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -18996,7 +19555,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157"/>
       <c r="D157" s="21" t="str" cm="1">
         <f t="array" ref="D157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -19007,7 +19566,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158"/>
       <c r="D158" s="21" t="str" cm="1">
         <f t="array" ref="D158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -19018,34 +19577,34 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159"/>
     </row>
-    <row r="160" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160"/>
     </row>
-    <row r="161" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D161" s="2" t="str" cm="1">
         <f t="array" ref="D161">Common_SourceData.Common_SourceData_FracLEACH_Title()</f>
         <v>Fraction of N that is available for leaching and runoff</v>
       </c>
       <c r="E161" s="9"/>
     </row>
-    <row r="162" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D162" s="18" t="str" cm="1">
         <f t="array" ref="D162">Common_SourceData.Common_SourceData_FracLEACH_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
       <c r="E162" s="9"/>
     </row>
-    <row r="163" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D163" s="18" t="str" cm="1">
         <f t="array" ref="D163">Common_SourceData.Common_SourceData_FracLEACH_NIRReference()</f>
         <v>National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)</v>
       </c>
       <c r="E163" s="9"/>
     </row>
-    <row r="164" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D164" s="9" t="str" cm="1">
         <f t="array" ref="D164:E164">Common_SourceData.Common_SourceData_FracLEACH_Data()</f>
         <v>FracLEACH</v>
@@ -19054,17 +19613,17 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="165" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN165" s="23"/>
       <c r="BO165" s="23"/>
       <c r="BP165" s="23"/>
     </row>
-    <row r="166" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN166" s="23"/>
       <c r="BO166" s="23"/>
       <c r="BP166" s="23"/>
     </row>
-    <row r="167" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D167" s="2" t="str" cm="1">
         <f t="array" ref="D167">Common_SourceData.Common_SourceData_EFleach_Title()</f>
         <v>Emission factor for nitrogen leaching and runoff</v>
@@ -19073,7 +19632,7 @@
       <c r="BO167" s="23"/>
       <c r="BP167" s="23"/>
     </row>
-    <row r="168" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D168" s="18" t="str" cm="1">
         <f t="array" ref="D168">Common_SourceData.Common_SourceData_EFleach_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
@@ -19082,7 +19641,7 @@
       <c r="BO168" s="23"/>
       <c r="BP168" s="23"/>
     </row>
-    <row r="169" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D169" s="18" t="str" cm="1">
         <f t="array" ref="D169">Common_SourceData.Common_SourceData_EFleach_NIRReference()</f>
         <v>National Inventory Report Volume 1: Equation 3.D.B_10</v>
@@ -19091,7 +19650,7 @@
       <c r="BO169" s="23"/>
       <c r="BP169" s="23"/>
     </row>
-    <row r="170" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D170" s="1" t="str" cm="1">
         <f t="array" ref="D170:E170">Common_SourceData.Common_SourceData_EFleach_Data()</f>
         <v>EFleach</v>
@@ -19103,17 +19662,17 @@
       <c r="BO170" s="23"/>
       <c r="BP170" s="23"/>
     </row>
-    <row r="171" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN171" s="23"/>
       <c r="BO171" s="23"/>
       <c r="BP171" s="23"/>
     </row>
-    <row r="172" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN172" s="23"/>
       <c r="BO172" s="23"/>
       <c r="BP172" s="23"/>
     </row>
-    <row r="173" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D173" s="2" t="str" cm="1">
         <f t="array" ref="D173">Common_SourceData.Common_SourceData_DensityOfMethane_Title()</f>
         <v>p = density of methane</v>
@@ -19122,7 +19681,7 @@
       <c r="BO173" s="23"/>
       <c r="BP173" s="23"/>
     </row>
-    <row r="174" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D174" s="18" t="str" cm="1">
         <f t="array" ref="D174">Common_SourceData.Common_SourceData_DensityOfMethane_Source()</f>
         <v>National Inventory Report 2023 Volume 1: Equations 3.B.1a_2, 3.B.1c_2, 3.B.3_1, 3.B.4g_2</v>
@@ -19131,7 +19690,7 @@
       <c r="BO174" s="23"/>
       <c r="BP174" s="23"/>
     </row>
-    <row r="175" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D175" s="1" cm="1">
         <f t="array" ref="D175">Common_SourceData.Common_SourceData_DensityOfMethane_Data()</f>
         <v>0.6784</v>
@@ -19144,17 +19703,17 @@
       <c r="BO175" s="23"/>
       <c r="BP175" s="23"/>
     </row>
-    <row r="176" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN176" s="23"/>
       <c r="BO176" s="23"/>
       <c r="BP176" s="23"/>
     </row>
-    <row r="177" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN177" s="23"/>
       <c r="BO177" s="23"/>
       <c r="BP177" s="23"/>
     </row>
-    <row r="178" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D178" s="2" t="str" cm="1">
         <f t="array" ref="D178">Common_SourceData.Common_SourceData_EFN2O_Title()</f>
         <v>Nitrous oxide emission factors for inorganic fertiliser application</v>
@@ -19163,7 +19722,7 @@
       <c r="BO178" s="23"/>
       <c r="BP178" s="23"/>
     </row>
-    <row r="179" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D179" s="18" t="str" cm="1">
         <f t="array" ref="D179">Common_SourceData.Common_SourceData_EFN2O_Source()</f>
         <v>VEERG 2026: Table A.2.2.1</v>
@@ -19172,39 +19731,39 @@
       <c r="BO179" s="23"/>
       <c r="BP179" s="23"/>
     </row>
-    <row r="180" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D180" s="10" t="str" cm="1">
         <f t="array" ref="D180">Common_SourceData.Common_SourceData_EFN2O_Unit()</f>
         <v>(kg N2O-N / kg N</v>
       </c>
     </row>
-    <row r="181" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D181" s="27" t="str" cm="1">
         <f t="array" ref="D181:D185">Common_SourceData.Common_SourceData_EFN2O_Variation()</f>
         <v>VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="182" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D182" s="27" t="str">
         <v>Removed duplicate 'Aquaculture' row.</v>
       </c>
     </row>
-    <row r="183" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D183" s="27" t="str">
         <v>Removed asterisks to aid lookup.</v>
       </c>
     </row>
-    <row r="184" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D184" s="27" t="str">
         <v>Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.</v>
       </c>
     </row>
-    <row r="185" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D185" s="27" t="str">
         <v>Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup.</v>
       </c>
     </row>
-    <row r="186" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D186" s="21" t="s">
         <v>61</v>
       </c>
@@ -19221,7 +19780,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="187" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D187" s="21" t="str" cm="1">
         <f t="array" ref="D187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated pasture</v>
@@ -19243,7 +19802,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="188" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D188" s="21" t="str" cm="1">
         <f t="array" ref="D188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated crop</v>
@@ -19265,7 +19824,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="189" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D189" s="21" t="str" cm="1">
         <f t="array" ref="D189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -19287,7 +19846,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="190" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D190" s="21" t="str" cm="1">
         <f t="array" ref="D190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -19309,7 +19868,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="191" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D191" s="21" t="str" cm="1">
         <f t="array" ref="D191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (low rainfall)</v>
@@ -19331,7 +19890,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="192" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D192" s="21" t="str" cm="1">
         <f t="array" ref="D192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (high rainfall)</v>
@@ -19353,7 +19912,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="193" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D193" s="21" t="str" cm="1">
         <f t="array" ref="D193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Sugar</v>
@@ -19375,7 +19934,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="194" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D194" s="21" t="str" cm="1">
         <f t="array" ref="D194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Cotton</v>
@@ -19397,7 +19956,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="195" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D195" s="21" t="str" cm="1">
         <f t="array" ref="D195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Horticultural crops</v>
@@ -19419,7 +19978,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="196" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D196" s="21" t="str" cm="1">
         <f t="array" ref="D196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (continuous flooding)</v>
@@ -19441,7 +20000,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="197" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D197" s="21" t="str" cm="1">
         <f t="array" ref="D197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (single and multiple drainage, or alternate wetting and drying)</v>
@@ -19463,7 +20022,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="198" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D198" s="21" t="str" cm="1">
         <f t="array" ref="D198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Aquaculture</v>
@@ -19485,7 +20044,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="199" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D199" s="21" t="str" cm="1">
         <f t="array" ref="D199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Forestry</v>
@@ -19507,31 +20066,31 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="202" spans="4:8" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="202" spans="4:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D202" s="2" t="str" cm="1">
         <f t="array" ref="D202">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Title()</f>
         <v>Emission factor for urine and dung deposited on pasture, range or paddock</v>
       </c>
     </row>
-    <row r="203" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D203" s="18" t="str" cm="1">
         <f t="array" ref="D203">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source()</f>
         <v>VEERG 2026: Table A.2.2.2</v>
       </c>
     </row>
-    <row r="204" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D204" s="27" t="str" cm="1">
         <f t="array" ref="D204">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Variation()</f>
         <v>VARIATION FROM SOURCE DATA: Changed 'Dry climate zones' to singular 'Dry climate zone' to aid lookup.</v>
       </c>
     </row>
-    <row r="205" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D205" s="10" t="str" cm="1">
         <f t="array" ref="D205">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="206" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D206" s="21" t="s">
         <v>32</v>
       </c>
@@ -19539,7 +20098,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="207" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D207" s="21" t="str" cm="1">
         <f t="array" ref="D207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -19549,7 +20108,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="208" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D208" s="1" t="str" cm="1">
         <f t="array" ref="D208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -19559,13 +20118,13 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="211" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D211" s="1" t="str" cm="1">
         <f t="array" ref="D211">Common_SourceData.Common_SourceData_MonthsToSeasons_Title()</f>
         <v>Months to Seasons Mapping</v>
       </c>
     </row>
-    <row r="212" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D212" s="21" t="s">
         <v>67</v>
       </c>
@@ -19573,7 +20132,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="213" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D213" s="21" t="str" cm="1">
         <f t="array" ref="D213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>January</v>
@@ -19583,7 +20142,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="214" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D214" s="1" t="str" cm="1">
         <f t="array" ref="D214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>February</v>
@@ -19593,7 +20152,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="215" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D215" s="1" t="str" cm="1">
         <f t="array" ref="D215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>March</v>
@@ -19603,7 +20162,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="216" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D216" s="1" t="str" cm="1">
         <f t="array" ref="D216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>April</v>
@@ -19613,7 +20172,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="217" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D217" s="1" t="str" cm="1">
         <f t="array" ref="D217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>May</v>
@@ -19623,7 +20182,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="218" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D218" s="1" t="str" cm="1">
         <f t="array" ref="D218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>June</v>
@@ -19633,7 +20192,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="219" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D219" s="1" t="str" cm="1">
         <f t="array" ref="D219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>July</v>
@@ -19643,7 +20202,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="220" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D220" s="1" t="str" cm="1">
         <f t="array" ref="D220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>August</v>
@@ -19653,7 +20212,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="221" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D221" s="1" t="str" cm="1">
         <f t="array" ref="D221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>September</v>
@@ -19663,7 +20222,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="222" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D222" s="1" t="str" cm="1">
         <f t="array" ref="D222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>October</v>
@@ -19673,7 +20232,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="223" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D223" s="1" t="str" cm="1">
         <f t="array" ref="D223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>November</v>
@@ -19683,7 +20242,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="224" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D224" s="1" t="str" cm="1">
         <f t="array" ref="D224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>December</v>
@@ -19693,25 +20252,25 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="227" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="227" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D227" s="2" t="str" cm="1">
         <f t="array" ref="D227">Common_SourceData.Common_SourceData_MCFTemperatureZone_Title()</f>
         <v>Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)</v>
       </c>
     </row>
-    <row r="228" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="228" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D228" s="18" t="str" cm="1">
         <f t="array" ref="D228">Common_SourceData.Common_SourceData_MCFTemperatureZone_Source()</f>
         <v>VEERG 2026: Table A.1.8.1</v>
       </c>
     </row>
-    <row r="229" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="229" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D229" s="27" t="str" cm="1">
         <f t="array" ref="D229">Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation()</f>
         <v>VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.</v>
       </c>
     </row>
-    <row r="231" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="231" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D231" s="21" t="s">
         <v>69</v>
       </c>
@@ -19761,7 +20320,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="232" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="232" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D232" s="21" t="str" cm="1">
         <f t="array" ref="D232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19827,7 +20386,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="233" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D233" s="1" t="str" cm="1">
         <f t="array" ref="D233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19893,7 +20452,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="234" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="234" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D234" s="1" t="str" cm="1">
         <f t="array" ref="D234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19959,7 +20518,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="235" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="235" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D235" s="1" t="str" cm="1">
         <f t="array" ref="D235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -20025,7 +20584,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="236" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="236" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D236" s="1" t="str" cm="1">
         <f t="array" ref="D236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -20091,7 +20650,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="237" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="237" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D237" s="1" t="str" cm="1">
         <f t="array" ref="D237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20157,7 +20716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="238" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="238" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D238" s="1" t="str" cm="1">
         <f t="array" ref="D238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20223,7 +20782,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="239" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="239" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D239" s="1" t="str" cm="1">
         <f t="array" ref="D239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20289,7 +20848,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="240" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D240" s="1" t="str" cm="1">
         <f t="array" ref="D240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20355,7 +20914,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="241" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="241" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D241" s="1" t="str" cm="1">
         <f t="array" ref="D241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20421,7 +20980,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="242" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="242" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D242" s="1" t="str" cm="1">
         <f t="array" ref="D242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20487,7 +21046,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="243" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="243" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D243" s="1" t="str" cm="1">
         <f t="array" ref="D243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20553,7 +21112,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="244" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D244" s="1" t="str" cm="1">
         <f t="array" ref="D244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20619,7 +21178,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="245" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="245" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D245" s="1" t="str" cm="1">
         <f t="array" ref="D245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20685,7 +21244,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="246" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="246" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D246" s="1" t="str" cm="1">
         <f t="array" ref="D246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20751,7 +21310,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="247" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="247" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D247" s="1" t="str" cm="1">
         <f t="array" ref="D247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20817,7 +21376,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="248" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="248" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D248" s="1" t="str" cm="1">
         <f t="array" ref="D248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -20883,7 +21442,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="249" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="249" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D249" s="1" t="str" cm="1">
         <f t="array" ref="D249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -20949,7 +21508,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="250" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="250" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D250" s="1" t="str" cm="1">
         <f t="array" ref="D250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -21015,31 +21574,31 @@
         <v>28</v>
       </c>
     </row>
-    <row r="253" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="253" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D253" s="2" t="str" cm="1">
         <f t="array" ref="D253">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Title()</f>
         <v>Emission factor for organic fertiliser and crop residues returned to the soil</v>
       </c>
     </row>
-    <row r="254" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="254" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D254" s="18" t="str" cm="1">
         <f t="array" ref="D254">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source()</f>
         <v>VEERG 2026: Table A.2.1.4</v>
       </c>
     </row>
-    <row r="255" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="255" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D255" s="1" t="str" cm="1">
         <f t="array" ref="D255">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable()</f>
         <v>EFNi &amp; EFN2Oi</v>
       </c>
     </row>
-    <row r="256" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="256" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D256" s="10" t="str" cm="1">
         <f t="array" ref="D256">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="257" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D257" s="21" t="s">
         <v>85</v>
       </c>
@@ -21047,7 +21606,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="258" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D258" s="21" t="str" cm="1">
         <f t="array" ref="D258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -21057,7 +21616,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="259" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D259" s="1" t="str" cm="1">
         <f t="array" ref="D259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -21067,17 +21626,17 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="263" spans="4:66" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="263" spans="4:66" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D263" s="2" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="264" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="264" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D264" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="265" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="265" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D265" s="21" t="s">
         <v>234</v>
       </c>
@@ -21093,7 +21652,7 @@
       <c r="V265" s="1"/>
       <c r="BN265" s="23"/>
     </row>
-    <row r="266" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="266" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D266" s="21" t="s">
         <v>235</v>
       </c>
@@ -21109,7 +21668,7 @@
       <c r="V266" s="1"/>
       <c r="BN266" s="23"/>
     </row>
-    <row r="267" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="267" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D267" s="21" t="s">
         <v>236</v>
       </c>
@@ -21125,7 +21684,7 @@
       <c r="V267" s="1"/>
       <c r="BN267" s="23"/>
     </row>
-    <row r="268" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="268" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D268" s="21" t="s">
         <v>237</v>
       </c>
@@ -21141,7 +21700,7 @@
       <c r="V268" s="1"/>
       <c r="BN268" s="23"/>
     </row>
-    <row r="269" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="269" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D269" s="21" t="s">
         <v>238</v>
       </c>
@@ -21157,7 +21716,7 @@
       <c r="V269" s="1"/>
       <c r="BN269" s="23"/>
     </row>
-    <row r="270" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="270" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D270" s="21" t="s">
         <v>239</v>
       </c>
@@ -21173,12 +21732,12 @@
       <c r="V270" s="1"/>
       <c r="BN270" s="23"/>
     </row>
-    <row r="273" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="273" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D273" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="274" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="274" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D274" s="21" t="s">
         <v>234</v>
       </c>
@@ -21194,7 +21753,7 @@
       <c r="V274" s="1"/>
       <c r="BN274" s="23"/>
     </row>
-    <row r="275" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="275" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D275" s="21" t="s">
         <v>240</v>
       </c>
@@ -21210,7 +21769,7 @@
       <c r="V275" s="1"/>
       <c r="BN275" s="23"/>
     </row>
-    <row r="276" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="276" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D276" s="21" t="s">
         <v>241</v>
       </c>
@@ -21226,7 +21785,7 @@
       <c r="V276" s="1"/>
       <c r="BN276" s="23"/>
     </row>
-    <row r="277" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="277" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D277" s="21" t="s">
         <v>242</v>
       </c>
@@ -21242,7 +21801,7 @@
       <c r="V277" s="1"/>
       <c r="BN277" s="23"/>
     </row>
-    <row r="278" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="278" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D278" s="21" t="s">
         <v>243</v>
       </c>
@@ -21258,7 +21817,7 @@
       <c r="V278" s="1"/>
       <c r="BN278" s="23"/>
     </row>
-    <row r="279" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="279" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D279" s="21" t="s">
         <v>244</v>
       </c>
@@ -21274,12 +21833,12 @@
       <c r="V279" s="1"/>
       <c r="BN279" s="23"/>
     </row>
-    <row r="282" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="282" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D282" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="283" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="283" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D283" s="21" t="s">
         <v>234</v>
       </c>
@@ -21295,7 +21854,7 @@
       <c r="V283" s="1"/>
       <c r="BN283" s="23"/>
     </row>
-    <row r="284" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="284" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D284" s="21" t="s">
         <v>245</v>
       </c>
@@ -21311,7 +21870,7 @@
       <c r="V284" s="1"/>
       <c r="BN284" s="23"/>
     </row>
-    <row r="285" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="285" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D285" s="21" t="s">
         <v>246</v>
       </c>
@@ -21327,7 +21886,7 @@
       <c r="V285" s="1"/>
       <c r="BN285" s="23"/>
     </row>
-    <row r="286" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="286" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D286" s="21" t="s">
         <v>247</v>
       </c>
@@ -21343,7 +21902,7 @@
       <c r="V286" s="1"/>
       <c r="BN286" s="23"/>
     </row>
-    <row r="287" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="287" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D287" s="21" t="s">
         <v>248</v>
       </c>
@@ -21359,7 +21918,7 @@
       <c r="V287" s="1"/>
       <c r="BN287" s="23"/>
     </row>
-    <row r="288" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="288" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D288" s="21" t="s">
         <v>249</v>
       </c>
@@ -21375,12 +21934,12 @@
       <c r="V288" s="1"/>
       <c r="BN288" s="23"/>
     </row>
-    <row r="291" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="291" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D291" s="1" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="292" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="292" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D292" s="21" t="s">
         <v>234</v>
       </c>
@@ -21396,7 +21955,7 @@
       <c r="V292" s="1"/>
       <c r="BN292" s="23"/>
     </row>
-    <row r="293" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="293" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D293" s="21" t="s">
         <v>250</v>
       </c>
@@ -21412,7 +21971,7 @@
       <c r="V293" s="1"/>
       <c r="BN293" s="23"/>
     </row>
-    <row r="294" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="294" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D294" s="21" t="s">
         <v>251</v>
       </c>
@@ -21428,7 +21987,7 @@
       <c r="V294" s="1"/>
       <c r="BN294" s="23"/>
     </row>
-    <row r="295" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="295" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D295" s="21" t="s">
         <v>252</v>
       </c>
@@ -21444,7 +22003,7 @@
       <c r="V295" s="1"/>
       <c r="BN295" s="23"/>
     </row>
-    <row r="296" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="296" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D296" s="21" t="s">
         <v>253</v>
       </c>
@@ -21460,7 +22019,7 @@
       <c r="V296" s="1"/>
       <c r="BN296" s="23"/>
     </row>
-    <row r="297" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="297" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D297" s="21" t="s">
         <v>254</v>
       </c>
@@ -21506,14 +22065,7 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAMAApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA0ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -21526,7 +22078,14 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAMAApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA0ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -21725,12 +22284,9 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -21744,9 +22300,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Excel/Enterprises/Enterprise_CroppingCotton_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_CroppingCotton_Template_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\Enterprises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37CE8981-2BA5-4F6C-9348-49CEB96E176F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E3AA2C-8D95-4578-87AE-F85D4F1A5BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1110" yWindow="465" windowWidth="36330" windowHeight="19485" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="36330" windowHeight="19485" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -23,9 +23,6 @@
     <sheet name="Input - Data quality" sheetId="78" r:id="rId8"/>
     <sheet name="Constants - Common" sheetId="79" r:id="rId9"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId10"/>
-  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -224,38 +221,53 @@
     <definedName name="Result_EmissionsForWholeProductionCycle_Method2">'Input - Enterprise'!$F$59</definedName>
     <definedName name="Result_EmissionsForWholeProductionCycle_Net_Method1">'Input - Enterprise'!$E$83</definedName>
     <definedName name="Result_EmissionsForWholeProductionCycle_Net_Method2">'Input - Enterprise'!$F$83</definedName>
-    <definedName name="Result_Enterprise_Gross_Method1">'Results - Activity period'!$E$62</definedName>
-    <definedName name="Result_Enterprise_Gross_Method2">'Results - Activity period'!$F$62</definedName>
-    <definedName name="Result_Enterprise_Net_Method1">'Results - Activity period'!$E$63</definedName>
-    <definedName name="Result_Enterprise_Net_Method2">'Results - Activity period'!$F$63</definedName>
-    <definedName name="Result_Enterprise_Removals">'Results - Activity period'!$E$56</definedName>
-    <definedName name="Result_Enterprise_Scope1_Method1">'Results - Activity period'!$H$27</definedName>
-    <definedName name="Result_Enterprise_Scope1_Method2">'Results - Activity period'!$I$27</definedName>
-    <definedName name="Result_Enterprise_Scope2_Method1">'Results - Activity period'!$H$34</definedName>
-    <definedName name="Result_Enterprise_Scope2_Method2">'Results - Activity period'!$I$34</definedName>
-    <definedName name="Result_Enterprise_Scope3_Method1">'Results - Activity period'!$H$51</definedName>
-    <definedName name="Result_Enterprise_Scope3_Method2">'Results - Activity period'!$I$51</definedName>
-    <definedName name="X_Cell_BaledHayYield">'Input - Enterprise'!$E$27</definedName>
+    <definedName name="Result_Enterprise_Gross_Method1">'Results - Activity period'!$E$60</definedName>
+    <definedName name="Result_Enterprise_Gross_Method2">'Results - Activity period'!$F$60</definedName>
+    <definedName name="Result_Enterprise_Net_Method1">'Results - Activity period'!$E$61</definedName>
+    <definedName name="Result_Enterprise_Net_Method2">'Results - Activity period'!$F$61</definedName>
+    <definedName name="Result_Enterprise_Removals">'Results - Activity period'!$E$54</definedName>
+    <definedName name="Result_Enterprise_Scope1_Method1">'Results - Activity period'!$H$25</definedName>
+    <definedName name="Result_Enterprise_Scope1_Method2">'Results - Activity period'!$I$25</definedName>
+    <definedName name="Result_Enterprise_Scope2_Method1">'Results - Activity period'!$H$32</definedName>
+    <definedName name="Result_Enterprise_Scope2_Method2">'Results - Activity period'!$I$32</definedName>
+    <definedName name="Result_Enterprise_Scope3_Method1">'Results - Activity period'!$H$49</definedName>
+    <definedName name="Result_Enterprise_Scope3_Method2">'Results - Activity period'!$I$49</definedName>
     <definedName name="X_Cell_Crop_AreaUnderCropping">'Input - Crop'!$E$12</definedName>
-    <definedName name="X_Cell_Crop_AverageWeightPerBale">'Input - Crop'!$E$34</definedName>
-    <definedName name="X_Cell_Crop_CropPurpose">'Input - Crop'!$E$10</definedName>
+    <definedName name="X_Cell_Crop_AverageWeightPerBale">'Input - Crop'!$E$39</definedName>
+    <definedName name="X_Cell_Crop_AverageWeightPerRoundModule">'Input - Crop'!$E$15</definedName>
+    <definedName name="X_Cell_Crop_CottonSeedAmountPerRoundModule">'Input - Crop'!$E$25</definedName>
+    <definedName name="X_Cell_Crop_CottonseedYieldTotal">'Input - Crop'!$E$26</definedName>
     <definedName name="X_Cell_Crop_CropType">'Input - Crop'!$E$9</definedName>
-    <definedName name="X_Cell_Crop_PercentResidueBaled">'Input - Crop'!$E$33</definedName>
-    <definedName name="X_Cell_Crop_PercentResidueBurned">'Input - Crop'!$E$39</definedName>
-    <definedName name="X_Cell_Crop_TotalResidueBaled">'Input - Crop'!$E$36</definedName>
-    <definedName name="X_Cell_Enterprise_GrainYield">'Input - Enterprise'!$E$22</definedName>
-    <definedName name="X_Cell_Enterprise_PercentGrainSold">'Input - Enterprise'!$E$23</definedName>
-    <definedName name="X_Cell_Enterprise_PercentGrainUsedAsFeed">'Input - Enterprise'!$E$24</definedName>
-    <definedName name="X_Cell_Enterprise_PercentIncomeFromBaledHaySilage">'Input - Enterprise'!$E$33</definedName>
-    <definedName name="X_Cell_Enterprise_PercentIncomeFromGrain">'Input - Enterprise'!$E$32</definedName>
+    <definedName name="X_Cell_Crop_IrrigationMethod">'Input - Crop'!$E$10</definedName>
+    <definedName name="X_Cell_Crop_LintBalesPerRoundModule">'Input - Crop'!$E$21</definedName>
+    <definedName name="X_Cell_Crop_LintYieldTotal">'Input - Crop'!$E$22</definedName>
+    <definedName name="X_Cell_Crop_NumberOfBales">'Input - Crop'!$E$40</definedName>
+    <definedName name="X_Cell_Crop_PercentResidueBaled">'Input - Crop'!$E$38</definedName>
+    <definedName name="X_Cell_Crop_PercentResidueBurned">'Input - Crop'!#REF!</definedName>
+    <definedName name="X_Cell_Crop_ResidueAfterHarvest">'Input - Crop'!$E$35</definedName>
+    <definedName name="X_Cell_Crop_ResidueToCropRatio">'Input - Crop'!$E$34</definedName>
+    <definedName name="X_Cell_Crop_RoundModulesPerHectare">'Input - Crop'!$E$17</definedName>
+    <definedName name="X_Cell_Crop_TotalResidueBaled">'Input - Crop'!$E$41</definedName>
+    <definedName name="X_Cell_Crop_TotalResidueBurned">'Input - Crop'!#REF!</definedName>
+    <definedName name="X_Cell_Crop_TotalResidueRemainingOnPaddocks">'Input - Crop'!$E$43</definedName>
+    <definedName name="X_Cell_Crop_TotalRoundModules">'Input - Crop'!$E$16</definedName>
+    <definedName name="X_Cell_Crop_TotalUnprocessedCottonYield">'Input - Crop'!$E$30</definedName>
+    <definedName name="X_Cell_Crop_TrashTotalProduced">'Input - Crop'!$E$28</definedName>
+    <definedName name="X_Cell_Crop_TurnoutRate">'Input - Crop'!$E$20</definedName>
+    <definedName name="X_Cell_Crop_WeightPerLintBale">'Input - Crop'!$E$19</definedName>
+    <definedName name="X_Cell_Crop_YieldPerHectare">'Input - Crop'!$E$23</definedName>
+    <definedName name="X_Cell_Enterprise_CottonLintYield">'Input - Enterprise'!$E$22</definedName>
+    <definedName name="X_Cell_Enterprise_CottonseedYield">'Input - Enterprise'!$E$26</definedName>
+    <definedName name="X_Cell_Enterprise_PercentCottonLintSold">'Input - Enterprise'!$E$23</definedName>
+    <definedName name="X_Cell_Enterprise_PercentCottonseedSold">'Input - Enterprise'!$E$27</definedName>
+    <definedName name="X_Cell_Enterprise_PercentIncomeFromCottonLint">'Input - Enterprise'!$E$32</definedName>
+    <definedName name="X_Cell_Enterprise_PercentIncomeFromCottonseed">'Input - Enterprise'!$E$33</definedName>
     <definedName name="X_Cell_Enterprise_ProductionTimeframeEnd">'Input - Enterprise'!$E$19</definedName>
     <definedName name="X_Cell_Enterprise_ProductionTimeframeStart">'Input - Enterprise'!$E$18</definedName>
     <definedName name="X_Cell_Fertiliser_AreaUnderCropping">'Input - Fert Prod System'!$E$10</definedName>
     <definedName name="X_Cell_Fertiliser_CropType">'Input - Fert Prod System'!$E$8</definedName>
     <definedName name="X_Cell_Fertiliser_IrrigationMethod">'Input - Fert Prod System'!$E$9</definedName>
     <definedName name="X_Cell_Fertiliser_ProductionSystem">'Input - Fert Prod System'!$E$7</definedName>
-    <definedName name="X_Cell_PercentBaledHaySold">'Input - Enterprise'!$E$28</definedName>
-    <definedName name="X_Cell_PercentBaledHayUsedOnFarm">'Input - Enterprise'!$E$29</definedName>
     <definedName name="X_Cell_Site_AverageTemperature">'Input - Site'!$E$14</definedName>
     <definedName name="X_Cell_Site_ClimateZone">'Input - Site'!$E$20</definedName>
     <definedName name="X_Cell_Site_Elevation">'Input - Site'!$E$13</definedName>
@@ -273,8 +285,8 @@
     <definedName name="X_Cell_Site_TemperatureZone">'Input - Site'!$E$22</definedName>
     <definedName name="X_Cell_Site_TotalRainfall">'Input - Site'!$E$15</definedName>
     <definedName name="X_Cell_Site_WetOrDryClimateZone">'Input - Site'!$E$21</definedName>
-    <definedName name="X_Table_Result_ActivityPeriodEmissions_RowsToCols">'Results - Activity period'!$D$33:$F$38</definedName>
-    <definedName name="X_Table_Result_CarbonRemovalsFromPlantings_RowsToCols">'Results - Activity period'!$D$44:$E$49</definedName>
+    <definedName name="X_Table_Result_ActivityPeriodEmissions_RowsToCols">'Results - Activity period'!$D$31:$F$36</definedName>
+    <definedName name="X_Table_Result_CarbonRemovalsFromPlantings_RowsToCols">'Results - Activity period'!$D$42:$E$47</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -334,7 +346,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="334">
   <si>
     <t>Home</t>
   </si>
@@ -765,12 +777,6 @@
     <t>Co-product</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Residual product</t>
-  </si>
-  <si>
     <t>CO2 removed attributed to this enterprise</t>
   </si>
   <si>
@@ -840,45 +846,9 @@
     <t>percent</t>
   </si>
   <si>
-    <t>Grain yield</t>
-  </si>
-  <si>
-    <t>Percentage of income from grain sold</t>
-  </si>
-  <si>
-    <t>Baled hay/silage yield</t>
-  </si>
-  <si>
-    <t>Percentage of income from baled hay/silage sold</t>
-  </si>
-  <si>
-    <t>Percent grain sold</t>
-  </si>
-  <si>
-    <t>Percent grain used as feed on own farm</t>
-  </si>
-  <si>
     <t>Percent grain stored and not sold or used</t>
   </si>
   <si>
-    <t>Percent baled hay/silage sold</t>
-  </si>
-  <si>
-    <t>Percent baled hay/silage used as feed on own farm</t>
-  </si>
-  <si>
-    <t>Grain used as feed on own farm</t>
-  </si>
-  <si>
-    <t>Baled haysilage used as feed on own farm</t>
-  </si>
-  <si>
-    <t>t co2e/t grain sold</t>
-  </si>
-  <si>
-    <t>t co2e/t baled hay/silage</t>
-  </si>
-  <si>
     <t>Economic emissions assignment</t>
   </si>
   <si>
@@ -915,12 +885,6 @@
     <t>6.1.1.1-2 Crop residue N2O</t>
   </si>
   <si>
-    <t>6.4.1.1-2 Residue burning CH4</t>
-  </si>
-  <si>
-    <t>6.4.1.1-2 Residue burning N2O</t>
-  </si>
-  <si>
     <t>Input - Fertiliser Production System</t>
   </si>
   <si>
@@ -1309,15 +1273,6 @@
   </si>
   <si>
     <t>Total residue baled</t>
-  </si>
-  <si>
-    <t>Burned residue</t>
-  </si>
-  <si>
-    <t>Percentage of residue that was burned</t>
-  </si>
-  <si>
-    <t>Total residue burned</t>
   </si>
   <si>
     <t>Residue retained on paddocks</t>
@@ -1411,6 +1366,60 @@
   </si>
   <si>
     <t>Total cottonseed produced</t>
+  </si>
+  <si>
+    <t>Total trash produced</t>
+  </si>
+  <si>
+    <t>Lint yield per hectare</t>
+  </si>
+  <si>
+    <t>tonnes / hectare</t>
+  </si>
+  <si>
+    <t>Residue after harvest</t>
+  </si>
+  <si>
+    <t>Cotton lint sold - excluding removals</t>
+  </si>
+  <si>
+    <t>Cotton lint sold - net emissions</t>
+  </si>
+  <si>
+    <t>Cottonseed sold - excluding removals</t>
+  </si>
+  <si>
+    <t>Cottonseed sold - net emissions</t>
+  </si>
+  <si>
+    <t>Cotton lint yield</t>
+  </si>
+  <si>
+    <t>Percent cotton lint sold</t>
+  </si>
+  <si>
+    <t>Percent cotton lint stored and not sold</t>
+  </si>
+  <si>
+    <t>Cottonseed yield</t>
+  </si>
+  <si>
+    <t>Percent cottonseed sold</t>
+  </si>
+  <si>
+    <t>Percentage of income from cotton lint sold</t>
+  </si>
+  <si>
+    <t>Percentage of income from cottonseed sold</t>
+  </si>
+  <si>
+    <t>Unprocessed cotton yield</t>
+  </si>
+  <si>
+    <t>t co2e/t cotton lint sold</t>
+  </si>
+  <si>
+    <t>t co2e/t cottonseed sold</t>
   </si>
 </sst>
 </file>
@@ -1884,7 +1893,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -2081,6 +2090,15 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2273,7 +2291,7 @@
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="8">
       <alignment horizontal="left" vertical="center"/>
@@ -2561,6 +2579,15 @@
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="2" xfId="16" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="23" fillId="4" borderId="2" xfId="46">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="18" xfId="8" applyBorder="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="53" applyBorder="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="69">
@@ -3845,9 +3872,9 @@
   </tableStyles>
   <colors>
     <mruColors>
+      <color rgb="FFC44340"/>
       <color rgb="FF0C769E"/>
       <color rgb="FFCC6600"/>
-      <color rgb="FFC44340"/>
       <color rgb="FF008000"/>
       <color rgb="FFFFCCCC"/>
       <color rgb="FFC4433F"/>
@@ -4095,7 +4122,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent3">
+                <a:schemeClr val="accent5">
                   <a:lumMod val="60000"/>
                 </a:schemeClr>
               </a:solidFill>
@@ -4117,7 +4144,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent4">
+                <a:schemeClr val="accent6">
                   <a:lumMod val="60000"/>
                 </a:schemeClr>
               </a:solidFill>
@@ -4139,8 +4166,9 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="60000"/>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:ln w="19050">
@@ -4161,8 +4189,9 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="60000"/>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:ln w="19050">
@@ -4183,7 +4212,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent1">
+                <a:schemeClr val="accent3">
                   <a:lumMod val="80000"/>
                   <a:lumOff val="20000"/>
                 </a:schemeClr>
@@ -4206,7 +4235,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2">
+                <a:schemeClr val="accent4">
                   <a:lumMod val="80000"/>
                   <a:lumOff val="20000"/>
                 </a:schemeClr>
@@ -4229,7 +4258,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent3">
+                <a:schemeClr val="accent5">
                   <a:lumMod val="80000"/>
                   <a:lumOff val="20000"/>
                 </a:schemeClr>
@@ -4252,7 +4281,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent4">
+                <a:schemeClr val="accent6">
                   <a:lumMod val="80000"/>
                   <a:lumOff val="20000"/>
                 </a:schemeClr>
@@ -4270,57 +4299,11 @@
               </c:ext>
             </c:extLst>
           </c:dPt>
-          <c:dPt>
-            <c:idx val="16"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000010-64C2-43EC-A71A-E7C288A256BA}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="17"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000011-64C2-43EC-A71A-E7C288A256BA}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
           <c:cat>
             <c:strRef>
-              <c:f>'Results - Activity period'!$D$9:$D$26</c:f>
+              <c:f>'Results - Activity period'!$D$9:$D$24</c:f>
               <c:strCache>
-                <c:ptCount val="18"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>5.1.1.1-2 Inorganic fert N2O</c:v>
                 </c:pt>
@@ -4346,33 +4329,27 @@
                   <c:v>6.3.1.1-2 Leach &amp; runoff (crop)</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.4.1.1-2 Residue burning N2O</c:v>
+                  <c:v>8.1.1.1-2 Transport fuel CO2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6.4.1.1-2 Residue burning CH4</c:v>
+                  <c:v>8.1.1.1-2 Transport fuel CH4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>8.1.1.1-2 Transport fuel CO2</c:v>
+                  <c:v>8.1.1.1-2 Transport fuel N2O</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>8.1.1.1-2 Transport fuel CH4</c:v>
+                  <c:v>8.2.1.1-2 Stationary fuel CO2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>8.1.1.1-2 Transport fuel N2O</c:v>
+                  <c:v>8.2.1.1-2 Stationary fuel CH4</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>8.2.1.1-2 Stationary fuel CO2</c:v>
+                  <c:v>8.2.1.1-2 Stationary fuel N2O</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>8.2.1.1-2 Stationary fuel CH4</c:v>
+                  <c:v>14.1.1-2 Purchased electricity (Location-based)</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>8.2.1.1-2 Stationary fuel N2O</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>14.1.1-2 Purchased electricity (Location-based)</c:v>
-                </c:pt>
-                <c:pt idx="17">
                   <c:v>14.1.1-2 Purchased electricity (Market-based)</c:v>
                 </c:pt>
               </c:strCache>
@@ -4380,10 +4357,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Results - Activity period'!$I$9:$I$26</c:f>
+              <c:f>'Results - Activity period'!$I$9:$I$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4430,12 +4407,6 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4590,7 +4561,7 @@
           <c:order val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Results - Activity period'!$D$40:$D$50</c:f>
+              <c:f>'Results - Activity period'!$D$38:$D$48</c:f>
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
@@ -4631,7 +4602,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Results - Activity period'!$I$40:$I$50</c:f>
+              <c:f>'Results - Activity period'!$I$38:$I$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -6239,13 +6210,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>938212</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>200025</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>1443037</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6448,7 +6419,7 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>108696</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="$H$53">
+    <xdr:sp macro="" textlink="$H$52">
       <xdr:nvSpPr>
         <xdr:cNvPr id="5" name="TextBox 4">
           <a:extLst>
@@ -6529,7 +6500,7 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>89646</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="$I$53">
+    <xdr:sp macro="" textlink="$I$52">
       <xdr:nvSpPr>
         <xdr:cNvPr id="6" name="TextBox 5">
           <a:extLst>
@@ -7731,7 +7702,7 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>49306</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1978747" cy="254493"/>
+    <xdr:ext cx="1955985" cy="254557"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="22" name="TextBox 21">
@@ -7745,8 +7716,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2686050" y="3373531"/>
-          <a:ext cx="1978747" cy="254493"/>
+          <a:off x="2686050" y="4145056"/>
+          <a:ext cx="1955985" cy="254557"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7785,7 +7756,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>t CO2-e / tonne liveweight sold</a:t>
+            <a:t>t CO2-e / tonne cotton lint sold</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-AU">
@@ -8299,7 +8270,7 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>49306</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1978747" cy="254493"/>
+    <xdr:ext cx="1952458" cy="239809"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="30" name="TextBox 29">
@@ -8313,8 +8284,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5009590" y="3373531"/>
-          <a:ext cx="1978747" cy="254493"/>
+          <a:off x="5009590" y="4145056"/>
+          <a:ext cx="1952458" cy="239809"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8353,26 +8324,8 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>t CO2-e / tonne liveweight sold</a:t>
+            <a:t>t CO2-e / tonne cotton lint sold </a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="en-AU">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-AU" sz="1000">
-            <a:solidFill>
-              <a:schemeClr val="bg2">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -8385,7 +8338,7 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>49306</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1978747" cy="254493"/>
+    <xdr:ext cx="1952458" cy="239809"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="31" name="TextBox 30">
@@ -8399,8 +8352,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8352864" y="3373531"/>
-          <a:ext cx="1978747" cy="254493"/>
+          <a:off x="8352864" y="4145056"/>
+          <a:ext cx="1952458" cy="239809"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8439,26 +8392,8 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>t CO2-e / tonne liveweight sold</a:t>
+            <a:t>t CO2-e / tonne cotton lint sold </a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="en-AU">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-AU" sz="1000">
-            <a:solidFill>
-              <a:schemeClr val="bg2">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -8471,7 +8406,7 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>49306</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1978747" cy="254493"/>
+    <xdr:ext cx="1952458" cy="239809"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="32" name="TextBox 31">
@@ -8485,8 +8420,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10837769" y="3373531"/>
-          <a:ext cx="1978747" cy="254493"/>
+          <a:off x="10837769" y="4145056"/>
+          <a:ext cx="1952458" cy="239809"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8525,26 +8460,8 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>t CO2-e / tonne liveweight sold</a:t>
+            <a:t>t CO2-e / tonne cotton lint sold </a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="en-AU">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-AU" sz="1000">
-            <a:solidFill>
-              <a:schemeClr val="bg2">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -8557,7 +8474,7 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>38660</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1978747" cy="254493"/>
+    <xdr:ext cx="1952458" cy="239809"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="33" name="TextBox 32">
@@ -8571,8 +8488,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2686050" y="5763185"/>
-          <a:ext cx="1978747" cy="254493"/>
+          <a:off x="2686050" y="7106210"/>
+          <a:ext cx="1952458" cy="239809"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8611,26 +8528,8 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>t CO2-e / tonne liveweight sold</a:t>
+            <a:t>t CO2-e / tonne cotton lint sold </a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="en-AU">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-AU" sz="1000">
-            <a:solidFill>
-              <a:schemeClr val="bg2">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -8643,7 +8542,7 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>38660</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1978747" cy="254493"/>
+    <xdr:ext cx="1952458" cy="239809"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="34" name="TextBox 33">
@@ -8657,8 +8556,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5019115" y="5763185"/>
-          <a:ext cx="1978747" cy="254493"/>
+          <a:off x="5019115" y="7106210"/>
+          <a:ext cx="1952458" cy="239809"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8697,26 +8596,8 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>t CO2-e / tonne liveweight sold</a:t>
+            <a:t>t CO2-e / tonne cotton lint sold </a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="en-AU">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-AU" sz="1000">
-            <a:solidFill>
-              <a:schemeClr val="bg2">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -8729,7 +8610,7 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>38660</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1978747" cy="254493"/>
+    <xdr:ext cx="1952458" cy="239809"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="35" name="TextBox 34">
@@ -8743,8 +8624,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8352864" y="5763185"/>
-          <a:ext cx="1978747" cy="254493"/>
+          <a:off x="8352864" y="7106210"/>
+          <a:ext cx="1952458" cy="239809"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8783,26 +8664,8 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>t CO2-e / tonne liveweight sold</a:t>
+            <a:t>t CO2-e / tonne cotton lint sold </a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="en-AU">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-AU" sz="1000">
-            <a:solidFill>
-              <a:schemeClr val="bg2">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -8815,7 +8678,7 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>38660</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1978747" cy="254493"/>
+    <xdr:ext cx="1952458" cy="239809"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="36" name="TextBox 35">
@@ -8829,8 +8692,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10837769" y="5763185"/>
-          <a:ext cx="1978747" cy="254493"/>
+          <a:off x="10837769" y="7106210"/>
+          <a:ext cx="1952458" cy="239809"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8869,26 +8732,8 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>t CO2-e / tonne liveweight sold</a:t>
+            <a:t>t CO2-e / tonne cotton lint sold </a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="en-AU">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-AU" sz="1000">
-            <a:solidFill>
-              <a:schemeClr val="bg2">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -8907,7 +8752,7 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>108696</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="$H$54">
+    <xdr:sp macro="" textlink="$H$53">
       <xdr:nvSpPr>
         <xdr:cNvPr id="37" name="TextBox 36">
           <a:extLst>
@@ -8988,7 +8833,7 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>89646</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="$I$54">
+    <xdr:sp macro="" textlink="$I$53">
       <xdr:nvSpPr>
         <xdr:cNvPr id="38" name="TextBox 37">
           <a:extLst>
@@ -9069,7 +8914,7 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>144555</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="$H$47">
+    <xdr:sp macro="" textlink="$H$46">
       <xdr:nvSpPr>
         <xdr:cNvPr id="39" name="TextBox 38">
           <a:extLst>
@@ -9150,7 +8995,7 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>144555</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="$I$47">
+    <xdr:sp macro="" textlink="$I$46">
       <xdr:nvSpPr>
         <xdr:cNvPr id="40" name="TextBox 39">
           <a:extLst>
@@ -9231,7 +9076,7 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>108696</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="$H$56">
+    <xdr:sp macro="" textlink="$H$54">
       <xdr:nvSpPr>
         <xdr:cNvPr id="41" name="TextBox 40">
           <a:extLst>
@@ -9312,7 +9157,7 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>89646</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="$I$56">
+    <xdr:sp macro="" textlink="$I$54">
       <xdr:nvSpPr>
         <xdr:cNvPr id="42" name="TextBox 41">
           <a:extLst>
@@ -9393,7 +9238,7 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>144555</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="$H$48">
+    <xdr:sp macro="" textlink="$H$47">
       <xdr:nvSpPr>
         <xdr:cNvPr id="43" name="TextBox 42">
           <a:extLst>
@@ -9474,7 +9319,7 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>144555</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="$I$48">
+    <xdr:sp macro="" textlink="$I$47">
       <xdr:nvSpPr>
         <xdr:cNvPr id="44" name="TextBox 43">
           <a:extLst>
@@ -10514,7 +10359,7 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>49306</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1978747" cy="254493"/>
+    <xdr:ext cx="2030941" cy="239809"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="58" name="TextBox 57">
@@ -10528,8 +10373,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14935200" y="3373531"/>
-          <a:ext cx="1978747" cy="254493"/>
+          <a:off x="14935200" y="4145056"/>
+          <a:ext cx="2030941" cy="239809"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10568,26 +10413,8 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>t CO2-e / tonne liveweight sold</a:t>
+            <a:t>t CO2-e / tonne cottonseed sold </a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="en-AU">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-AU" sz="1000">
-            <a:solidFill>
-              <a:schemeClr val="bg2">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -10987,7 +10814,7 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>49306</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1978747" cy="254493"/>
+    <xdr:ext cx="2030941" cy="239809"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="65" name="TextBox 64">
@@ -11001,8 +10828,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17267704" y="3373531"/>
-          <a:ext cx="1978747" cy="254493"/>
+          <a:off x="17267704" y="4145056"/>
+          <a:ext cx="2030941" cy="239809"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -11041,26 +10868,8 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>t CO2-e / tonne liveweight sold</a:t>
+            <a:t>t CO2-e / tonne cottonseed sold </a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="en-AU">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-AU" sz="1000">
-            <a:solidFill>
-              <a:schemeClr val="bg2">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -11073,7 +10882,7 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>49306</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1978747" cy="254493"/>
+    <xdr:ext cx="2030941" cy="239809"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="66" name="TextBox 65">
@@ -11087,8 +10896,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20616582" y="3373531"/>
-          <a:ext cx="1978747" cy="254493"/>
+          <a:off x="20616582" y="4145056"/>
+          <a:ext cx="2030941" cy="239809"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -11127,26 +10936,8 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>t CO2-e / tonne liveweight sold</a:t>
+            <a:t>t CO2-e / tonne cottonseed sold </a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="en-AU">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-AU" sz="1000">
-            <a:solidFill>
-              <a:schemeClr val="bg2">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -11159,7 +10950,7 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>49306</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1978747" cy="254493"/>
+    <xdr:ext cx="2030941" cy="239809"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="67" name="TextBox 66">
@@ -11173,8 +10964,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="23101487" y="3373531"/>
-          <a:ext cx="1978747" cy="254493"/>
+          <a:off x="23101487" y="4145056"/>
+          <a:ext cx="2030941" cy="239809"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -11213,26 +11004,8 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>t CO2-e / tonne liveweight sold</a:t>
+            <a:t>t CO2-e / tonne cottonseed sold </a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="en-AU">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-AU" sz="1000">
-            <a:solidFill>
-              <a:schemeClr val="bg2">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -11245,7 +11018,7 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>38660</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1978747" cy="254493"/>
+    <xdr:ext cx="2030941" cy="239809"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="68" name="TextBox 67">
@@ -11259,8 +11032,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14935200" y="5763185"/>
-          <a:ext cx="1978747" cy="254493"/>
+          <a:off x="14935200" y="7106210"/>
+          <a:ext cx="2030941" cy="239809"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -11299,26 +11072,8 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>t CO2-e / tonne liveweight sold</a:t>
+            <a:t>t CO2-e / tonne cottonseed sold </a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="en-AU">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-AU" sz="1000">
-            <a:solidFill>
-              <a:schemeClr val="bg2">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -11331,7 +11086,7 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>38660</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1978747" cy="254493"/>
+    <xdr:ext cx="2030941" cy="239809"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="69" name="TextBox 68">
@@ -11345,8 +11100,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17277229" y="5763185"/>
-          <a:ext cx="1978747" cy="254493"/>
+          <a:off x="17277229" y="7106210"/>
+          <a:ext cx="2030941" cy="239809"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -11385,26 +11140,8 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>t CO2-e / tonne liveweight sold</a:t>
+            <a:t>t CO2-e / tonne cottonseed sold </a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="en-AU">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-AU" sz="1000">
-            <a:solidFill>
-              <a:schemeClr val="bg2">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -11417,7 +11154,7 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>38660</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1978747" cy="254493"/>
+    <xdr:ext cx="2030941" cy="239809"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="70" name="TextBox 69">
@@ -11431,8 +11168,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20616582" y="5763185"/>
-          <a:ext cx="1978747" cy="254493"/>
+          <a:off x="20616582" y="7106210"/>
+          <a:ext cx="2030941" cy="239809"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -11471,26 +11208,8 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>t CO2-e / tonne liveweight sold</a:t>
+            <a:t>t CO2-e / tonne cottonseed sold </a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="en-AU">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-AU" sz="1000">
-            <a:solidFill>
-              <a:schemeClr val="bg2">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -11503,7 +11222,7 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>29135</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1978747" cy="254493"/>
+    <xdr:ext cx="2030941" cy="239809"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="71" name="TextBox 70">
@@ -11517,8 +11236,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="23168162" y="5753660"/>
-          <a:ext cx="1978747" cy="254493"/>
+          <a:off x="23168162" y="7096685"/>
+          <a:ext cx="2030941" cy="239809"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -11557,26 +11276,8 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>t CO2-e / tonne liveweight sold</a:t>
+            <a:t>t CO2-e / tonne cottonseed sold </a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="en-AU">
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-AU" sz="1000">
-            <a:solidFill>
-              <a:schemeClr val="bg2">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -11595,7 +11296,7 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>108696</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="$H$57">
+    <xdr:sp macro="" textlink="$H$55">
       <xdr:nvSpPr>
         <xdr:cNvPr id="72" name="TextBox 71">
           <a:extLst>
@@ -11676,7 +11377,7 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>80121</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="$I$57">
+    <xdr:sp macro="" textlink="$I$55">
       <xdr:nvSpPr>
         <xdr:cNvPr id="73" name="TextBox 72">
           <a:extLst>
@@ -11801,7 +11502,7 @@
         <a:p>
           <a:r>
             <a:rPr lang="en-AU" sz="1800"/>
-            <a:t>Grain sold</a:t>
+            <a:t>Cotton lint sold</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -11813,7 +11514,7 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>113741</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>38099</xdr:rowOff>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
@@ -11835,20 +11536,20 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect l="6954" r="6954"/>
+        <a:srcRect l="115" r="115"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2790266" y="962024"/>
-          <a:ext cx="841254" cy="793939"/>
+          <a:off x="2790266" y="1304925"/>
+          <a:ext cx="841254" cy="841563"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -11938,7 +11639,7 @@
         <a:p>
           <a:r>
             <a:rPr lang="en-AU" sz="1800"/>
-            <a:t>Baled hay/silage sold</a:t>
+            <a:t>Cottonseed sold</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -11972,20 +11673,20 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect l="4962" r="4962"/>
+        <a:srcRect l="11117" r="11117"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="14976136" y="923925"/>
-          <a:ext cx="927642" cy="879662"/>
+          <a:off x="14976136" y="1123950"/>
+          <a:ext cx="927642" cy="1070162"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -12022,13 +11723,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>938212</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>200025</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>1443037</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -12057,92 +11758,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Home"/>
-      <sheetName val="Overview"/>
-      <sheetName val="Results"/>
-      <sheetName val="Input - Site"/>
-      <sheetName val="Input - Crop"/>
-      <sheetName val="Input - Pasture"/>
-      <sheetName val="6.1.1.1-2 Crop residue N2O"/>
-      <sheetName val="6.2.1.1-2 Pasture residue N2O"/>
-      <sheetName val="6.3.1.1-2 Leaching and runoff"/>
-      <sheetName val="6.3.1.1-2 Leach runoff crop"/>
-      <sheetName val="6.3.1.1-2 Leach runoff pasture"/>
-      <sheetName val="6.4.1.1-2 Residue burning"/>
-      <sheetName val="Constants - Ag Residue"/>
-      <sheetName val="Constants - Common"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12">
-        <row r="8">
-          <cell r="D8" t="str">
-            <v>Cash grain crop</v>
-          </cell>
-          <cell r="E8" t="str">
-            <v>grain</v>
-          </cell>
-          <cell r="F8" t="str">
-            <v>yield</v>
-          </cell>
-          <cell r="G8" t="str">
-            <v>harvest</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="D9" t="str">
-            <v>Cash crop for hay/silage</v>
-          </cell>
-          <cell r="E9" t="str">
-            <v>above ground biomass</v>
-          </cell>
-          <cell r="F9" t="str">
-            <v>yield</v>
-          </cell>
-          <cell r="G9" t="str">
-            <v>harvest</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="D10" t="str">
-            <v>Cover crop</v>
-          </cell>
-          <cell r="E10" t="str">
-            <v>above ground biomass</v>
-          </cell>
-          <cell r="F10" t="str">
-            <v>mass</v>
-          </cell>
-          <cell r="G10" t="str">
-            <v>end of crop cycle</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="13" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13121,31 +12736,31 @@
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25" ht="30" customHeight="1">
+    <row r="1" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="3" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="82" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="6" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="83" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
+    <row r="7" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
+    <row r="8" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -13162,8 +12777,8 @@
     <tabColor rgb="FF0C769E"/>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:K87"/>
-  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
+  <dimension ref="A1:K61"/>
+  <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="2.7109375" customWidth="1"/>
@@ -13180,7 +12795,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="93" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="D1" s="93"/>
       <c r="E1" s="93"/>
@@ -13191,7 +12806,7 @@
       <c r="J1" s="93"/>
       <c r="K1" s="93"/>
     </row>
-    <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -13203,7 +12818,7 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -13218,7 +12833,7 @@
       <c r="J3" s="94"/>
       <c r="K3" s="94"/>
     </row>
-    <row r="4" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -13228,24 +12843,24 @@
         <v>Emissions breakdown for activities running between 01 January 2025 and 31 December 2025</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4"/>
     </row>
-    <row r="6" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="80" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Input - Pasture Beef'!A1", "Pasture Beef")</f>
         <v>Pasture Beef</v>
@@ -13270,10 +12885,10 @@
       </c>
       <c r="J8" s="12"/>
     </row>
-    <row r="9" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5"/>
       <c r="D9" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E9" s="1" t="e" cm="1">
         <f t="array" ref="E9">VEERG_5_1_1_1__1_InorganicFertiliserApplicationN2OEmissions_Result_Method1</f>
@@ -13298,12 +12913,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E10" s="1" t="e" cm="1">
         <f t="array" ref="E10">VEERG_5_1_1_3__1_InorganicFertiliserApplicationCO2Emissions_Result_Method1</f>
@@ -13314,7 +12929,7 @@
         <v>#NAME?</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H10" s="1" t="e">
         <f>E10</f>
@@ -13328,13 +12943,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.1-2 Methane'!A1", "4.2.1.1-2 Methane")</f>
         <v>4.2.1.1-2 Methane</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E11" s="1" t="e" cm="1">
         <f t="array" ref="E11">VEERG_5_2_1_1__2_MassOfNitrogenInOrganicFertiliser_Result_Method1</f>
@@ -13359,13 +12974,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.3-4 Soil direct N2O'!A1", "4.2.1.3-4 Soil direct N2O")</f>
         <v>4.2.1.3-4 Soil direct N2O</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E12" s="1" t="e" cm="1">
         <f t="array" ref="E12">VEERG_5_3_1_1__1_LimeApplicationCO2Emissions_Result_Method1</f>
@@ -13376,7 +12991,7 @@
         <v>#NAME?</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H12" s="1" t="e">
         <f>E12</f>
@@ -13390,13 +13005,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.5-6 Soil Atmos Dep'!A1", "4.2.1.5-6 Soil atm. deposition")</f>
         <v>4.2.1.5-6 Soil atm. deposition</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E13" s="1" t="e" cm="1">
         <f t="array" ref="E13">VEERG_5_4_1_3__1_OrganicFertiliserAtmosphericDepositionN2OEmissions_Result_Method1</f>
@@ -13421,13 +13036,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.7-8 Soil leach runoff'!A1", "4.2.1.7-8 Soil leach &amp; runoff")</f>
         <v>4.2.1.7-8 Soil leach &amp; runoff</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E14" s="1" t="e" cm="1">
         <f t="array" ref="E14">VEERG_5_5_1_1__1_FertiliserLeachingAndRunoffN2OEmissions_result_Method1</f>
@@ -13452,10 +13067,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5"/>
       <c r="D15" s="1" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="E15" s="1" t="e" cm="1">
         <f t="array" ref="E15">VEERG_6_1_1_1__1__NitrousOxideEmissionsFromCropResidues_Result_Method1</f>
@@ -13480,12 +13095,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="E16" s="1" t="e" cm="1">
         <f t="array" ref="E16">VEERG_6_3_1_1__1__LeachingAndRunoffEmissionsCropAndPastureResidue_CropOnly_Result_Method1</f>
@@ -13510,51 +13125,51 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="str">
         <f>HYPERLINK("#'Constants - Pasture Beef'!A1", "Constants - Pasture Beef")</f>
         <v>Constants - Pasture Beef</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>176</v>
+        <v>138</v>
       </c>
       <c r="E17" s="1" t="e" cm="1">
-        <f t="array" ref="E17">VEERG_6_4_1_1__2__NitrousOxideEmissionsFromBurningOfCropResidues_Result_Method1</f>
+        <f t="array" ref="E17">VEERG_8_1_1_1__1_FuelCombustionTransport_Result_CO2</f>
         <v>#NAME?</v>
       </c>
       <c r="F17" s="1" t="e">
-        <f t="shared" ref="F17:F22" si="0">E17</f>
+        <f>E17</f>
         <v>#NAME?</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17" s="1" t="e" cm="1">
-        <f t="array" ref="H17">Common_Equations.Common_ConvertN2OToCO2e(E17,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>126</v>
+      </c>
+      <c r="H17" s="1" t="e">
+        <f>E17</f>
         <v>#NAME?</v>
       </c>
-      <c r="I17" s="1" t="e" cm="1">
-        <f t="array" ref="I17">Common_Equations.Common_ConvertN2OToCO2e(F17,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+      <c r="I17" s="1" t="e">
+        <f>F17</f>
         <v>#NAME?</v>
       </c>
       <c r="J17" s="10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="str">
         <f>HYPERLINK("#'Constants - Livestock'!A1", "Constants - Livestock")</f>
         <v>Constants - Livestock</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="E18" s="1" t="e" cm="1">
-        <f t="array" ref="E18">VEERG_6_4_1_1__1__MethaneEmissionsFromBurningOfCropResidues_Result_Method1</f>
+        <f t="array" ref="E18">VEERG_8_1_1_1__1_FuelCombustionTransport_Result_CH4</f>
         <v>#NAME?</v>
       </c>
       <c r="F18" s="1" t="e">
-        <f t="shared" si="0"/>
+        <f>E18</f>
         <v>#NAME?</v>
       </c>
       <c r="G18" s="10" t="s">
@@ -13572,102 +13187,102 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E19" s="1" t="e" cm="1">
-        <f t="array" ref="E19">VEERG_8_1_1_1__1_FuelCombustionTransport_Result_CO2</f>
+        <f t="array" ref="E19">VEERG_8_1_1_1__1_FuelCombustionTransport_Result_N2O</f>
         <v>#NAME?</v>
       </c>
       <c r="F19" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="H19" s="1" t="e">
         <f>E19</f>
         <v>#NAME?</v>
       </c>
-      <c r="I19" s="1" t="e">
-        <f>F19</f>
+      <c r="G19" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="1" t="e" cm="1">
+        <f t="array" ref="H19">Common_Equations.Common_ConvertN2OToCO2e(E19,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I19" s="1" t="e" cm="1">
+        <f t="array" ref="I19">Common_Equations.Common_ConvertN2OToCO2e(F19,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="J19" s="10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E20" s="1" t="e" cm="1">
-        <f t="array" ref="E20">VEERG_8_1_1_1__1_FuelCombustionTransport_Result_CH4</f>
+        <f t="array" ref="E20">VEERG_8_2_1_1__1_FuelCombustionStationary_Result_CO2</f>
         <v>#NAME?</v>
       </c>
       <c r="F20" s="1" t="e">
-        <f t="shared" si="0"/>
+        <f>E20</f>
         <v>#NAME?</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H20" s="1" t="e" cm="1">
-        <f t="array" ref="H20">Common_Equations.Common_ConvertCH4ToCO2e(E20,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>126</v>
+      </c>
+      <c r="H20" s="1" t="e">
+        <f>E20</f>
         <v>#NAME?</v>
       </c>
-      <c r="I20" s="1" t="e" cm="1">
-        <f t="array" ref="I20">Common_Equations.Common_ConvertCH4ToCO2e(F20,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+      <c r="I20" s="1" t="e">
+        <f>F20</f>
         <v>#NAME?</v>
       </c>
       <c r="J20" s="10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D21" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E21" s="1" t="e" cm="1">
-        <f t="array" ref="E21">VEERG_8_1_1_1__1_FuelCombustionTransport_Result_N2O</f>
+        <f t="array" ref="E21">VEERG_8_2_1_1__1_FuelCombustionStationary_Result_CH4</f>
         <v>#NAME?</v>
       </c>
       <c r="F21" s="1" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F21:F24" si="0">E21</f>
         <v>#NAME?</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H21" s="1" t="e" cm="1">
-        <f t="array" ref="H21">Common_Equations.Common_ConvertN2OToCO2e(E21,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" ref="H21">Common_Equations.Common_ConvertCH4ToCO2e(E21,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="I21" s="1" t="e" cm="1">
-        <f t="array" ref="I21">Common_Equations.Common_ConvertN2OToCO2e(F21,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <f t="array" ref="I21">Common_Equations.Common_ConvertCH4ToCO2e(F21,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="J21" s="10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5"/>
       <c r="D22" s="1" t="s">
         <v>143</v>
       </c>
       <c r="E22" s="1" t="e" cm="1">
-        <f t="array" ref="E22">VEERG_8_2_1_1__1_FuelCombustionStationary_Result_CO2</f>
+        <f t="array" ref="E22">VEERG_8_2_1_1__1_FuelCombustionStationary_Result_N2O</f>
         <v>#NAME?</v>
       </c>
       <c r="F22" s="1" t="e">
@@ -13675,450 +13290,444 @@
         <v>#NAME?</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="H22" s="1" t="e">
-        <f>E22</f>
+        <v>13</v>
+      </c>
+      <c r="H22" s="1" t="e" cm="1">
+        <f t="array" ref="H22">Common_Equations.Common_ConvertN2OToCO2e(E22,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
-      <c r="I22" s="1" t="e">
-        <f>F22</f>
+      <c r="I22" s="1" t="e" cm="1">
+        <f t="array" ref="I22">Common_Equations.Common_ConvertN2OToCO2e(F22,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
         <v>#NAME?</v>
       </c>
       <c r="J22" s="10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5"/>
       <c r="D23" s="1" t="s">
         <v>144</v>
       </c>
       <c r="E23" s="1" t="e" cm="1">
-        <f t="array" ref="E23">VEERG_8_2_1_1__1_FuelCombustionStationary_Result_CH4</f>
+        <f t="array" ref="E23">VEERG_14_1_1__1_LocationBasedScopeElectricityEmissions_Result_Method1</f>
         <v>#NAME?</v>
       </c>
       <c r="F23" s="1" t="e">
-        <f t="shared" ref="F23:F26" si="1">E23</f>
+        <f t="shared" si="0"/>
         <v>#NAME?</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H23" s="1" t="e" cm="1">
-        <f t="array" ref="H23">Common_Equations.Common_ConvertCH4ToCO2e(E23,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>8</v>
+      </c>
+      <c r="H23" s="1" t="e">
+        <f>E23</f>
         <v>#NAME?</v>
       </c>
-      <c r="I23" s="1" t="e" cm="1">
-        <f t="array" ref="I23">Common_Equations.Common_ConvertCH4ToCO2e(F23,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+      <c r="I23" s="1" t="e">
+        <f>F23</f>
         <v>#NAME?</v>
       </c>
       <c r="J23" s="10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5"/>
       <c r="D24" s="1" t="s">
         <v>145</v>
       </c>
       <c r="E24" s="1" t="e" cm="1">
-        <f t="array" ref="E24">VEERG_8_2_1_1__1_FuelCombustionStationary_Result_N2O</f>
+        <f t="array" ref="E24">VEERG_14_1_2__1_MarketBasedScopeElectricityEmissionsVariation_Result_Method1</f>
         <v>#NAME?</v>
       </c>
       <c r="F24" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="1" t="e">
+        <f>E24</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I24" s="1" t="e">
+        <f>F24</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D25" s="88" t="s">
+        <v>5</v>
+      </c>
+      <c r="E25" s="89"/>
+      <c r="F25" s="89"/>
+      <c r="G25" s="89"/>
+      <c r="H25" s="88" t="e">
+        <f>SUM(H9:H24)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I25" s="88" t="e">
+        <f>SUM(I9:I24)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J25" s="98" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D28" s="80" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D30" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="I30" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J30" s="12"/>
+    </row>
+    <row r="31" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D31" s="1" t="e" cm="1">
+        <f t="array" ref="D31">"14.1.1-2 Purchased electricity " &amp; IF(X_Cell_Electricity_CalculationMethod="Location-based (simpler)", "(Location-based)", "(Market-based)")</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="E31" s="1" t="e" cm="1">
+        <f t="array" ref="E31">IF(X_Cell_Electricity_CalculationMethod="Location-based (simpler)", VEERG_14_1_1__1_LocationBasedScopeElectricityEmissions_Result_Method1, VEERG_14_1_2__1_MarketBasedScopeElectricityEmissionsVariation_Result_Method1)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F31" s="1" t="e">
+        <f>E31</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="H31" s="1" t="e">
+        <f>E31</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I31" s="1" t="e">
+        <f>F31</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D32" s="88" t="s">
+        <v>259</v>
+      </c>
+      <c r="E32" s="89"/>
+      <c r="F32" s="89"/>
+      <c r="G32" s="89"/>
+      <c r="H32" s="88" t="e">
+        <f>SUM(H31:H31)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I32" s="88" t="e">
+        <f>SUM(I31:I31)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J32" s="98" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D35" s="80" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="37" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D37" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J37" s="12"/>
+    </row>
+    <row r="38" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D38" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E38" s="1" t="e" cm="1">
+        <f t="array" ref="E38">VEERG_15_4_1_1__2_EmissionsFromPurchasedFertiliserComponentsVariation_Result_Method1</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F38" s="1" t="e" cm="1">
+        <f t="array" ref="F38">VEERG_15_4_1_1__2_EmissionsFromPurchasedFertiliserComponentsVariation_Result_Method2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="H38" s="1" t="e">
+        <f t="shared" ref="H38:H45" si="1">E38</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I38" s="1" t="e">
+        <f t="shared" ref="I38:I48" si="2">F38</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D39" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="E39" s="1" t="e" cm="1">
+        <f t="array" ref="E39">VEERG_15_5_1_1__1_EmissionsFromPurchasedAgrichemicals_Result_Method1</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F39" s="1" t="e" cm="1">
+        <f t="array" ref="F39">VEERG_15_5_1_1__1_EmissionsFromPurchasedAgrichemicals_Result_Method2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="H39" s="1" t="e">
         <f t="shared" si="1"/>
         <v>#NAME?</v>
       </c>
-      <c r="G24" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="H24" s="1" t="e" cm="1">
-        <f t="array" ref="H24">Common_Equations.Common_ConvertN2OToCO2e(E24,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+      <c r="I39" s="1" t="e">
+        <f t="shared" si="2"/>
         <v>#NAME?</v>
       </c>
-      <c r="I24" s="1" t="e" cm="1">
-        <f t="array" ref="I24">Common_Equations.Common_ConvertN2OToCO2e(F24,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+      <c r="J39" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D40" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E40" s="1" t="e" cm="1">
+        <f t="array" ref="E40">VEERG_15_6_1_1__1_EmissionsFromPurchasedLime_Result_Method1</f>
         <v>#NAME?</v>
       </c>
-      <c r="J24" s="10" t="s">
+      <c r="F40" s="1" t="e" cm="1">
+        <f t="array" ref="F40">VEERG_15_6_1_1__1_EmissionsFromPurchasedLime_Result_Method2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G40" s="10" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E25" s="1" t="e" cm="1">
-        <f t="array" ref="E25">VEERG_14_1_1__1_LocationBasedScopeElectricityEmissions_Result_Method1</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="F25" s="1" t="e">
+      <c r="H40" s="1" t="e">
         <f t="shared" si="1"/>
         <v>#NAME?</v>
       </c>
-      <c r="G25" s="10" t="s">
+      <c r="I40" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="J40" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="H25" s="1" t="e">
-        <f>E25</f>
+    </row>
+    <row r="41" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D41" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E41" s="1" t="e" cm="1">
+        <f t="array" ref="E41">VEERG_15_7_1_1__1_EmissionsFromPurchasedServices_Result_Method1</f>
         <v>#NAME?</v>
       </c>
-      <c r="I25" s="1" t="e">
-        <f>F25</f>
+      <c r="F41" s="1" t="e" cm="1">
+        <f t="array" ref="F41">VEERG_15_7_1_1__1_EmissionsFromPurchasedServices_Result_Method2</f>
         <v>#NAME?</v>
       </c>
-      <c r="J25" s="10" t="s">
+      <c r="G41" s="10" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D26" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E26" s="1" t="e" cm="1">
-        <f t="array" ref="E26">VEERG_14_1_2__1_MarketBasedScopeElectricityEmissionsVariation_Result_Method1</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="F26" s="1" t="e">
+      <c r="H41" s="1" t="e">
         <f t="shared" si="1"/>
         <v>#NAME?</v>
       </c>
-      <c r="G26" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="H26" s="1" t="e">
-        <f>E26</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="I26" s="1" t="e">
-        <f>F26</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="J26" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D27" s="88" t="s">
-        <v>5</v>
-      </c>
-      <c r="E27" s="89"/>
-      <c r="F27" s="89"/>
-      <c r="G27" s="89"/>
-      <c r="H27" s="88" t="e">
-        <f>SUM(H9:H26)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="I27" s="88" t="e">
-        <f>SUM(I9:I26)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="J27" s="98" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D30" s="80" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D32" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G32" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="H32" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="I32" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="J32" s="12"/>
-    </row>
-    <row r="33" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D33" s="1" t="e" cm="1">
-        <f t="array" ref="D33">"14.1.1-2 Purchased electricity " &amp; IF(X_Cell_Electricity_CalculationMethod="Location-based (simpler)", "(Location-based)", "(Market-based)")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="E33" s="1" t="e" cm="1">
-        <f t="array" ref="E33">IF(X_Cell_Electricity_CalculationMethod="Location-based (simpler)", VEERG_14_1_1__1_LocationBasedScopeElectricityEmissions_Result_Method1, VEERG_14_1_2__1_MarketBasedScopeElectricityEmissionsVariation_Result_Method1)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="F33" s="1" t="e">
-        <f>E33</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="H33" s="1" t="e">
-        <f>E33</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="I33" s="1" t="e">
-        <f>F33</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="J33" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D34" s="88" t="s">
-        <v>275</v>
-      </c>
-      <c r="E34" s="89"/>
-      <c r="F34" s="89"/>
-      <c r="G34" s="89"/>
-      <c r="H34" s="88" t="e">
-        <f>SUM(H33:H33)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="I34" s="88" t="e">
-        <f>SUM(I33:I33)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="J34" s="98" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D37" s="80" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="38" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D39" s="12" t="s">
-        <v>277</v>
-      </c>
-      <c r="E39" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G39" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="H39" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="I39" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="J39" s="12"/>
-    </row>
-    <row r="40" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="E40" s="1" t="e" cm="1">
-        <f t="array" ref="E40">VEERG_15_4_1_1__2_EmissionsFromPurchasedFertiliserComponentsVariation_Result_Method1</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="F40" s="1" t="e" cm="1">
-        <f t="array" ref="F40">VEERG_15_4_1_1__2_EmissionsFromPurchasedFertiliserComponentsVariation_Result_Method2</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="G40" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="H40" s="1" t="e">
-        <f t="shared" ref="H40:H47" si="2">E40</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="I40" s="1" t="e">
-        <f t="shared" ref="I40:I50" si="3">F40</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="J40" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="E41" s="1" t="e" cm="1">
-        <f t="array" ref="E41">VEERG_15_5_1_1__1_EmissionsFromPurchasedAgrichemicals_Result_Method1</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="F41" s="1" t="e" cm="1">
-        <f t="array" ref="F41">VEERG_15_5_1_1__1_EmissionsFromPurchasedAgrichemicals_Result_Method2</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="G41" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="H41" s="1" t="e">
+      <c r="I41" s="1" t="e">
         <f t="shared" si="2"/>
         <v>#NAME?</v>
       </c>
-      <c r="I41" s="1" t="e">
-        <f t="shared" si="3"/>
-        <v>#NAME?</v>
-      </c>
       <c r="J41" s="10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D42" s="1" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="E42" s="1" t="e" cm="1">
-        <f t="array" ref="E42">VEERG_15_6_1_1__1_EmissionsFromPurchasedLime_Result_Method1</f>
+        <f t="array" ref="E42">VEERG_15_10_1_1__1_OtherPurchasedGoodsAndServices_CleaningChemicals_Result_Method1</f>
         <v>#NAME?</v>
       </c>
       <c r="F42" s="1" t="e" cm="1">
-        <f t="array" ref="F42">VEERG_15_6_1_1__1_EmissionsFromPurchasedLime_Result_Method2</f>
+        <f t="array" ref="F42">VEERG_15_10_1_1__1_OtherPurchasedGoodsAndServices_CleaningChemicals_Result_Method2</f>
         <v>#NAME?</v>
       </c>
       <c r="G42" s="10" t="s">
         <v>8</v>
       </c>
       <c r="H42" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="I42" s="1" t="e">
         <f t="shared" si="2"/>
         <v>#NAME?</v>
       </c>
-      <c r="I42" s="1" t="e">
-        <f t="shared" si="3"/>
-        <v>#NAME?</v>
-      </c>
       <c r="J42" s="10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D43" s="1" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="E43" s="1" t="e" cm="1">
-        <f t="array" ref="E43">VEERG_15_7_1_1__1_EmissionsFromPurchasedServices_Result_Method1</f>
+        <f t="array" ref="E43">VEERG_15_10_1_1__1_OtherPurchasedGoodsAndServices_Uncategorised_Result_Method1</f>
         <v>#NAME?</v>
       </c>
       <c r="F43" s="1" t="e" cm="1">
-        <f t="array" ref="F43">VEERG_15_7_1_1__1_EmissionsFromPurchasedServices_Result_Method2</f>
+        <f t="array" ref="F43">VEERG_15_10_1_1__1_OtherPurchasedGoodsAndServices_Uncategorised_Result_Method2</f>
         <v>#NAME?</v>
       </c>
       <c r="G43" s="10" t="s">
         <v>8</v>
       </c>
       <c r="H43" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="I43" s="1" t="e">
         <f t="shared" si="2"/>
         <v>#NAME?</v>
       </c>
-      <c r="I43" s="1" t="e">
-        <f t="shared" si="3"/>
-        <v>#NAME?</v>
-      </c>
       <c r="J43" s="10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D44" s="1" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="E44" s="1" t="e" cm="1">
-        <f t="array" ref="E44">VEERG_15_10_1_1__1_OtherPurchasedGoodsAndServices_CleaningChemicals_Result_Method1</f>
+        <f t="array" ref="E44">VEERG_15_11_1_1__1_TotalUpstreamEmissionsFromFuel_Result</f>
         <v>#NAME?</v>
       </c>
-      <c r="F44" s="1" t="e" cm="1">
-        <f t="array" ref="F44">VEERG_15_10_1_1__1_OtherPurchasedGoodsAndServices_CleaningChemicals_Result_Method2</f>
+      <c r="F44" s="1" t="e">
+        <f>E44</f>
         <v>#NAME?</v>
       </c>
       <c r="G44" s="10" t="s">
         <v>8</v>
       </c>
       <c r="H44" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="I44" s="1" t="e">
         <f t="shared" si="2"/>
         <v>#NAME?</v>
       </c>
-      <c r="I44" s="1" t="e">
-        <f t="shared" si="3"/>
-        <v>#NAME?</v>
-      </c>
       <c r="J44" s="10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D45" s="1" t="s">
-        <v>283</v>
+    <row r="45" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D45" s="1" t="e" cm="1">
+        <f t="array" ref="D45">"15.12.1.1 Purchased electricity " &amp; IF(X_Cell_Electricity_CalculationMethod="Location-based (simpler)", "(Location-based)", "(Market-based)")</f>
+        <v>#NAME?</v>
       </c>
       <c r="E45" s="1" t="e" cm="1">
-        <f t="array" ref="E45">VEERG_15_10_1_1__1_OtherPurchasedGoodsAndServices_Uncategorised_Result_Method1</f>
+        <f t="array" ref="E45">IF(X_Cell_Electricity_CalculationMethod="Location-based (simpler)", VEERG_15_12_1_1__1_UpstreamPurchasedElectricityLocationBased_Result, VEERG_15_12_1_1__1_UpstreamPurchasedElectricityMarketBased_Result)</f>
         <v>#NAME?</v>
       </c>
-      <c r="F45" s="1" t="e" cm="1">
-        <f t="array" ref="F45">VEERG_15_10_1_1__1_OtherPurchasedGoodsAndServices_Uncategorised_Result_Method2</f>
+      <c r="F45" s="1" t="e">
+        <f>E45</f>
         <v>#NAME?</v>
       </c>
       <c r="G45" s="10" t="s">
         <v>8</v>
       </c>
       <c r="H45" s="1" t="e">
+        <f t="shared" si="1"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="I45" s="1" t="e">
         <f t="shared" si="2"/>
         <v>#NAME?</v>
       </c>
-      <c r="I45" s="1" t="e">
-        <f t="shared" si="3"/>
-        <v>#NAME?</v>
-      </c>
       <c r="J45" s="10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D46" s="1" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="E46" s="1" t="e" cm="1">
-        <f t="array" ref="E46">VEERG_15_11_1_1__1_TotalUpstreamEmissionsFromFuel_Result</f>
+        <f t="array" ref="E46">VEERG_15_14_1_1__1_EmbeddedEmissionsFromUpstreamFreight_Incoming_Result_Method1</f>
         <v>#NAME?</v>
       </c>
-      <c r="F46" s="1" t="e">
+      <c r="F46" s="1" t="e" cm="1">
+        <f t="array" ref="F46">VEERG_15_14_1_1__1_EmbeddedEmissionsFromUpstreamFreight_Incoming_Result_Method2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="H46" s="1" t="e">
         <f>E46</f>
         <v>#NAME?</v>
       </c>
-      <c r="G46" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="H46" s="1" t="e">
+      <c r="I46" s="1" t="e">
         <f t="shared" si="2"/>
         <v>#NAME?</v>
       </c>
-      <c r="I46" s="1" t="e">
-        <f t="shared" si="3"/>
-        <v>#NAME?</v>
-      </c>
       <c r="J46" s="10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D47" s="1" t="e" cm="1">
-        <f t="array" ref="D47">"15.12.1.1 Purchased electricity " &amp; IF(X_Cell_Electricity_CalculationMethod="Location-based (simpler)", "(Location-based)", "(Market-based)")</f>
-        <v>#NAME?</v>
+    <row r="47" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D47" s="1" t="s">
+        <v>270</v>
       </c>
       <c r="E47" s="1" t="e" cm="1">
-        <f t="array" ref="E47">IF(X_Cell_Electricity_CalculationMethod="Location-based (simpler)", VEERG_15_12_1_1__1_UpstreamPurchasedElectricityLocationBased_Result, VEERG_15_12_1_1__1_UpstreamPurchasedElectricityMarketBased_Result)</f>
+        <f t="array" ref="E47">VEERG_10_1_1_1__1_EmissionsFromWasteManagement_Scope3_Result_Method1</f>
         <v>#NAME?</v>
       </c>
       <c r="F47" s="1" t="e">
@@ -14129,213 +13738,129 @@
         <v>8</v>
       </c>
       <c r="H47" s="1" t="e">
+        <f t="shared" ref="H47:H48" si="3">E47</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I47" s="1" t="e">
         <f t="shared" si="2"/>
         <v>#NAME?</v>
       </c>
-      <c r="I47" s="1" t="e">
+      <c r="J47" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D48" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E48" s="1" t="e" cm="1">
+        <f t="array" ref="E48">VEERG_15_14_1_1__1_EmbeddedEmissionsFromUpstreamFreight_Outgoing_Result_Method1</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F48" s="1" t="e" cm="1">
+        <f t="array" ref="F48">VEERG_15_14_1_1__1_EmbeddedEmissionsFromUpstreamFreight_Outgoing_Result_Method2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="H48" s="1" t="e">
         <f t="shared" si="3"/>
         <v>#NAME?</v>
       </c>
-      <c r="J47" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D48" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E48" s="1" t="e" cm="1">
-        <f t="array" ref="E48">VEERG_15_14_1_1__1_EmbeddedEmissionsFromUpstreamFreight_Incoming_Result_Method1</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="F48" s="1" t="e" cm="1">
-        <f t="array" ref="F48">VEERG_15_14_1_1__1_EmbeddedEmissionsFromUpstreamFreight_Incoming_Result_Method2</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="G48" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="H48" s="1" t="e">
-        <f>E48</f>
-        <v>#NAME?</v>
-      </c>
       <c r="I48" s="1" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>#NAME?</v>
       </c>
       <c r="J48" s="10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D49" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="E49" s="1" t="e" cm="1">
-        <f t="array" ref="E49">VEERG_10_1_1_1__1_EmissionsFromWasteManagement_Scope3_Result_Method1</f>
+    <row r="49" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D49" s="88" t="s">
+        <v>272</v>
+      </c>
+      <c r="E49" s="89"/>
+      <c r="F49" s="89"/>
+      <c r="G49" s="89"/>
+      <c r="H49" s="88" t="e">
+        <f>SUM(H38:H48)</f>
         <v>#NAME?</v>
       </c>
-      <c r="F49" s="1" t="e">
-        <f>E49</f>
+      <c r="I49" s="88" t="e">
+        <f>SUM(I38:I48)</f>
         <v>#NAME?</v>
       </c>
-      <c r="G49" s="10" t="s">
+      <c r="J49" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="H49" s="1" t="e">
-        <f t="shared" ref="H49:H50" si="4">E49</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="I49" s="1" t="e">
-        <f t="shared" si="3"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="J49" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D50" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E50" s="1" t="e" cm="1">
-        <f t="array" ref="E50">VEERG_15_14_1_1__1_EmbeddedEmissionsFromUpstreamFreight_Outgoing_Result_Method1</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="F50" s="1" t="e" cm="1">
-        <f t="array" ref="F50">VEERG_15_14_1_1__1_EmbeddedEmissionsFromUpstreamFreight_Outgoing_Result_Method2</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="G50" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="H50" s="1" t="e">
-        <f t="shared" si="4"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="I50" s="1" t="e">
-        <f t="shared" si="3"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="J50" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D51" s="88" t="s">
-        <v>288</v>
-      </c>
-      <c r="E51" s="89"/>
-      <c r="F51" s="89"/>
-      <c r="G51" s="89"/>
-      <c r="H51" s="88" t="e">
-        <f>SUM(H40:H50)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="I51" s="88" t="e">
-        <f>SUM(I40:I50)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="J51" s="98" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D54" s="80" t="str">
+    </row>
+    <row r="52" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D52" s="80" t="str">
         <f>"Carbon removals from plantings for the activity period " &amp; TEXT(X_Cell_Site_StartDate, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Site_EndDate, "d mmmm yyyy")</f>
         <v>Carbon removals from plantings for the activity period 1 January 2025 and 31 December 2025</v>
       </c>
     </row>
-    <row r="55" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D56" s="88" t="s">
-        <v>289</v>
-      </c>
-      <c r="E56" s="89">
+    <row r="54" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D54" s="88" t="s">
+        <v>273</v>
+      </c>
+      <c r="E54" s="89">
         <f>SUM(Table_Input_Enterprise_PlantingRemovals[Removal allocated to this enterprise])</f>
         <v>0</v>
       </c>
-      <c r="F56" s="98" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="57" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D59" s="80" t="str">
+      <c r="F54" s="98" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="57" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D57" s="80" t="str">
         <f>"Net emissions for the activity period " &amp; TEXT(X_Cell_Site_StartDate, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Site_EndDate, "d mmmm yyyy")</f>
         <v>Net emissions for the activity period 1 January 2025 and 31 December 2025</v>
       </c>
     </row>
-    <row r="60" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D61" s="12"/>
-      <c r="E61" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="F61" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="G61" s="12"/>
-    </row>
-    <row r="62" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D62" s="97" t="s">
-        <v>290</v>
-      </c>
-      <c r="E62" s="95" t="e">
+    <row r="59" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D59" s="12"/>
+      <c r="E59" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="G59" s="12"/>
+    </row>
+    <row r="60" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D60" s="97" t="s">
+        <v>274</v>
+      </c>
+      <c r="E60" s="95" t="e">
         <f>Result_Enterprise_Scope1_Method1+Result_Enterprise_Scope2_Method1+Result_Enterprise_Scope3_Method1</f>
         <v>#NAME?</v>
       </c>
-      <c r="F62" s="95" t="e">
+      <c r="F60" s="95" t="e">
         <f>Result_Enterprise_Scope1_Method2+Result_Enterprise_Scope2_Method2+Result_Enterprise_Scope3_Method2</f>
         <v>#NAME?</v>
       </c>
-      <c r="G62" s="96" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="63" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D63" s="97" t="s">
-        <v>292</v>
-      </c>
-      <c r="E63" s="95" t="e">
+      <c r="G60" s="96" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="61" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D61" s="97" t="s">
+        <v>276</v>
+      </c>
+      <c r="E61" s="95" t="e">
         <f>Result_Enterprise_Gross_Method1-Result_Enterprise_Removals</f>
         <v>#NAME?</v>
       </c>
-      <c r="F63" s="95" t="e">
+      <c r="F61" s="95" t="e">
         <f>Result_Enterprise_Gross_Method2-Result_Enterprise_Removals</f>
         <v>#NAME?</v>
       </c>
-      <c r="G63" s="96" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="64" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="G61" s="96" t="s">
+        <v>275</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -14348,8 +13873,8 @@
   <sheetPr>
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
-  <dimension ref="A1:N58"/>
-  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
+  <dimension ref="A1:N56"/>
+  <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -14359,16 +13884,16 @@
     <col min="14" max="14" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="93" customFormat="1" ht="30" x14ac:dyDescent="0.35" customHeight="1">
+    <row r="1" spans="1:14" s="93" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="93" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25" ht="20" customHeight="1"/>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="94"/>
       <c r="D3" s="94"/>
       <c r="E3" s="94"/>
@@ -14382,25 +13907,25 @@
       <c r="M3" s="94"/>
       <c r="N3" s="94"/>
     </row>
-    <row r="32" spans="4:4" ht="20" x14ac:dyDescent="0.25" customHeight="1">
+    <row r="32" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D32" s="2" t="str">
         <f>"Emissions for whole production cycle running between " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Emissions for whole production cycle running between 1 November 2025 and 31 March 2026</v>
       </c>
     </row>
-    <row r="35" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="35" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D35" s="12"/>
       <c r="E35" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G35" s="12"/>
     </row>
-    <row r="36" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="36" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D36" s="78" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="E36" s="1" t="e">
         <f>Result_EmissionsForWholeProductionCycle_Gross_Method1</f>
@@ -14414,9 +13939,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="37" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D37" s="78" t="s">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="E37" s="1" t="e">
         <f>Result_EmissionsForWholeProductionCycle_Net_Method1</f>
@@ -14430,20 +13955,20 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
+    <row r="39" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D39" s="2" t="str">
         <f>"Product emissions intensity for whole production cycle running between " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Product emissions intensity for whole production cycle running between 1 November 2025 and 31 March 2026</v>
       </c>
     </row>
-    <row r="42" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="42" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D42" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="43" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="43" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D43" s="12" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E43" s="12" t="s">
         <v>122</v>
@@ -14452,7 +13977,7 @@
         <v>118</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="H43" s="12" t="s">
         <v>120</v>
@@ -14464,20 +13989,20 @@
         <v>119</v>
       </c>
     </row>
-    <row r="44" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="44" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D44" s="1" t="s">
-        <v>169</v>
+        <v>320</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>123</v>
       </c>
       <c r="F44" s="1">
-        <f>X_Cell_Enterprise_GrainYield*X_Cell_Enterprise_PercentGrainSold</f>
-        <v>0</v>
-      </c>
-      <c r="G44" s="1" t="e">
-        <f>F44/(F44+F47)</f>
-        <v>#DIV/0!</v>
+        <f>X_Cell_Enterprise_CottonLintYield*X_Cell_Enterprise_PercentCottonLintSold</f>
+        <v>2502.0320000000002</v>
+      </c>
+      <c r="G44" s="1">
+        <f>F44/(F44+F46)</f>
+        <v>0.80012996349253862</v>
       </c>
       <c r="H44" s="1" t="e">
         <f>(E36/F44)*G44</f>
@@ -14488,313 +14013,231 @@
         <v>#NAME?</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="45" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
-      <c r="D45" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="E45" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="45" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D45" s="104" t="s">
+        <v>321</v>
+      </c>
+      <c r="E45" s="104" t="s">
         <v>123</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F45" s="104">
         <f>F44</f>
-        <v>0</v>
-      </c>
-      <c r="G45" s="1" t="e">
+        <v>2502.0320000000002</v>
+      </c>
+      <c r="G45" s="104">
         <f>G44</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H45" s="1" t="e">
+        <v>0.80012996349253862</v>
+      </c>
+      <c r="H45" s="104" t="e">
         <f>(E37/F45)*G45</f>
         <v>#NAME?</v>
       </c>
-      <c r="I45" s="1" t="e">
+      <c r="I45" s="104" t="e">
         <f>(F37/F45)*G45</f>
         <v>#NAME?</v>
       </c>
-      <c r="J45" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="46" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+      <c r="J45" s="105" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="46" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D46" s="1" t="s">
-        <v>159</v>
+        <v>322</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F46" s="1">
-        <f>X_Cell_Enterprise_GrainYield*X_Cell_Enterprise_PercentGrainUsedAsFeed</f>
-        <v>0</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="J46" s="10"/>
-    </row>
-    <row r="47" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <f>X_Cell_Enterprise_CottonseedYield*X_Cell_Enterprise_PercentCottonseedSold</f>
+        <v>625</v>
+      </c>
+      <c r="G46" s="1">
+        <f>F46/(F44+F46)</f>
+        <v>0.19987003650746138</v>
+      </c>
+      <c r="H46" s="1" t="e">
+        <f>(E36/F46)*G46</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I46" s="1" t="e">
+        <f>(F36/F46)*G46</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J46" s="10" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="47" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D47" s="1" t="s">
-        <v>171</v>
+        <v>323</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>124</v>
       </c>
       <c r="F47" s="1">
-        <f>X_Cell_BaledHayYield*X_Cell_PercentBaledHaySold</f>
-        <v>0</v>
-      </c>
-      <c r="G47" s="1" t="e">
-        <f>F47/(F44+F47)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H47" s="1" t="e">
-        <f>(E36/F47)*G47</f>
+        <f>F46</f>
+        <v>625</v>
+      </c>
+      <c r="G47" s="1">
+        <f>G46</f>
+        <v>0.19987003650746138</v>
+      </c>
+      <c r="H47" s="99" t="e">
+        <f>(E37/F47)*G47</f>
         <v>#NAME?</v>
       </c>
-      <c r="I47" s="1" t="e">
-        <f>(F36/F47)*G47</f>
+      <c r="I47" s="99" t="e">
+        <f>(F37/F47)*G47</f>
         <v>#NAME?</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="48" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
-      <c r="D48" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E48" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="48" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J48" s="10"/>
+    </row>
+    <row r="50" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D50" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="51" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D51" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G51" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="H51" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="I51" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="J51" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="52" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D52" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F52" s="1">
+        <f>X_Cell_Enterprise_CottonLintYield*X_Cell_Enterprise_PercentCottonLintSold</f>
+        <v>2502.0320000000002</v>
+      </c>
+      <c r="G52" s="1">
+        <f>X_Cell_Enterprise_PercentIncomeFromCottonLint</f>
+        <v>0.8</v>
+      </c>
+      <c r="H52" s="1" t="e">
+        <f>E36*G52/F52</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I52" s="1" t="e">
+        <f>F36*G52/F52</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J52" s="10" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="53" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D53" s="104" t="s">
+        <v>156</v>
+      </c>
+      <c r="E53" s="104" t="s">
+        <v>123</v>
+      </c>
+      <c r="F53" s="104">
+        <f>F52</f>
+        <v>2502.0320000000002</v>
+      </c>
+      <c r="G53" s="104">
+        <f>G52</f>
+        <v>0.8</v>
+      </c>
+      <c r="H53" s="104" t="e">
+        <f>E37*G53/F53</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I53" s="104" t="e">
+        <f>F37*G53/F53</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J53" s="105" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="54" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D54" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F48" s="1">
-        <f>F47</f>
-        <v>0</v>
-      </c>
-      <c r="G48" s="1" t="e">
-        <f>G47</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H48" s="99" t="e">
-        <f>(E37/F48)*G48</f>
+      <c r="F54" s="1">
+        <f>X_Cell_Enterprise_CottonseedYield*X_Cell_Enterprise_PercentCottonseedSold</f>
+        <v>625</v>
+      </c>
+      <c r="G54" s="1">
+        <f>X_Cell_Enterprise_PercentIncomeFromCottonLint</f>
+        <v>0.8</v>
+      </c>
+      <c r="H54" s="1" t="e">
+        <f>E36*G54/F54</f>
         <v>#NAME?</v>
       </c>
-      <c r="I48" s="99" t="e">
-        <f>(F37/F48)*G48</f>
+      <c r="I54" s="1" t="e">
+        <f>F36*G54/F54</f>
         <v>#NAME?</v>
       </c>
-      <c r="J48" s="10" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="49" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
-      <c r="D49" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F49" s="1">
-        <f>X_Cell_BaledHayYield*X_Cell_PercentBaledHayUsedOnFarm</f>
-        <v>0</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="J49" s="10"/>
-    </row>
-    <row r="51" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
-      <c r="D51" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="52" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
-      <c r="D52" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="E52" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="F52" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="G52" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="H52" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="I52" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="J52" s="12" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="53" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
-      <c r="D53" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F53" s="1">
-        <f>X_Cell_Enterprise_GrainYield*X_Cell_Enterprise_PercentGrainSold</f>
-        <v>0</v>
-      </c>
-      <c r="G53" s="1">
-        <f>X_Cell_Enterprise_PercentIncomeFromGrain</f>
+      <c r="J54" s="10" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="55" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D55" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F55" s="1">
+        <f>F54</f>
+        <v>625</v>
+      </c>
+      <c r="G55" s="1">
+        <f>G54</f>
         <v>0.8</v>
       </c>
-      <c r="H53" s="1" t="e">
-        <f>E36*G53/F53</f>
+      <c r="H55" s="1" t="e">
+        <f>E37*G55/F55</f>
         <v>#NAME?</v>
       </c>
-      <c r="I53" s="1" t="e">
-        <f>F36*G53/F53</f>
+      <c r="I55" s="1" t="e">
+        <f>F37*G55/F55</f>
         <v>#NAME?</v>
       </c>
-      <c r="J53" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="54" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
-      <c r="D54" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F54" s="1">
-        <f>F53</f>
-        <v>0</v>
-      </c>
-      <c r="G54" s="1">
-        <f>G53</f>
-        <v>0.8</v>
-      </c>
-      <c r="H54" s="1" t="e">
-        <f>E37*G54/F54</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="I54" s="1" t="e">
-        <f>F37*G54/F54</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="J54" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="55" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
-      <c r="D55" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F55" s="1">
-        <f>X_Cell_Enterprise_GrainYield*X_Cell_Enterprise_PercentGrainUsedAsFeed</f>
-        <v>0</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="J55" s="10"/>
-    </row>
-    <row r="56" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
-      <c r="D56" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F56" s="1">
-        <f>X_Cell_BaledHayYield*X_Cell_PercentBaledHaySold</f>
-        <v>0</v>
-      </c>
-      <c r="G56" s="1">
-        <f>X_Cell_Enterprise_PercentIncomeFromGrain</f>
-        <v>0.8</v>
-      </c>
-      <c r="H56" s="1" t="e">
-        <f>E36*G56/F56</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="I56" s="1" t="e">
-        <f>F36*G56/F56</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="J56" s="10" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="57" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
-      <c r="D57" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F57" s="1">
-        <f>F56</f>
-        <v>0</v>
-      </c>
-      <c r="G57" s="1">
-        <f>G56</f>
-        <v>0.8</v>
-      </c>
-      <c r="H57" s="1" t="e">
-        <f>E37*G57/F57</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="I57" s="1" t="e">
-        <f>F37*G57/F57</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="J57" s="10" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="58" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
-      <c r="D58" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F58" s="1">
-        <f>X_Cell_BaledHayYield*X_Cell_PercentBaledHayUsedOnFarm</f>
-        <v>0</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="J58" s="10"/>
+      <c r="J55" s="10" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="56" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J56" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14808,8 +14251,8 @@
     <tabColor rgb="FFCC6600"/>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:AA115"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
+  <dimension ref="A1:AA82"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="4" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" style="23" customWidth="1"/>
@@ -14830,7 +14273,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:24" s="23" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="23" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -14841,7 +14284,7 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -14868,7 +14311,7 @@
       <c r="W3" s="25"/>
       <c r="X3" s="25"/>
     </row>
-    <row r="4" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -14883,19 +14326,19 @@
       <c r="J4" s="31"/>
       <c r="K4" s="31"/>
     </row>
-    <row r="5" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D5" s="2" t="s">
         <v>96</v>
       </c>
       <c r="N5" s="32"/>
     </row>
-    <row r="6" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>1</v>
       </c>
       <c r="N6" s="34"/>
     </row>
-    <row r="7" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
@@ -14907,7 +14350,7 @@
       <c r="F7" s="45"/>
       <c r="G7" s="46"/>
     </row>
-    <row r="8" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Input - Pasture Beef'!A1", "Pasture Beef")</f>
         <v>Pasture Beef</v>
@@ -14919,14 +14362,14 @@
       <c r="F8" s="48"/>
       <c r="G8" s="49"/>
     </row>
-    <row r="9" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5"/>
       <c r="D9" s="1"/>
       <c r="E9" s="50"/>
       <c r="F9" s="17"/>
       <c r="N9" s="36"/>
     </row>
-    <row r="10" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
@@ -14941,7 +14384,7 @@
       </c>
       <c r="N10" s="36"/>
     </row>
-    <row r="11" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.1-2 Methane'!A1", "4.2.1.1-2 Methane")</f>
         <v>4.2.1.1-2 Methane</v>
@@ -14958,7 +14401,7 @@
       <c r="G11" s="1"/>
       <c r="N11" s="41"/>
     </row>
-    <row r="12" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.3-4 Soil direct N2O'!A1", "4.2.1.3-4 Soil direct N2O")</f>
         <v>4.2.1.3-4 Soil direct N2O</v>
@@ -14973,7 +14416,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.5-6 Soil Atmos Dep'!A1", "4.2.1.5-6 Soil atm. deposition")</f>
         <v>4.2.1.5-6 Soil atm. deposition</v>
@@ -14990,7 +14433,7 @@
       <c r="N13" s="43"/>
       <c r="O13" s="43"/>
     </row>
-    <row r="14" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.7-8 Soil leach runoff'!A1", "4.2.1.7-8 Soil leach &amp; runoff")</f>
         <v>4.2.1.7-8 Soil leach &amp; runoff</v>
@@ -15007,7 +14450,7 @@
       <c r="N14" s="43"/>
       <c r="O14" s="43"/>
     </row>
-    <row r="15" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5"/>
       <c r="D15" s="1" t="s">
         <v>109</v>
@@ -15021,7 +14464,7 @@
       <c r="N15" s="43"/>
       <c r="O15" s="43"/>
     </row>
-    <row r="16" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
         <v>2</v>
       </c>
@@ -15037,7 +14480,7 @@
       <c r="N16" s="43"/>
       <c r="O16" s="43"/>
     </row>
-    <row r="17" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="str">
         <f>HYPERLINK("#'Constants - Pasture Beef'!A1", "Constants - Pasture Beef")</f>
         <v>Constants - Pasture Beef</v>
@@ -15052,7 +14495,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="str">
         <f>HYPERLINK("#'Constants - Livestock'!A1", "Constants - Livestock")</f>
         <v>Constants - Livestock</v>
@@ -15066,7 +14509,7 @@
       </c>
       <c r="F18" s="17"/>
     </row>
-    <row r="19" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -15081,7 +14524,7 @@
       <c r="G19" s="51"/>
       <c r="N19" s="32"/>
     </row>
-    <row r="20" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -15097,7 +14540,7 @@
       <c r="G20" s="50"/>
       <c r="N20" s="34"/>
     </row>
-    <row r="21" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21"/>
       <c r="D21" s="1" t="s">
         <v>115</v>
@@ -15109,7 +14552,7 @@
       <c r="F21" s="1"/>
       <c r="G21" s="50"/>
     </row>
-    <row r="22" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5"/>
       <c r="D22" s="1" t="s">
         <v>69</v>
@@ -15120,29 +14563,29 @@
       </c>
       <c r="G22" s="54"/>
     </row>
-    <row r="23" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25"/>
       <c r="N25" s="34"/>
     </row>
-    <row r="26" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26"/>
     </row>
-    <row r="27" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27"/>
     </row>
-    <row r="28" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28"/>
     </row>
-    <row r="29" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29"/>
     </row>
-    <row r="30" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30"/>
       <c r="L30" s="52"/>
       <c r="M30" s="52"/>
@@ -15159,7 +14602,7 @@
       <c r="X30" s="52"/>
       <c r="Y30" s="52"/>
     </row>
-    <row r="31" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31"/>
       <c r="L31" s="53"/>
       <c r="M31" s="53"/>
@@ -15176,7 +14619,7 @@
       <c r="X31" s="53"/>
       <c r="Y31" s="53"/>
     </row>
-    <row r="32" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32"/>
       <c r="L32" s="53"/>
       <c r="M32" s="53"/>
@@ -15193,7 +14636,7 @@
       <c r="X32" s="53"/>
       <c r="Y32" s="53"/>
     </row>
-    <row r="33" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33"/>
       <c r="L33" s="53"/>
       <c r="M33" s="53"/>
@@ -15210,7 +14653,7 @@
       <c r="X33" s="53"/>
       <c r="Y33" s="53"/>
     </row>
-    <row r="34" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34"/>
       <c r="J34" s="55"/>
       <c r="K34" s="56"/>
@@ -15229,7 +14672,7 @@
       <c r="X34" s="53"/>
       <c r="Y34" s="53"/>
     </row>
-    <row r="35" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35"/>
       <c r="J35" s="55"/>
       <c r="K35" s="56"/>
@@ -15248,7 +14691,7 @@
       <c r="X35" s="53"/>
       <c r="Y35" s="53"/>
     </row>
-    <row r="36" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36"/>
       <c r="D36" s="57"/>
       <c r="E36" s="57"/>
@@ -15273,7 +14716,7 @@
       <c r="X36" s="53"/>
       <c r="Y36" s="53"/>
     </row>
-    <row r="37" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37"/>
       <c r="D37" s="57"/>
       <c r="E37" s="57"/>
@@ -15298,7 +14741,7 @@
       <c r="X37" s="53"/>
       <c r="Y37" s="53"/>
     </row>
-    <row r="38" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38"/>
       <c r="D38" s="57"/>
       <c r="E38" s="57"/>
@@ -15323,7 +14766,7 @@
       <c r="X38" s="53"/>
       <c r="Y38" s="53"/>
     </row>
-    <row r="39" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39"/>
       <c r="D39" s="57"/>
       <c r="E39" s="57"/>
@@ -15348,7 +14791,7 @@
       <c r="X39" s="53"/>
       <c r="Y39" s="53"/>
     </row>
-    <row r="40" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40"/>
       <c r="D40" s="60"/>
       <c r="E40" s="60"/>
@@ -15373,104 +14816,97 @@
       <c r="X40" s="63"/>
       <c r="Y40" s="63"/>
     </row>
-    <row r="41" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41"/>
     </row>
-    <row r="42" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42"/>
     </row>
-    <row r="43" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43"/>
     </row>
-    <row r="44" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D45" s="2"/>
     </row>
-    <row r="46" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D47" s="64"/>
       <c r="E47" s="64"/>
       <c r="F47" s="64"/>
       <c r="G47" s="64"/>
       <c r="H47" s="64"/>
     </row>
-    <row r="48" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D48" s="65"/>
       <c r="E48" s="65"/>
       <c r="F48" s="66"/>
       <c r="G48" s="66"/>
       <c r="H48" s="65"/>
     </row>
-    <row r="49" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D49" s="65"/>
       <c r="E49" s="65"/>
       <c r="F49" s="66"/>
       <c r="G49" s="66"/>
       <c r="H49" s="65"/>
     </row>
-    <row r="50" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D50" s="65"/>
       <c r="E50" s="65"/>
       <c r="F50" s="66"/>
       <c r="G50" s="66"/>
       <c r="H50" s="65"/>
     </row>
-    <row r="51" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D51" s="67"/>
       <c r="E51" s="68"/>
       <c r="F51" s="68"/>
       <c r="G51" s="68"/>
       <c r="H51" s="69"/>
     </row>
-    <row r="52" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G54" s="70"/>
     </row>
-    <row r="55" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D55" s="2"/>
     </row>
-    <row r="56" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D57" s="71"/>
       <c r="F57" s="72"/>
     </row>
-    <row r="58" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D58" s="1"/>
       <c r="E58" s="73"/>
     </row>
-    <row r="59" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D59" s="1"/>
       <c r="E59" s="73"/>
     </row>
-    <row r="60" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D60" s="1"/>
       <c r="E60" s="74"/>
     </row>
-    <row r="61" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D61" s="1"/>
     </row>
-    <row r="62" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D63" s="71"/>
     </row>
-    <row r="64" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D64" s="1"/>
       <c r="E64" s="73"/>
     </row>
-    <row r="65" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D65" s="1"/>
       <c r="E65" s="73"/>
     </row>
-    <row r="66" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D66" s="1"/>
       <c r="E66" s="74"/>
     </row>
-    <row r="67" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D69" s="75"/>
       <c r="E69" s="75"/>
       <c r="F69" s="75"/>
@@ -15478,7 +14914,7 @@
       <c r="H69" s="75"/>
       <c r="I69" s="75"/>
     </row>
-    <row r="70" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D70" s="75"/>
       <c r="E70" s="75"/>
       <c r="F70" s="75"/>
@@ -15486,7 +14922,7 @@
       <c r="H70" s="75"/>
       <c r="I70" s="75"/>
     </row>
-    <row r="71" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D71" s="75"/>
       <c r="E71" s="75"/>
       <c r="F71" s="75"/>
@@ -15494,7 +14930,7 @@
       <c r="H71" s="75"/>
       <c r="I71" s="75"/>
     </row>
-    <row r="72" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D72" s="75"/>
       <c r="E72" s="75"/>
       <c r="F72" s="75"/>
@@ -15502,59 +14938,21 @@
       <c r="H72" s="75"/>
       <c r="I72" s="75"/>
     </row>
-    <row r="73" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D78" s="76"/>
     </row>
-    <row r="79" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D79" s="76"/>
     </row>
-    <row r="80" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D80" s="76"/>
     </row>
-    <row r="81" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D81" s="76"/>
     </row>
-    <row r="82" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D82" s="76"/>
     </row>
-    <row r="83" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E12" xr:uid="{620909BD-05B7-4260-BB85-4888DFAEE1F3}">
@@ -15580,7 +14978,7 @@
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
   <dimension ref="C1:J83"/>
-  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -15591,9 +14989,9 @@
     <col min="11" max="11" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:10" ht="30" x14ac:dyDescent="0.35" customHeight="1">
+    <row r="1" spans="3:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1" s="29" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D1" s="23"/>
       <c r="E1" s="23"/>
@@ -15603,7 +15001,7 @@
       <c r="I1" s="23"/>
       <c r="J1" s="23"/>
     </row>
-    <row r="2" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="2" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -15613,7 +15011,7 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="3:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
+    <row r="3" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="30"/>
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
@@ -15623,7 +15021,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="5" spans="3:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
+    <row r="5" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D5" s="2" t="s">
         <v>88</v>
       </c>
@@ -15631,13 +15029,13 @@
       <c r="F5" s="26"/>
       <c r="G5" s="26"/>
     </row>
-    <row r="6" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="6" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D6" s="33"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
       <c r="G6" s="26"/>
     </row>
-    <row r="7" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="7" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D7" s="1" t="s">
         <v>89</v>
       </c>
@@ -15647,7 +15045,7 @@
       <c r="F7" s="17"/>
       <c r="G7" s="26"/>
     </row>
-    <row r="8" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="8" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D8" s="13" t="s">
         <v>91</v>
       </c>
@@ -15657,13 +15055,13 @@
       <c r="F8" s="26"/>
       <c r="G8" s="26"/>
     </row>
-    <row r="9" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="9" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D9" s="26"/>
       <c r="E9" s="26"/>
       <c r="F9" s="26"/>
       <c r="G9" s="26"/>
     </row>
-    <row r="10" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="10" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D10" s="37" t="s">
         <v>93</v>
       </c>
@@ -15671,13 +15069,13 @@
       <c r="F10" s="39"/>
       <c r="G10" s="40"/>
     </row>
-    <row r="11" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="11" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D11" s="26"/>
       <c r="E11" s="26"/>
       <c r="F11" s="26"/>
       <c r="G11" s="26"/>
     </row>
-    <row r="12" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="12" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D12" s="13" t="s">
         <v>17</v>
       </c>
@@ -15689,7 +15087,7 @@
       </c>
       <c r="G12" s="26"/>
     </row>
-    <row r="13" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="13" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D13" s="13" t="s">
         <v>18</v>
       </c>
@@ -15702,16 +15100,16 @@
       </c>
       <c r="G13" s="26"/>
     </row>
-    <row r="14" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="14" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F14" s="26"/>
       <c r="G14" s="26"/>
     </row>
-    <row r="16" spans="3:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
+    <row r="16" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D16" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="18" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D18" s="1" t="s">
         <v>14</v>
       </c>
@@ -15722,7 +15120,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="19" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D19" s="1" t="s">
         <v>15</v>
       </c>
@@ -15733,7 +15131,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="20" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="20" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D20" s="1" t="s">
         <v>16</v>
       </c>
@@ -15745,146 +15143,136 @@
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="22" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D22" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="E22" s="79" cm="1">
-        <f t="array" ref="E22">IF(X_Cell_Crop_CropPurpose = "Cash grain crop", X_Cell_Crop_TotalProductionOfCrop, 0)</f>
-        <v>0</v>
+        <v>324</v>
+      </c>
+      <c r="E22" s="79">
+        <f>X_Cell_Crop_LintYieldTotal</f>
+        <v>2502.0320000000002</v>
       </c>
       <c r="F22" s="17" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="23" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D23" s="1" t="s">
-        <v>154</v>
+        <v>325</v>
       </c>
       <c r="E23" s="19">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="24" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="24" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D24" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E24" s="19">
-        <v>0.1</v>
+        <v>326</v>
+      </c>
+      <c r="E24" s="20">
+        <f>100%-E23</f>
+        <v>0</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="25" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
-      <c r="D25" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E25" s="20">
-        <f>100%-E23-E24</f>
-        <v>0.8</v>
-      </c>
-      <c r="F25" s="17" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="27" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="26" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D26" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="E26" s="79">
+        <f>X_Cell_Crop_CottonseedYieldTotal</f>
+        <v>625</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D27" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E27" s="79" cm="1">
-        <f t="array" ref="E27">X_Cell_Crop_TotalResidueBaled</f>
+        <v>328</v>
+      </c>
+      <c r="E27" s="19">
+        <v>1</v>
+      </c>
+      <c r="F27" s="17" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="28" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D28" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E28" s="20">
+        <f>100%-E27</f>
         <v>0</v>
       </c>
-      <c r="F27" s="17" t="s">
+      <c r="F28" s="17" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="30" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D30" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="E30" s="79">
+        <f>X_Cell_Crop_TotalUnprocessedCottonYield</f>
+        <v>3127.0320000000002</v>
+      </c>
+      <c r="F30" s="17" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
-      <c r="D28" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E28" s="19">
-        <v>0.2</v>
-      </c>
-      <c r="F28" s="17" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="29" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
-      <c r="D29" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E29" s="19">
-        <v>0.1</v>
-      </c>
-      <c r="F29" s="17" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="30" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
-      <c r="D30" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E30" s="20">
-        <f>100%-E28-E29</f>
-        <v>0.70000000000000007</v>
-      </c>
-      <c r="F30" s="17" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="32" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="32" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D32" s="1" t="s">
-        <v>151</v>
+        <v>329</v>
       </c>
       <c r="E32" s="19">
         <v>0.8</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="33" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="33" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D33" s="1" t="s">
-        <v>153</v>
+        <v>330</v>
       </c>
       <c r="E33" s="19">
         <v>0.2</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="36" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="36" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D36" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="39" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="39" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D39" s="80" t="str">
         <f>"Carbon captured from " &amp; TEXT(X_Cell_Site_StartDate, "d mmmm yyyy") &amp; " to " &amp; TEXT(X_Cell_Site_EndDate, "d, mmmm, yyyy") &amp; " from environmental plantings"</f>
         <v>Carbon captured from 1 January 2025 to 31, December, 2025 from environmental plantings</v>
       </c>
     </row>
-    <row r="41" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="41" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D41" s="21" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="E41" s="21" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="F41" s="21" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="G41" s="81" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="42" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="42" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D42" s="35"/>
       <c r="E42" s="77"/>
       <c r="F42" s="19"/>
@@ -15893,29 +15281,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
+    <row r="46" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D46" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="48" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="48" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D48" s="80" t="str">
         <f>"Gross emissions from other activity periods in the production timeframe " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " to " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Gross emissions from other activity periods in the production timeframe 1 November 2025 to 31 March 2026</v>
       </c>
     </row>
-    <row r="50" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="50" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D50" s="90" t="str" cm="1">
         <f t="array" ref="D50">"There are " &amp; Common_InputFunctions.getOverlappingReportingCycles(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate) &amp; " emissions calculation periods that need to be completed before total product emissions can be determined."</f>
         <v>There are 2 emissions calculation periods that need to be completed before total product emissions can be determined.</v>
       </c>
     </row>
-    <row r="51" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="51" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D51" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="53" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="53" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D53" s="81" t="s">
         <v>116</v>
       </c>
@@ -15926,7 +15314,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="54" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D54" s="1" t="str" cm="1">
         <f t="array" ref="D54:D55">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
         <v>01 Jan 2025 to 31 Dec 2025 (This reporting cycle)</v>
@@ -15943,7 +15331,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="55" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D55" s="1" t="str">
         <v>01 Jan 2026 to 31 Dec 2026</v>
       </c>
@@ -15959,7 +15347,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="56" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E56" s="77">
         <f>IF(ISBLANK($D56), 0, IF(ISNUMBER(SEARCH("reporting", $D56)), Result_Enterprise_Gross_Method1, "Enter value"))</f>
         <v>0</v>
@@ -15972,7 +15360,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="57" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E57" s="77">
         <f>IF(ISBLANK($D57), 0, IF(ISNUMBER(SEARCH("reporting", $D57)), Result_Enterprise_Gross_Method1, "Enter value"))</f>
         <v>0</v>
@@ -15985,7 +15373,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="58" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E58" s="77">
         <f>IF(ISBLANK($D58), 0, IF(ISNUMBER(SEARCH("reporting", $D58)), Result_Enterprise_Gross_Method1, "Enter value"))</f>
         <v>0</v>
@@ -15998,9 +15386,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="59" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D59" s="91" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E59" s="86" t="e">
         <f>SUM(E54:E58)</f>
@@ -16014,22 +15402,22 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
+    <row r="64" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D64" s="80" t="str">
         <f>"Carbon removals from environmental plantings for whole production cycle running between " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Carbon removals from environmental plantings for whole production cycle running between 1 November 2025 and 31 March 2026</v>
       </c>
     </row>
-    <row r="66" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="66" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D66" s="81" t="s">
         <v>116</v>
       </c>
       <c r="E66" s="81" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F66" s="81"/>
     </row>
-    <row r="67" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="67" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D67" s="1" t="str" cm="1">
         <f t="array" ref="D67:D68">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
         <v>01 Jan 2025 to 31 Dec 2025 (This reporting cycle)</v>
@@ -16039,10 +15427,10 @@
         <v>0</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="68" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="68" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D68" s="1" t="str">
         <v>01 Jan 2026 to 31 Dec 2026</v>
       </c>
@@ -16051,55 +15439,55 @@
         <v>Enter value</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="69" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="69" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E69" s="77">
         <f>IF(ISBLANK($D69), 0, IF(ISNUMBER(SEARCH("reporting", $D69)), SUM(Table_Input_Enterprise_PlantingRemovals[Removal allocated to this enterprise]), "Enter value"))</f>
         <v>0</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="70" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="70" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E70" s="77">
         <f>IF(ISBLANK($D70), 0, IF(ISNUMBER(SEARCH("reporting", $D70)), SUM(Table_Input_Enterprise_PlantingRemovals[Removal allocated to this enterprise]), "Enter value"))</f>
         <v>0</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="71" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="71" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E71" s="77">
         <f>IF(ISBLANK($D71), 0, IF(ISNUMBER(SEARCH("reporting", $D71)), SUM(Table_Input_Enterprise_PlantingRemovals[Removal allocated to this enterprise]), "Enter value"))</f>
         <v>0</v>
       </c>
       <c r="F71" s="10" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="72" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D72" s="91" t="s">
         <v>128</v>
-      </c>
-    </row>
-    <row r="72" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
-      <c r="D72" s="91" t="s">
-        <v>130</v>
       </c>
       <c r="E72" s="86">
         <f>SUM(E67:E71)</f>
         <v>0</v>
       </c>
       <c r="F72" s="92" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="75" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="75" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D75" s="80" t="str">
         <f>"Net emissions from other activity periods in the production timeframe " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " to " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Net emissions from other activity periods in the production timeframe 1 November 2025 to 31 March 2026</v>
       </c>
     </row>
-    <row r="77" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="77" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D77" s="81" t="s">
         <v>116</v>
       </c>
@@ -16110,7 +15498,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="78" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D78" s="1" t="str" cm="1">
         <f t="array" ref="D78:D79">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
         <v>01 Jan 2025 to 31 Dec 2025 (This reporting cycle)</v>
@@ -16127,7 +15515,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="79" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D79" s="1" t="str">
         <v>01 Jan 2026 to 31 Dec 2026</v>
       </c>
@@ -16143,7 +15531,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="80" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E80" s="77">
         <f>IF(ISBLANK($D80), 0, IF(ISNUMBER(SEARCH("reporting", $D80)), E56-$E$69, "Enter value"))</f>
         <v>0</v>
@@ -16156,7 +15544,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="81" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E81" s="77">
         <f>IF(ISBLANK($D81), 0, IF(ISNUMBER(SEARCH("reporting", $D81)), E57-$E$70, "Enter value"))</f>
         <v>0</v>
@@ -16169,7 +15557,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="82" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E82" s="77">
         <f>IF(ISBLANK($D82), 0, IF(ISNUMBER(SEARCH("reporting", $D82)), E58-$E$71, "Enter value"))</f>
         <v>0</v>
@@ -16182,9 +15570,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="83" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D83" s="91" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E83" s="86" t="e">
         <f>SUM(E78:E82)</f>
@@ -16211,8 +15599,8 @@
   <sheetPr>
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
-  <dimension ref="C1:K59"/>
-  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
+  <dimension ref="C1:K43"/>
+  <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -16223,9 +15611,9 @@
     <col min="12" max="12" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:11" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.35" customHeight="1"/>
-    <row r="2" spans="3:11" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="3:11" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="3:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="30"/>
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
@@ -16236,322 +15624,283 @@
       <c r="J3" s="30"/>
       <c r="K3" s="30"/>
     </row>
-    <row r="4" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D5" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="6" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="7" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D7" s="71" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="E7" s="71"/>
       <c r="F7" s="71"/>
     </row>
-    <row r="8" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D9" s="1" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="10" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="10" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D10" s="13" t="s">
         <v>64</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="11" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="12" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D12" s="1" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="E12" s="100">
         <v>1000</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="13" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="14" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D14" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="15" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="15" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D15" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E15" s="77">
+        <v>2392</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="16" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D16" s="1" t="s">
-        <v>324</v>
+        <v>303</v>
       </c>
       <c r="E16" s="77">
-        <v>2</v>
+        <v>2500</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="17" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="17" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D17" s="1" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="E17" s="16">
-        <f>X_Cell_Crop_AreaUnderCropping*E16</f>
-        <v>2000</v>
+        <f>X_Cell_Crop_TotalRoundModules/X_Cell_Crop_AreaUnderCropping</f>
+        <v>2.5</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="18" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D18" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="E18" s="77">
-        <v>4.41</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="19" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="19" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D19" s="1" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="E19" s="77">
         <v>227</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="20" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="20" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D20" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="E20" s="16">
-        <f>(E17*E18)*E19*10^-3</f>
-        <v>2002.14</v>
+        <v>295</v>
+      </c>
+      <c r="E20" s="102">
+        <v>0.41839999999999999</v>
       </c>
       <c r="F20" s="17" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="21" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D21" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="E21" s="103">
+        <f>(X_Cell_Crop_AverageWeightPerRoundModule*X_Cell_Crop_TurnoutRate)/X_Cell_Crop_WeightPerLintBale</f>
+        <v>4.4088669603524231</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D22" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E22" s="16">
+        <f>(X_Cell_Crop_TotalRoundModules*X_Cell_Crop_LintBalesPerRoundModule)*E19*10^-3</f>
+        <v>2502.0320000000002</v>
+      </c>
+      <c r="F22" s="17" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D21" s="1" t="s">
+    <row r="23" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D23" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="E23" s="16">
+        <f>E22/X_Cell_Crop_AreaUnderCropping</f>
+        <v>2.5020320000000003</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="25" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D25" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="E25" s="77">
+        <v>250</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="26" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D26" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E26" s="16">
+        <f>X_Cell_Crop_CottonSeedAmountPerRoundModule*X_Cell_Crop_TotalRoundModules*10^-3</f>
+        <v>625</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D28" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="E28" s="16">
+        <f>(X_Cell_Crop_AverageWeightPerRoundModule*X_Cell_Crop_TotalRoundModules*10^-3)-(X_Cell_Crop_LintYieldTotal+X_Cell_Crop_CottonseedYieldTotal)</f>
+        <v>2852.9679999999998</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D30" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="E21" s="102">
-        <v>0.41839999999999999</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="22" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D22" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E22" s="16">
-        <f>(E19*E18)/E21</f>
-        <v>2392.6147227533461</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="23" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D24" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="E24" s="77">
-        <v>250</v>
-      </c>
-      <c r="F24" s="17" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="25" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="E25" s="16">
-        <f>E24*E17*10^-3</f>
-        <v>500</v>
-      </c>
-      <c r="F25" s="17" t="s">
+      <c r="E30" s="16">
+        <f>(X_Cell_Crop_AverageWeightPerRoundModule*X_Cell_Crop_TotalRoundModules*10^-3)-X_Cell_Crop_TrashTotalProduced</f>
+        <v>3127.0320000000002</v>
+      </c>
+      <c r="F30" s="17" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D27" s="1" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="28" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D28" s="78"/>
-    </row>
-    <row r="29" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D29" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="E29" s="16" cm="1">
-        <f t="array" ref="E29">Common_InputFunctions.Utility_LookupValueInTableNumber(X_Cell_Crop_CropType, [1]!Table_SourceData_CropAttributes[Crop type],[1]!Table_SourceData_CropAttributes[Residue: Crop ratio])</f>
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="30" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D30" s="90"/>
-    </row>
-    <row r="31" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D31" s="90"/>
-    </row>
-    <row r="32" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D33" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="34" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D35" s="1" t="e">
-        <f>"Residue after " &amp; VLOOKUP(X_Cell_Crop_CropPurpose,'[1]Constants - Ag Residue'!D8:G10, 4, FALSE)</f>
-        <v>#N/A</v>
+        <v>285</v>
+      </c>
+    </row>
+    <row r="34" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D34" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="E34" s="16">
+        <f ca="1">Common_InputFunctions.Utility_LookupValueInTableNumber(X_Cell_Crop_CropType, INDIRECT("Table_SourceData_CropAttributes[Crop type]"),INDIRECT("Table_SourceData_CropAttributes[Residue: Crop ratio]"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D35" s="1" t="s">
+        <v>319</v>
       </c>
       <c r="E35" s="16">
-        <f>E29*X_Cell_Crop_AreaUnderCropping</f>
-        <v>1900</v>
+        <f ca="1">X_Cell_Crop_LintYieldTotal*X_Cell_Crop_ResidueToCropRatio</f>
+        <v>0</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="36" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D37" s="80" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="38" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="38" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D38" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E38" s="16">
-        <f>E28*X_Cell_Crop_AreaUnderCropping</f>
+        <v>287</v>
+      </c>
+      <c r="E38" s="19">
+        <v>0.1</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="39" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D39" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="E39" s="19">
+        <v>0.6</v>
+      </c>
+      <c r="F39" s="17" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="40" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D40" s="78" t="s">
+        <v>289</v>
+      </c>
+      <c r="E40" s="101">
+        <f ca="1">IFERROR((X_Cell_Crop_TotalResidueBaled*10^3)/X_Cell_Crop_AverageWeightPerBale, 0)</f>
         <v>0</v>
       </c>
-      <c r="F38" s="17" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="39" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D39" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="F39" s="17" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="40" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="78" t="s">
-        <v>305</v>
-      </c>
       <c r="F40" s="17" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="41" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="41" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D41" s="78" t="s">
-        <v>306</v>
-      </c>
-      <c r="E41" s="19">
-        <v>0.11</v>
+        <v>290</v>
+      </c>
+      <c r="E41" s="16">
+        <f ca="1">X_Cell_Crop_ResidueAfterHarvest*X_Cell_Crop_PercentResidueBaled</f>
+        <v>0</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="42" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E42" s="77">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="43" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D43" s="80" t="s">
-        <v>307</v>
-      </c>
-      <c r="E43" s="101">
-        <f>IFERROR((X_Cell_Crop_TotalResidueBaled*10^3)/X_Cell_Crop_AverageWeightPerBale, 0)</f>
+        <v>308</v>
+      </c>
+    </row>
+    <row r="43" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D43" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E43" s="16">
+        <f ca="1">E35-X_Cell_Crop_TotalResidueBaled</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D44" s="1" t="s">
+      <c r="F43" s="17" t="s">
         <v>308</v>
       </c>
-      <c r="E44" s="16">
-        <f>E38*X_Cell_Crop_PercentResidueBaled</f>
-        <v>0</v>
-      </c>
-      <c r="F44" s="17" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="45" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D45" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="F45" s="17" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="46" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D47" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E47" s="19">
-        <v>0.3</v>
-      </c>
-      <c r="F47" s="17" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="48" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E48" s="16">
-        <f>E38*X_Cell_Crop_PercentResidueBurned</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="5:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="5:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E50" s="16">
-        <f>E38-X_Cell_Crop_TotalResidueBaled-E48</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="5:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="5:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="5:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="5:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="5:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="5:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="5:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="5:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="5:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="F47">
+  <conditionalFormatting sqref="F43">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -16571,7 +15920,7 @@
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -16580,16 +15929,16 @@
     <col min="11" max="11" width="4.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.35" customHeight="1">
+    <row r="1" spans="1:11" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25" ht="20" customHeight="1"/>
-    <row r="3" spans="1:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="30"/>
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
@@ -16600,29 +15949,29 @@
       <c r="J3" s="30"/>
       <c r="K3" s="30"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="5" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D5" s="71" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="E5" s="71"/>
       <c r="F5" s="71"/>
       <c r="G5" s="71"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="6" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F6" s="17"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D7" s="1" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="F7" s="17"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="8" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D8" s="1" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="E8" s="16" t="str" cm="1">
         <f t="array" ref="E8">_xlfn.IFS(X_Cell_Crop_CropType="Maize", "Maize", X_Cell_Crop_CropType="Cotton", "Cotton", TRUE, "Grains")</f>
@@ -16630,18 +15979,18 @@
       </c>
       <c r="F8" s="17"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="9" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D9" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="16" t="e" cm="1">
+      <c r="E9" s="16" t="str" cm="1">
         <f t="array" ref="E9">X_Cell_Crop_IrrigationMethod</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>Sprinkler irrigation</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D10" s="1" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="E10" s="16" cm="1">
         <f t="array" ref="E10">X_Cell_Crop_AreaUnderCropping</f>
@@ -16659,7 +16008,7 @@
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
   <dimension ref="C1:M65"/>
-  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -16672,13 +16021,13 @@
     <col min="14" max="14" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:13" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.35" customHeight="1">
+    <row r="1" spans="3:13" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1" s="11" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="2" spans="3:13" s="3" customFormat="1" x14ac:dyDescent="0.25" ht="20" customHeight="1"/>
-    <row r="3" spans="3:13" ht="20" x14ac:dyDescent="0.25" customHeight="1">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="30"/>
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
@@ -16691,47 +16040,47 @@
       <c r="L3" s="30"/>
       <c r="M3" s="30"/>
     </row>
-    <row r="5" spans="3:13" ht="20" x14ac:dyDescent="0.25" customHeight="1">
+    <row r="5" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D5" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="7" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="7" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D7" s="81" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="E7" s="81" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="F7" s="81" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="G7" s="81" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="H7" s="81" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="I7" s="81" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="J7" s="81" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="8" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="8" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D8" s="1" t="str">
         <f>"Unprocessed cotton yield"</f>
         <v>Unprocessed cotton yield</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="H8" s="85"/>
       <c r="I8" s="85"/>
@@ -16740,7 +16089,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="9" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D9" s="1" t="str">
         <f>"Processed cotton lint yield"</f>
         <v>Processed cotton lint yield</v>
@@ -16755,7 +16104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="10" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D10" s="1" t="str">
         <f>"Cottonseed yield"</f>
         <v>Cottonseed yield</v>
@@ -16770,19 +16119,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="11" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D11" s="1" t="str">
         <f>"Cotton lint sold"</f>
         <v>Cotton lint sold</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="H11" s="85"/>
       <c r="I11" s="85"/>
@@ -16791,19 +16140,19 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="12" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D12" s="1" t="str">
         <f>"Cottonseed sold"</f>
         <v>Cottonseed sold</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="H12" s="85"/>
       <c r="I12" s="85"/>
@@ -16812,19 +16161,19 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="13" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D13" s="1" t="str">
         <f>"Percent income from cotton lint sold"</f>
         <v>Percent income from cotton lint sold</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="H13" s="85"/>
       <c r="I13" s="85"/>
@@ -16833,19 +16182,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="14" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D14" s="1" t="str">
         <f>"Percent income from cotton seed sold"</f>
         <v>Percent income from cotton seed sold</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="H14" s="85"/>
       <c r="I14" s="85"/>
@@ -16854,53 +16203,53 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="16" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J16" s="86">
         <f>SUM(Table_Input_DataQuality_Enterprise[Score])</f>
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
+    <row r="17" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D17" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="19" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="19" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D19" s="81" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="E19" s="81" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="F19" s="81" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="G19" s="81" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="H19" s="81" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="I19" s="81" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="J19" s="81" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="20" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="20" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D20" s="1" t="str">
         <f>"Leaching zone"</f>
         <v>Leaching zone</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="H20" s="85"/>
       <c r="I20" s="85"/>
@@ -16909,19 +16258,19 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="21" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D21" s="1" t="str">
         <f>"Elevation"</f>
         <v>Elevation</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="H21" s="85"/>
       <c r="I21" s="85"/>
@@ -16930,19 +16279,19 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="22" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D22" s="1" t="str">
         <f>"Average temperature for reporting period"</f>
         <v>Average temperature for reporting period</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="H22" s="85"/>
       <c r="I22" s="85"/>
@@ -16951,19 +16300,19 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="23" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D23" s="1" t="str">
         <f>"Total rainfall for reporting period"</f>
         <v>Total rainfall for reporting period</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="H23" s="85"/>
       <c r="I23" s="85"/>
@@ -16972,19 +16321,19 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="24" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D24" s="1" t="str">
         <f>"Potential evapotranspiration for reporting period"</f>
         <v>Potential evapotranspiration for reporting period</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="H24" s="85"/>
       <c r="I24" s="85"/>
@@ -16993,19 +16342,19 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="25" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D25" s="1" t="str">
         <f>"Number of frost days for reporting period"</f>
         <v>Number of frost days for reporting period</v>
       </c>
       <c r="E25" s="87" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="F25" s="87" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="G25" s="87" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="H25" s="85"/>
       <c r="I25" s="85"/>
@@ -17014,53 +16363,53 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="27" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J27" s="86">
         <f>SUM(Table_Input_DataQuality_Site[Score])</f>
         <v>73</v>
       </c>
     </row>
-    <row r="28" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
+    <row r="28" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D28" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="30" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="30" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D30" s="81" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="E30" s="81" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="F30" s="81" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="G30" s="81" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="H30" s="81" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="I30" s="81" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="J30" s="81" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="31" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="31" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D31" s="1" t="str">
         <f>"Irrigation method"</f>
         <v>Irrigation method</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="H31" s="85"/>
       <c r="I31" s="85"/>
@@ -17069,19 +16418,19 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="32" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D32" s="1" t="str">
         <f>"Area under cropping"</f>
         <v>Area under cropping</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="H32" s="85"/>
       <c r="I32" s="85"/>
@@ -17090,19 +16439,19 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="33" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D33" s="1" t="str">
         <f>"Residue management"</f>
         <v>Residue management</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="H33" s="85"/>
       <c r="I33" s="85"/>
@@ -17111,53 +16460,53 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="35" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J35" s="86">
         <f>SUM(Table_Input_DataQuality_PastureManagement[Score])</f>
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
+    <row r="36" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D36" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="38" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="38" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D38" s="81" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="E38" s="81" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="F38" s="81" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="G38" s="81" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="H38" s="81" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="I38" s="81" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="J38" s="81" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="39" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="39" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D39" s="1" t="str">
         <f>"Branded inorganic fertiliser applications"</f>
         <v>Branded inorganic fertiliser applications</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="G39" s="14" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="H39" s="85"/>
       <c r="I39" s="85"/>
@@ -17166,19 +16515,19 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="40" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D40" s="1" t="str">
         <f>"Custom inorganic fertiliser blend applications"</f>
         <v>Custom inorganic fertiliser blend applications</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="H40" s="85"/>
       <c r="I40" s="85"/>
@@ -17187,19 +16536,19 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="41" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D41" s="1" t="str">
         <f>"Lime applications"</f>
         <v>Lime applications</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="G41" s="14" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="H41" s="85"/>
       <c r="I41" s="85"/>
@@ -17208,19 +16557,19 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="42" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D42" s="1" t="str">
         <f>"Organic fertiliser applications"</f>
         <v>Organic fertiliser applications</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="H42" s="85"/>
       <c r="I42" s="85"/>
@@ -17229,53 +16578,53 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="44" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J44" s="86">
         <f>SUM(Table_Input_DataQuality_FertiliserApplications[Score])</f>
         <v>55</v>
       </c>
     </row>
-    <row r="45" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
+    <row r="45" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D45" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="47" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="47" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D47" s="81" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="E47" s="81" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="F47" s="81" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="G47" s="81" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="H47" s="81" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="I47" s="81" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="J47" s="81" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="48" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="48" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D48" s="1" t="str">
         <f>"Fuel purchases"</f>
         <v>Fuel purchases</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="G48" s="14" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="H48" s="85"/>
       <c r="I48" s="85"/>
@@ -17284,19 +16633,19 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="49" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D49" s="1" t="str">
         <f>"Fuel consumption"</f>
         <v>Fuel consumption</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="G49" s="14" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="H49" s="85"/>
       <c r="I49" s="85"/>
@@ -17305,19 +16654,19 @@
         <v>14</v>
       </c>
     </row>
-    <row r="50" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="50" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D50" s="1" t="str">
         <f>"Electricity consumption"</f>
         <v>Electricity consumption</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="G50" s="14" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="H50" s="85"/>
       <c r="I50" s="85"/>
@@ -17326,19 +16675,19 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="51" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D51" s="1" t="str">
         <f>"Electricity generation"</f>
         <v>Electricity generation</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="G51" s="14" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="H51" s="85"/>
       <c r="I51" s="85"/>
@@ -17347,53 +16696,53 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="53" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J53" s="86">
         <f>SUM(Table_Input_DataQuality_FuelElectricity[Score])</f>
         <v>55</v>
       </c>
     </row>
-    <row r="55" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
+    <row r="55" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D55" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="57" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="57" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D57" s="81" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="E57" s="81" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="F57" s="81" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="G57" s="81" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="H57" s="81" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="I57" s="81" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="J57" s="81" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="58" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="58" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D58" s="1" t="str">
         <f>"Farm input purchases"</f>
         <v>Farm input purchases</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="G58" s="14" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="H58" s="85"/>
       <c r="I58" s="85"/>
@@ -17402,19 +16751,19 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="59" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D59" s="1" t="str">
         <f>"Inbound freight use"</f>
         <v>Inbound freight use</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="G59" s="14" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="H59" s="85"/>
       <c r="I59" s="85"/>
@@ -17423,19 +16772,19 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="60" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D60" s="1" t="str">
         <f>"Outbound freight use"</f>
         <v>Outbound freight use</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="F60" s="14" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="G60" s="14" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="H60" s="85"/>
       <c r="I60" s="85"/>
@@ -17444,19 +16793,19 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="61" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D61" s="1" t="str">
         <f>"Solid waste generation and treatment"</f>
         <v>Solid waste generation and treatment</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="G61" s="14" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="H61" s="85"/>
       <c r="I61" s="85"/>
@@ -17465,15 +16814,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="63" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J63" s="86">
         <f>SUM(Table_Input_DataQuality_FarmInputsFreightWaste[Score])</f>
         <v>55</v>
       </c>
     </row>
-    <row r="65" spans="4:5" ht="20" x14ac:dyDescent="0.25" customHeight="1">
+    <row r="65" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D65" s="88" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="E65" s="89" t="str">
         <f>(J16+J27+J35+J44+J53+J63)&amp;" out of "&amp;((COUNT(Table_Input_DataQuality_Enterprise[Score])*15)+(COUNT(Table_Input_DataQuality_Site[Score])*15)+(COUNT(Table_Input_DataQuality_PastureManagement[Score])*15)+(COUNT(Table_Input_DataQuality_FertiliserApplications[Score])*15)+(COUNT(Table_Input_DataQuality_FuelElectricity[Score])*15)+(COUNT(Table_Input_DataQuality_FarmInputsFreightWaste[Score])*15))</f>
@@ -17510,7 +16859,7 @@
     <tabColor theme="2" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:BY297"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="23" customWidth="1"/>
     <col min="2" max="2" width="2.7109375" style="23" customWidth="1"/>
@@ -17543,10 +16892,10 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:65" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -17573,11 +16922,11 @@
       <c r="V3" s="25"/>
       <c r="W3" s="25"/>
     </row>
-    <row r="4" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4"/>
       <c r="BM4" s="26"/>
     </row>
-    <row r="5" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5"/>
       <c r="D5" s="2" t="str" cm="1">
         <f t="array" ref="D5">Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title()</f>
@@ -17585,7 +16934,7 @@
       </c>
       <c r="BM5" s="26"/>
     </row>
-    <row r="6" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="83" t="s">
         <v>2</v>
       </c>
@@ -17599,7 +16948,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="84" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -17617,7 +16966,7 @@
         <v>NSW</v>
       </c>
     </row>
-    <row r="8" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -17635,7 +16984,7 @@
         <v>ACT</v>
       </c>
     </row>
-    <row r="9" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9"/>
       <c r="D9" s="21" t="str" cm="1">
         <f t="array" ref="D9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -17650,7 +16999,7 @@
         <v>VIC</v>
       </c>
     </row>
-    <row r="10" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10"/>
       <c r="D10" s="21" t="str" cm="1">
         <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -17665,7 +17014,7 @@
         <v>QLD</v>
       </c>
     </row>
-    <row r="11" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11"/>
       <c r="D11" s="21" t="str" cm="1">
         <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -17681,7 +17030,7 @@
       </c>
       <c r="BM11" s="26"/>
     </row>
-    <row r="12" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12"/>
       <c r="D12" s="21" t="str" cm="1">
         <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -17697,7 +17046,7 @@
       </c>
       <c r="BM12" s="26"/>
     </row>
-    <row r="13" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13"/>
       <c r="D13" s="21" t="str" cm="1">
         <f t="array" ref="D13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -17712,7 +17061,7 @@
         <v>TAS</v>
       </c>
     </row>
-    <row r="14" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14"/>
       <c r="D14" s="21" t="str" cm="1">
         <f t="array" ref="D14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -17727,129 +17076,129 @@
         <v>NT</v>
       </c>
     </row>
-    <row r="15" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15"/>
     </row>
-    <row r="16" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16"/>
     </row>
-    <row r="17" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17"/>
     </row>
-    <row r="18" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18"/>
       <c r="D18" s="2" t="str" cm="1">
         <f t="array" ref="D18">Common_SourceData.Common_SourceData_WASA4Areas_Title()</f>
         <v>ABS Statistcal Areas Level 4 - Western Australia</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19"/>
       <c r="D19" s="18" t="str" cm="1">
         <f t="array" ref="D19">Common_SourceData.Common_SourceData_WASA4Areas_Source()</f>
         <v>Australian Bureau of Statistics (ABS) - Statistical Areas Level 2 - 2021 - Shapefile</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20"/>
       <c r="D20" s="21" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21"/>
       <c r="D21" s="21" t="str" cm="1">
         <f t="array" ref="D21">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Bunbury</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22"/>
       <c r="D22" s="21" t="str" cm="1">
         <f t="array" ref="D22">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Mandurah</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23"/>
       <c r="D23" s="21" t="str" cm="1">
         <f t="array" ref="D23">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - Inner</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24"/>
       <c r="D24" s="21" t="str" cm="1">
         <f t="array" ref="D24">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North East</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25"/>
       <c r="D25" s="21" t="str" cm="1">
         <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North West</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26"/>
       <c r="D26" s="21" t="str" cm="1">
         <f t="array" ref="D26">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South East</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27"/>
       <c r="D27" s="21" t="str" cm="1">
         <f t="array" ref="D27">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South West</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28"/>
       <c r="D28" s="21" t="str" cm="1">
         <f t="array" ref="D28">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Wheat Belt</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29"/>
       <c r="D29" s="21" t="str" cm="1">
         <f t="array" ref="D29">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (North)</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30"/>
       <c r="D30" s="21" t="str" cm="1">
         <f t="array" ref="D30">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (South)</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31"/>
     </row>
-    <row r="32" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32"/>
     </row>
-    <row r="33" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33"/>
     </row>
-    <row r="34" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34"/>
       <c r="D34" s="2" t="str" cm="1">
         <f t="array" ref="D34">Common_SourceData.Common_SourceData_GWP_Title()</f>
         <v>Global warming potential for greenhouse gases</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35"/>
       <c r="D35" s="18" t="str" cm="1">
         <f t="array" ref="D35">Common_SourceData.Common_SourceData_GWP_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36"/>
       <c r="D36" s="21" t="s">
         <v>26</v>
@@ -17858,7 +17207,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37"/>
       <c r="D37" s="21" t="str" cm="1">
         <f t="array" ref="D37">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17869,7 +17218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38"/>
       <c r="D38" s="21" t="str" cm="1">
         <f t="array" ref="D38">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17880,7 +17229,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39"/>
       <c r="D39" s="21" t="str" cm="1">
         <f t="array" ref="D39">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17891,7 +17240,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40"/>
       <c r="D40" s="21" t="str" cm="1">
         <f t="array" ref="D40">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17902,7 +17251,7 @@
         <v>6630</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41"/>
       <c r="D41" s="21" t="str" cm="1">
         <f t="array" ref="D41">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17913,7 +17262,7 @@
         <v>12200</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42"/>
       <c r="D42" s="21" t="str" cm="1">
         <f t="array" ref="D42">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17924,7 +17273,7 @@
         <v>22800</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43"/>
       <c r="D43" s="21" t="str" cm="1">
         <f t="array" ref="D43">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17935,24 +17284,24 @@
         <v>17200</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44"/>
     </row>
-    <row r="45" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45"/>
       <c r="D45" s="2" t="str" cm="1">
         <f t="array" ref="D45">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Title()</f>
         <v>Factor to convert elemental mass of gas to molecular mass</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46"/>
       <c r="D46" s="18" t="str" cm="1">
         <f t="array" ref="D46">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47"/>
       <c r="D47" s="21" t="s">
         <v>26</v>
@@ -17970,7 +17319,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48"/>
       <c r="D48" s="21" t="str" cm="1">
         <f t="array" ref="D48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17993,7 +17342,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49"/>
       <c r="D49" s="21" t="str" cm="1">
         <f t="array" ref="D49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -18016,7 +17365,7 @@
         <v>1.3333333333333333</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50"/>
       <c r="D50" s="21" t="str" cm="1">
         <f t="array" ref="D50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -18039,7 +17388,7 @@
         <v>1.5714285714285714</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51"/>
       <c r="D51" s="21" t="str" cm="1">
         <f t="array" ref="D51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -18062,7 +17411,7 @@
         <v>3.2857142857142856</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52"/>
       <c r="D52" s="21" t="str" cm="1">
         <f t="array" ref="D52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -18085,7 +17434,7 @@
         <v>2.3333333333333335</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53"/>
       <c r="D53" s="21" t="str" cm="1">
         <f t="array" ref="D53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -18108,7 +17457,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54"/>
       <c r="D54" s="21" t="str" cm="1">
         <f t="array" ref="D54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -18131,49 +17480,49 @@
         <v>1.1666666666666667</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55"/>
     </row>
-    <row r="56" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56"/>
     </row>
-    <row r="57" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57"/>
       <c r="D57" s="2" t="str" cm="1">
         <f t="array" ref="D57">Common_SourceData.Common_SourceData_WetAndDryZones_Title()</f>
         <v>VEERG Australian wet and dry zones</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58"/>
       <c r="D58" s="18" t="str" cm="1">
         <f t="array" ref="D58">Common_SourceData.Common_SourceData_WetAndDryZones_Source()</f>
         <v>VEERG 2026: Table 1.2: Translating climate zones to wet and dry zones</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59"/>
       <c r="D59" s="27" t="str" cm="1">
         <f t="array" ref="D59:D61">"⚠️" &amp; Common_SourceData.Common_SourceData_WetAndDryZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60"/>
       <c r="D60" s="27" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61"/>
       <c r="D61" s="27" t="str">
         <v>⚠️Fixed typo - Changed 'Fry' to 'Dry'.</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62"/>
     </row>
-    <row r="63" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63"/>
       <c r="D63" s="21" t="s">
         <v>32</v>
@@ -18182,7 +17531,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64"/>
       <c r="D64" s="21" t="str" cm="1">
         <f t="array" ref="D64">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -18193,7 +17542,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65"/>
       <c r="D65" s="21" t="str" cm="1">
         <f t="array" ref="D65">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -18204,7 +17553,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66"/>
       <c r="D66" s="21" t="str" cm="1">
         <f t="array" ref="D66">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -18215,7 +17564,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67"/>
       <c r="D67" s="21" t="str" cm="1">
         <f t="array" ref="D67">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -18226,7 +17575,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68"/>
       <c r="D68" s="21" t="str" cm="1">
         <f t="array" ref="D68">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -18237,7 +17586,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69"/>
       <c r="D69" s="21" t="str" cm="1">
         <f t="array" ref="D69">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -18248,7 +17597,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70"/>
       <c r="D70" s="21" t="str" cm="1">
         <f t="array" ref="D70">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -18259,7 +17608,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71"/>
       <c r="D71" s="21" t="str" cm="1">
         <f t="array" ref="D71">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -18270,7 +17619,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72"/>
       <c r="D72" s="21" t="str" cm="1">
         <f t="array" ref="D72">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -18281,7 +17630,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73"/>
       <c r="D73" s="21" t="str" cm="1">
         <f t="array" ref="D73">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -18292,7 +17641,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74"/>
       <c r="D74" s="21" t="str" cm="1">
         <f t="array" ref="D74">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -18303,7 +17652,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75"/>
       <c r="D75" s="21" t="str" cm="1">
         <f t="array" ref="D75">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -18314,7 +17663,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76"/>
       <c r="D76" s="21" t="str" cm="1">
         <f t="array" ref="D76">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -18325,7 +17674,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77"/>
       <c r="D77" s="21" t="str" cm="1">
         <f t="array" ref="D77">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -18336,64 +17685,64 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78"/>
     </row>
-    <row r="79" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79"/>
     </row>
-    <row r="80" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80"/>
     </row>
-    <row r="81" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81"/>
       <c r="D81" s="2" t="str" cm="1">
         <f t="array" ref="D81">Common_SourceData.Common_SourceData_ClimateZones_Title()</f>
         <v>VEERG Australian climate zones</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82"/>
       <c r="D82" s="18" t="str" cm="1">
         <f t="array" ref="D82">Common_SourceData.Common_SourceData_ClimateZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83"/>
       <c r="D83" s="27" t="str" cm="1">
         <f t="array" ref="D83:D87">"⚠️" &amp; Common_SourceData.Common_SourceData_ClimateZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84"/>
       <c r="D84" s="27" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85"/>
       <c r="D85" s="27" t="str">
         <v>⚠️Fixed typo in MAT value for warm temperate dry - changed 10 to 11.</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86"/>
       <c r="D86" s="27" t="str">
         <v>⚠️Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87"/>
       <c r="D87" s="27" t="str">
         <v>⚠️GAF accepts rainfall as a proxy for precipitation.</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88"/>
     </row>
-    <row r="89" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89"/>
       <c r="D89" s="21" t="s">
         <v>32</v>
@@ -18445,7 +17794,7 @@
       </c>
       <c r="T89" s="21"/>
     </row>
-    <row r="90" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90"/>
       <c r="D90" s="21" t="str" cm="1">
         <f t="array" ref="D90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18513,7 +17862,7 @@
       </c>
       <c r="T90" s="21"/>
     </row>
-    <row r="91" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91"/>
       <c r="D91" s="21" t="str" cm="1">
         <f t="array" ref="D91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18581,7 +17930,7 @@
       </c>
       <c r="T91" s="21"/>
     </row>
-    <row r="92" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92"/>
       <c r="D92" s="21" t="str" cm="1">
         <f t="array" ref="D92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18649,7 +17998,7 @@
       </c>
       <c r="T92" s="21"/>
     </row>
-    <row r="93" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93"/>
       <c r="D93" s="21" t="str" cm="1">
         <f t="array" ref="D93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18717,7 +18066,7 @@
       </c>
       <c r="T93" s="21"/>
     </row>
-    <row r="94" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94"/>
       <c r="D94" s="21" t="str" cm="1">
         <f t="array" ref="D94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18785,7 +18134,7 @@
       </c>
       <c r="T94" s="21"/>
     </row>
-    <row r="95" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95"/>
       <c r="D95" s="21" t="str" cm="1">
         <f t="array" ref="D95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18853,7 +18202,7 @@
       </c>
       <c r="T95" s="21"/>
     </row>
-    <row r="96" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96"/>
       <c r="D96" s="21" t="str" cm="1">
         <f t="array" ref="D96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18921,7 +18270,7 @@
       </c>
       <c r="T96" s="21"/>
     </row>
-    <row r="97" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97"/>
       <c r="D97" s="21" t="str" cm="1">
         <f t="array" ref="D97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18989,66 +18338,66 @@
       </c>
       <c r="T97" s="21"/>
     </row>
-    <row r="98" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98"/>
     </row>
-    <row r="99" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99"/>
       <c r="D99" s="10" t="str" cm="1">
         <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100"/>
       <c r="D100" s="10" t="str">
         <v>MAT = mean annual temperature</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101"/>
       <c r="D101" s="10" t="str">
         <v>MAP = mean annual precipitation</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102"/>
       <c r="D102" s="10" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="103" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103"/>
       <c r="D103" s="10"/>
     </row>
-    <row r="104" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104"/>
     </row>
-    <row r="105" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105"/>
       <c r="D105" s="2" t="str" cm="1">
         <f t="array" ref="D105">Common_SourceData.Common_SourceData_TemperatureZones_Title()</f>
         <v>VEERG Australian temperature zones</v>
       </c>
     </row>
-    <row r="106" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106"/>
       <c r="D106" s="18" t="str" cm="1">
         <f t="array" ref="D106">Common_SourceData.Common_SourceData_TemperatureZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="107" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107"/>
       <c r="D107" s="27" t="str" cm="1">
         <f t="array" ref="D107">"⚠️" &amp; Common_SourceData.Common_SourceData_TemperatureZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.</v>
       </c>
     </row>
-    <row r="108" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108"/>
     </row>
-    <row r="109" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109"/>
       <c r="D109" s="21" t="s">
         <v>49</v>
@@ -19063,7 +18412,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="110" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110"/>
       <c r="D110" s="21" t="str" cm="1">
         <f t="array" ref="D110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -19082,7 +18431,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="111" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111"/>
       <c r="D111" s="21" t="str" cm="1">
         <f t="array" ref="D111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -19101,7 +18450,7 @@
         <v>25.998999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112"/>
       <c r="D112" s="21" t="str" cm="1">
         <f t="array" ref="D112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -19120,13 +18469,13 @@
         <v>14.999000000000001</v>
       </c>
     </row>
-    <row r="113" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113"/>
     </row>
-    <row r="114" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114"/>
     </row>
-    <row r="115" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115"/>
       <c r="D115" s="2" t="str" cm="1">
         <f t="array" ref="D115">Common_SourceData.Common_SourceData_RainfallZones_Title()</f>
@@ -19134,7 +18483,7 @@
       </c>
       <c r="BN115" s="23"/>
     </row>
-    <row r="116" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116"/>
       <c r="D116" s="18" t="str" cm="1">
         <f t="array" ref="D116">Common_SourceData.Common_SourceData_RainfallZones_Source()</f>
@@ -19142,7 +18491,7 @@
       </c>
       <c r="BN116" s="23"/>
     </row>
-    <row r="117" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117"/>
       <c r="D117" s="27" t="str" cm="1">
         <f t="array" ref="D117">"⚠️" &amp; Common_SourceData.Common_SourceData_RainfallZones_Variation()</f>
@@ -19150,11 +18499,11 @@
       </c>
       <c r="BN117" s="23"/>
     </row>
-    <row r="118" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118"/>
       <c r="BN118" s="23"/>
     </row>
-    <row r="119" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119"/>
       <c r="D119" s="21" t="s">
         <v>52</v>
@@ -19170,7 +18519,7 @@
       </c>
       <c r="BN119" s="23"/>
     </row>
-    <row r="120" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120"/>
       <c r="D120" s="21" t="str" cm="1">
         <f t="array" ref="D120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -19190,7 +18539,7 @@
       </c>
       <c r="BN120" s="23"/>
     </row>
-    <row r="121" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121"/>
       <c r="D121" s="21" t="str" cm="1">
         <f t="array" ref="D121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -19210,31 +18559,31 @@
       </c>
       <c r="BN121" s="23"/>
     </row>
-    <row r="122" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122"/>
       <c r="BN122" s="23"/>
     </row>
-    <row r="123" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123"/>
     </row>
-    <row r="124" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124"/>
       <c r="D124" s="2" t="str" cm="1">
         <f t="array" ref="D124">Common_SourceData.Common_SourceData_LeachingZones_Title()</f>
         <v>VEERG Australian leaching zones</v>
       </c>
     </row>
-    <row r="125" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125"/>
       <c r="D125" s="18" t="str" cm="1">
         <f t="array" ref="D125">Common_SourceData.Common_SourceData_LeachingZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="126" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126"/>
     </row>
-    <row r="127" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127"/>
       <c r="D127" s="21" t="s">
         <v>54</v>
@@ -19243,7 +18592,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="128" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128"/>
       <c r="D128" s="21" t="str" cm="1">
         <f t="array" ref="D128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -19254,7 +18603,7 @@
         <v>Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="129" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129"/>
       <c r="D129" s="21" t="str" cm="1">
         <f t="array" ref="D129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -19265,13 +18614,13 @@
         <v>Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="130" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130"/>
     </row>
-    <row r="131" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131"/>
     </row>
-    <row r="132" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132"/>
       <c r="D132" s="2" t="str" cm="1">
         <f t="array" ref="D132">Common_SourceData.Common_SourceData_FracWET_Title()</f>
@@ -19279,7 +18628,7 @@
       </c>
       <c r="E132" s="9"/>
     </row>
-    <row r="133" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133"/>
       <c r="D133" s="18" t="str" cm="1">
         <f t="array" ref="D133">Common_SourceData.Common_SourceData_FracWET_Source()</f>
@@ -19287,7 +18636,7 @@
       </c>
       <c r="E133" s="9"/>
     </row>
-    <row r="134" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134"/>
       <c r="D134" t="s">
         <v>56</v>
@@ -19296,7 +18645,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="135" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135"/>
       <c r="D135" t="str" cm="1">
         <f t="array" ref="D135">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -19307,7 +18656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136"/>
       <c r="D136" s="1" t="str" cm="1">
         <f t="array" ref="D136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -19318,10 +18667,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137"/>
     </row>
-    <row r="138" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138"/>
       <c r="BN138" s="23"/>
       <c r="BO138" s="23"/>
@@ -19336,7 +18685,7 @@
       <c r="BX138" s="23"/>
       <c r="BY138" s="23"/>
     </row>
-    <row r="139" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139"/>
       <c r="D139" s="2" t="str" cm="1">
         <f t="array" ref="D139">Common_SourceData.Common_SourceData_FracWETIrrigation_Title()</f>
@@ -19355,7 +18704,7 @@
       <c r="BX139" s="23"/>
       <c r="BY139" s="23"/>
     </row>
-    <row r="140" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140"/>
       <c r="D140" s="18" t="str" cm="1">
         <f t="array" ref="D140">Common_SourceData.Common_SourceData_FracWETIrrigation_Source()</f>
@@ -19374,7 +18723,7 @@
       <c r="BX140" s="23"/>
       <c r="BY140" s="23"/>
     </row>
-    <row r="141" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141"/>
       <c r="D141" s="27" t="str" cm="1">
         <f t="array" ref="D141">Common_SourceData.Common_SourceData_FracWETIrrigation_Variation()</f>
@@ -19382,7 +18731,7 @@
       </c>
       <c r="BN141" s="23"/>
     </row>
-    <row r="142" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142"/>
       <c r="D142" s="21" t="s">
         <v>58</v>
@@ -19392,7 +18741,7 @@
       </c>
       <c r="BN142" s="23"/>
     </row>
-    <row r="143" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143"/>
       <c r="D143" s="21" t="str" cm="1">
         <f t="array" ref="D143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -19404,7 +18753,7 @@
       </c>
       <c r="BN143" s="23"/>
     </row>
-    <row r="144" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144"/>
       <c r="D144" s="1" t="str" cm="1">
         <f t="array" ref="D144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -19416,7 +18765,7 @@
       </c>
       <c r="BN144" s="23"/>
     </row>
-    <row r="145" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145"/>
       <c r="D145" s="1" t="str" cm="1">
         <f t="array" ref="D145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -19428,7 +18777,7 @@
       </c>
       <c r="BN145" s="23"/>
     </row>
-    <row r="146" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146"/>
       <c r="D146" s="1" t="str" cm="1">
         <f t="array" ref="D146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -19440,7 +18789,7 @@
       </c>
       <c r="BN146" s="23"/>
     </row>
-    <row r="147" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147"/>
       <c r="D147" s="1" t="str" cm="1">
         <f t="array" ref="D147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -19452,15 +18801,15 @@
       </c>
       <c r="BN147" s="23"/>
     </row>
-    <row r="148" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148"/>
       <c r="BN148" s="23"/>
     </row>
-    <row r="149" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149"/>
       <c r="BN149" s="23"/>
     </row>
-    <row r="150" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150"/>
       <c r="D150" s="2" t="str" cm="1">
         <f t="array" ref="D150">Common_SourceData.Common_SourceData_DataScores_Scope3_Title()</f>
@@ -19468,7 +18817,7 @@
       </c>
       <c r="BN150" s="23"/>
     </row>
-    <row r="151" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151"/>
       <c r="D151" s="18" t="str" cm="1">
         <f t="array" ref="D151">Common_SourceData.Common_SourceData_DataScores_Scope3_Source()</f>
@@ -19476,11 +18825,11 @@
       </c>
       <c r="BN151" s="23"/>
     </row>
-    <row r="152" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152"/>
       <c r="BN152" s="23"/>
     </row>
-    <row r="153" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153"/>
       <c r="D153" s="21" t="s">
         <v>59</v>
@@ -19500,7 +18849,7 @@
       <c r="BL153" s="26"/>
       <c r="BM153" s="26"/>
     </row>
-    <row r="154" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154"/>
       <c r="D154" s="21" t="str" cm="1">
         <f t="array" ref="D154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -19522,7 +18871,7 @@
       <c r="BL154" s="26"/>
       <c r="BM154" s="26"/>
     </row>
-    <row r="155" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155"/>
       <c r="D155" s="21" t="str" cm="1">
         <f t="array" ref="D155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -19544,7 +18893,7 @@
       <c r="BL155" s="26"/>
       <c r="BM155" s="26"/>
     </row>
-    <row r="156" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156"/>
       <c r="D156" s="21" t="str" cm="1">
         <f t="array" ref="D156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -19555,7 +18904,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157"/>
       <c r="D157" s="21" t="str" cm="1">
         <f t="array" ref="D157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -19566,7 +18915,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158"/>
       <c r="D158" s="21" t="str" cm="1">
         <f t="array" ref="D158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -19577,34 +18926,34 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159"/>
     </row>
-    <row r="160" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160"/>
     </row>
-    <row r="161" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D161" s="2" t="str" cm="1">
         <f t="array" ref="D161">Common_SourceData.Common_SourceData_FracLEACH_Title()</f>
         <v>Fraction of N that is available for leaching and runoff</v>
       </c>
       <c r="E161" s="9"/>
     </row>
-    <row r="162" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D162" s="18" t="str" cm="1">
         <f t="array" ref="D162">Common_SourceData.Common_SourceData_FracLEACH_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
       <c r="E162" s="9"/>
     </row>
-    <row r="163" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D163" s="18" t="str" cm="1">
         <f t="array" ref="D163">Common_SourceData.Common_SourceData_FracLEACH_NIRReference()</f>
         <v>National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)</v>
       </c>
       <c r="E163" s="9"/>
     </row>
-    <row r="164" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D164" s="9" t="str" cm="1">
         <f t="array" ref="D164:E164">Common_SourceData.Common_SourceData_FracLEACH_Data()</f>
         <v>FracLEACH</v>
@@ -19613,17 +18962,17 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="165" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="BN165" s="23"/>
       <c r="BO165" s="23"/>
       <c r="BP165" s="23"/>
     </row>
-    <row r="166" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="BN166" s="23"/>
       <c r="BO166" s="23"/>
       <c r="BP166" s="23"/>
     </row>
-    <row r="167" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D167" s="2" t="str" cm="1">
         <f t="array" ref="D167">Common_SourceData.Common_SourceData_EFleach_Title()</f>
         <v>Emission factor for nitrogen leaching and runoff</v>
@@ -19632,7 +18981,7 @@
       <c r="BO167" s="23"/>
       <c r="BP167" s="23"/>
     </row>
-    <row r="168" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D168" s="18" t="str" cm="1">
         <f t="array" ref="D168">Common_SourceData.Common_SourceData_EFleach_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
@@ -19641,7 +18990,7 @@
       <c r="BO168" s="23"/>
       <c r="BP168" s="23"/>
     </row>
-    <row r="169" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D169" s="18" t="str" cm="1">
         <f t="array" ref="D169">Common_SourceData.Common_SourceData_EFleach_NIRReference()</f>
         <v>National Inventory Report Volume 1: Equation 3.D.B_10</v>
@@ -19650,7 +18999,7 @@
       <c r="BO169" s="23"/>
       <c r="BP169" s="23"/>
     </row>
-    <row r="170" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D170" s="1" t="str" cm="1">
         <f t="array" ref="D170:E170">Common_SourceData.Common_SourceData_EFleach_Data()</f>
         <v>EFleach</v>
@@ -19662,17 +19011,17 @@
       <c r="BO170" s="23"/>
       <c r="BP170" s="23"/>
     </row>
-    <row r="171" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="BN171" s="23"/>
       <c r="BO171" s="23"/>
       <c r="BP171" s="23"/>
     </row>
-    <row r="172" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="BN172" s="23"/>
       <c r="BO172" s="23"/>
       <c r="BP172" s="23"/>
     </row>
-    <row r="173" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D173" s="2" t="str" cm="1">
         <f t="array" ref="D173">Common_SourceData.Common_SourceData_DensityOfMethane_Title()</f>
         <v>p = density of methane</v>
@@ -19681,7 +19030,7 @@
       <c r="BO173" s="23"/>
       <c r="BP173" s="23"/>
     </row>
-    <row r="174" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D174" s="18" t="str" cm="1">
         <f t="array" ref="D174">Common_SourceData.Common_SourceData_DensityOfMethane_Source()</f>
         <v>National Inventory Report 2023 Volume 1: Equations 3.B.1a_2, 3.B.1c_2, 3.B.3_1, 3.B.4g_2</v>
@@ -19690,7 +19039,7 @@
       <c r="BO174" s="23"/>
       <c r="BP174" s="23"/>
     </row>
-    <row r="175" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D175" s="1" cm="1">
         <f t="array" ref="D175">Common_SourceData.Common_SourceData_DensityOfMethane_Data()</f>
         <v>0.6784</v>
@@ -19703,17 +19052,17 @@
       <c r="BO175" s="23"/>
       <c r="BP175" s="23"/>
     </row>
-    <row r="176" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="BN176" s="23"/>
       <c r="BO176" s="23"/>
       <c r="BP176" s="23"/>
     </row>
-    <row r="177" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="BN177" s="23"/>
       <c r="BO177" s="23"/>
       <c r="BP177" s="23"/>
     </row>
-    <row r="178" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D178" s="2" t="str" cm="1">
         <f t="array" ref="D178">Common_SourceData.Common_SourceData_EFN2O_Title()</f>
         <v>Nitrous oxide emission factors for inorganic fertiliser application</v>
@@ -19722,7 +19071,7 @@
       <c r="BO178" s="23"/>
       <c r="BP178" s="23"/>
     </row>
-    <row r="179" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D179" s="18" t="str" cm="1">
         <f t="array" ref="D179">Common_SourceData.Common_SourceData_EFN2O_Source()</f>
         <v>VEERG 2026: Table A.2.2.1</v>
@@ -19731,39 +19080,39 @@
       <c r="BO179" s="23"/>
       <c r="BP179" s="23"/>
     </row>
-    <row r="180" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D180" s="10" t="str" cm="1">
         <f t="array" ref="D180">Common_SourceData.Common_SourceData_EFN2O_Unit()</f>
         <v>(kg N2O-N / kg N</v>
       </c>
     </row>
-    <row r="181" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D181" s="27" t="str" cm="1">
         <f t="array" ref="D181:D185">Common_SourceData.Common_SourceData_EFN2O_Variation()</f>
         <v>VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="182" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D182" s="27" t="str">
         <v>Removed duplicate 'Aquaculture' row.</v>
       </c>
     </row>
-    <row r="183" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D183" s="27" t="str">
         <v>Removed asterisks to aid lookup.</v>
       </c>
     </row>
-    <row r="184" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D184" s="27" t="str">
         <v>Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.</v>
       </c>
     </row>
-    <row r="185" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D185" s="27" t="str">
         <v>Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup.</v>
       </c>
     </row>
-    <row r="186" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D186" s="21" t="s">
         <v>61</v>
       </c>
@@ -19780,7 +19129,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="187" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D187" s="21" t="str" cm="1">
         <f t="array" ref="D187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated pasture</v>
@@ -19802,7 +19151,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="188" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D188" s="21" t="str" cm="1">
         <f t="array" ref="D188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated crop</v>
@@ -19824,7 +19173,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="189" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D189" s="21" t="str" cm="1">
         <f t="array" ref="D189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -19846,7 +19195,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="190" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D190" s="21" t="str" cm="1">
         <f t="array" ref="D190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -19868,7 +19217,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="191" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D191" s="21" t="str" cm="1">
         <f t="array" ref="D191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (low rainfall)</v>
@@ -19890,7 +19239,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="192" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D192" s="21" t="str" cm="1">
         <f t="array" ref="D192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (high rainfall)</v>
@@ -19912,7 +19261,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="193" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D193" s="21" t="str" cm="1">
         <f t="array" ref="D193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Sugar</v>
@@ -19934,7 +19283,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="194" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D194" s="21" t="str" cm="1">
         <f t="array" ref="D194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Cotton</v>
@@ -19956,7 +19305,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="195" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D195" s="21" t="str" cm="1">
         <f t="array" ref="D195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Horticultural crops</v>
@@ -19978,7 +19327,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="196" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D196" s="21" t="str" cm="1">
         <f t="array" ref="D196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (continuous flooding)</v>
@@ -20000,7 +19349,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="197" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="197" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D197" s="21" t="str" cm="1">
         <f t="array" ref="D197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (single and multiple drainage, or alternate wetting and drying)</v>
@@ -20022,7 +19371,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="198" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="198" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D198" s="21" t="str" cm="1">
         <f t="array" ref="D198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Aquaculture</v>
@@ -20044,7 +19393,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="199" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="199" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D199" s="21" t="str" cm="1">
         <f t="array" ref="D199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Forestry</v>
@@ -20066,31 +19415,31 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="202" spans="4:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
+    <row r="202" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D202" s="2" t="str" cm="1">
         <f t="array" ref="D202">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Title()</f>
         <v>Emission factor for urine and dung deposited on pasture, range or paddock</v>
       </c>
     </row>
-    <row r="203" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="203" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D203" s="18" t="str" cm="1">
         <f t="array" ref="D203">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source()</f>
         <v>VEERG 2026: Table A.2.2.2</v>
       </c>
     </row>
-    <row r="204" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="204" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D204" s="27" t="str" cm="1">
         <f t="array" ref="D204">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Variation()</f>
         <v>VARIATION FROM SOURCE DATA: Changed 'Dry climate zones' to singular 'Dry climate zone' to aid lookup.</v>
       </c>
     </row>
-    <row r="205" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="205" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D205" s="10" t="str" cm="1">
         <f t="array" ref="D205">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="206" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="206" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D206" s="21" t="s">
         <v>32</v>
       </c>
@@ -20098,7 +19447,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="207" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="207" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D207" s="21" t="str" cm="1">
         <f t="array" ref="D207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -20108,7 +19457,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="208" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="208" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D208" s="1" t="str" cm="1">
         <f t="array" ref="D208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -20118,13 +19467,13 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="211" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="211" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D211" s="1" t="str" cm="1">
         <f t="array" ref="D211">Common_SourceData.Common_SourceData_MonthsToSeasons_Title()</f>
         <v>Months to Seasons Mapping</v>
       </c>
     </row>
-    <row r="212" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="212" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D212" s="21" t="s">
         <v>67</v>
       </c>
@@ -20132,7 +19481,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="213" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="213" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D213" s="21" t="str" cm="1">
         <f t="array" ref="D213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>January</v>
@@ -20142,7 +19491,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="214" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="214" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D214" s="1" t="str" cm="1">
         <f t="array" ref="D214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>February</v>
@@ -20152,7 +19501,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="215" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="215" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D215" s="1" t="str" cm="1">
         <f t="array" ref="D215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>March</v>
@@ -20162,7 +19511,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="216" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="216" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D216" s="1" t="str" cm="1">
         <f t="array" ref="D216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>April</v>
@@ -20172,7 +19521,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="217" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="217" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D217" s="1" t="str" cm="1">
         <f t="array" ref="D217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>May</v>
@@ -20182,7 +19531,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="218" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="218" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D218" s="1" t="str" cm="1">
         <f t="array" ref="D218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>June</v>
@@ -20192,7 +19541,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="219" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="219" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D219" s="1" t="str" cm="1">
         <f t="array" ref="D219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>July</v>
@@ -20202,7 +19551,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="220" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="220" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D220" s="1" t="str" cm="1">
         <f t="array" ref="D220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>August</v>
@@ -20212,7 +19561,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="221" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="221" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D221" s="1" t="str" cm="1">
         <f t="array" ref="D221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>September</v>
@@ -20222,7 +19571,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="222" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="222" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D222" s="1" t="str" cm="1">
         <f t="array" ref="D222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>October</v>
@@ -20232,7 +19581,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="223" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="223" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D223" s="1" t="str" cm="1">
         <f t="array" ref="D223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>November</v>
@@ -20242,7 +19591,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="224" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="224" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D224" s="1" t="str" cm="1">
         <f t="array" ref="D224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>December</v>
@@ -20252,25 +19601,25 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="227" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
+    <row r="227" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D227" s="2" t="str" cm="1">
         <f t="array" ref="D227">Common_SourceData.Common_SourceData_MCFTemperatureZone_Title()</f>
         <v>Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)</v>
       </c>
     </row>
-    <row r="228" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="228" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D228" s="18" t="str" cm="1">
         <f t="array" ref="D228">Common_SourceData.Common_SourceData_MCFTemperatureZone_Source()</f>
         <v>VEERG 2026: Table A.1.8.1</v>
       </c>
     </row>
-    <row r="229" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="229" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D229" s="27" t="str" cm="1">
         <f t="array" ref="D229">Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation()</f>
         <v>VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.</v>
       </c>
     </row>
-    <row r="231" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="231" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D231" s="21" t="s">
         <v>69</v>
       </c>
@@ -20320,7 +19669,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="232" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="232" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D232" s="21" t="str" cm="1">
         <f t="array" ref="D232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -20386,7 +19735,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="233" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D233" s="1" t="str" cm="1">
         <f t="array" ref="D233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -20452,7 +19801,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="234" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="234" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D234" s="1" t="str" cm="1">
         <f t="array" ref="D234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -20518,7 +19867,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="235" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="235" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D235" s="1" t="str" cm="1">
         <f t="array" ref="D235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -20584,7 +19933,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="236" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="236" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D236" s="1" t="str" cm="1">
         <f t="array" ref="D236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -20650,7 +19999,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="237" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="237" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D237" s="1" t="str" cm="1">
         <f t="array" ref="D237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20716,7 +20065,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="238" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="238" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D238" s="1" t="str" cm="1">
         <f t="array" ref="D238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20782,7 +20131,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="239" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="239" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D239" s="1" t="str" cm="1">
         <f t="array" ref="D239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20848,7 +20197,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="240" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D240" s="1" t="str" cm="1">
         <f t="array" ref="D240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20914,7 +20263,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="241" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="241" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D241" s="1" t="str" cm="1">
         <f t="array" ref="D241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20980,7 +20329,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="242" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="242" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D242" s="1" t="str" cm="1">
         <f t="array" ref="D242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -21046,7 +20395,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="243" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="243" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D243" s="1" t="str" cm="1">
         <f t="array" ref="D243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -21112,7 +20461,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="244" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D244" s="1" t="str" cm="1">
         <f t="array" ref="D244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -21178,7 +20527,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="245" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="245" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D245" s="1" t="str" cm="1">
         <f t="array" ref="D245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -21244,7 +20593,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="246" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="246" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D246" s="1" t="str" cm="1">
         <f t="array" ref="D246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -21310,7 +20659,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="247" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="247" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D247" s="1" t="str" cm="1">
         <f t="array" ref="D247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -21376,7 +20725,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="248" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="248" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D248" s="1" t="str" cm="1">
         <f t="array" ref="D248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -21442,7 +20791,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="249" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="249" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D249" s="1" t="str" cm="1">
         <f t="array" ref="D249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -21508,7 +20857,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="250" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="250" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D250" s="1" t="str" cm="1">
         <f t="array" ref="D250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -21574,31 +20923,31 @@
         <v>28</v>
       </c>
     </row>
-    <row r="253" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
+    <row r="253" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D253" s="2" t="str" cm="1">
         <f t="array" ref="D253">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Title()</f>
         <v>Emission factor for organic fertiliser and crop residues returned to the soil</v>
       </c>
     </row>
-    <row r="254" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="254" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D254" s="18" t="str" cm="1">
         <f t="array" ref="D254">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source()</f>
         <v>VEERG 2026: Table A.2.1.4</v>
       </c>
     </row>
-    <row r="255" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="255" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D255" s="1" t="str" cm="1">
         <f t="array" ref="D255">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable()</f>
         <v>EFNi &amp; EFN2Oi</v>
       </c>
     </row>
-    <row r="256" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="256" spans="4:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D256" s="10" t="str" cm="1">
         <f t="array" ref="D256">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="257" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="257" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D257" s="21" t="s">
         <v>85</v>
       </c>
@@ -21606,7 +20955,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="258" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="258" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D258" s="21" t="str" cm="1">
         <f t="array" ref="D258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -21616,7 +20965,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="259" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="259" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D259" s="1" t="str" cm="1">
         <f t="array" ref="D259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -21626,41 +20975,41 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="263" spans="4:66" ht="20" x14ac:dyDescent="0.25" customHeight="1">
+    <row r="263" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D263" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="264" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="264" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D264" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="265" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="265" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D265" s="21" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="E265" s="21" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="F265" s="21" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="G265" s="21" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="V265" s="1"/>
       <c r="BN265" s="23"/>
     </row>
-    <row r="266" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="266" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D266" s="21" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="E266" s="21" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="F266" s="21" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="G266" s="21">
         <v>5</v>
@@ -21668,15 +21017,15 @@
       <c r="V266" s="1"/>
       <c r="BN266" s="23"/>
     </row>
-    <row r="267" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="267" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D267" s="21" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="E267" s="21" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="F267" s="21" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="G267" s="21">
         <v>4</v>
@@ -21684,15 +21033,15 @@
       <c r="V267" s="1"/>
       <c r="BN267" s="23"/>
     </row>
-    <row r="268" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="268" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D268" s="21" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="E268" s="21" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="F268" s="21" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="G268" s="21">
         <v>3</v>
@@ -21700,15 +21049,15 @@
       <c r="V268" s="1"/>
       <c r="BN268" s="23"/>
     </row>
-    <row r="269" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="269" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D269" s="21" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="E269" s="21" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="F269" s="21" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="G269" s="21">
         <v>2</v>
@@ -21716,15 +21065,15 @@
       <c r="V269" s="1"/>
       <c r="BN269" s="23"/>
     </row>
-    <row r="270" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="270" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D270" s="21" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="E270" s="21" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="F270" s="21" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="G270" s="21">
         <v>1</v>
@@ -21732,36 +21081,36 @@
       <c r="V270" s="1"/>
       <c r="BN270" s="23"/>
     </row>
-    <row r="273" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="273" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D273" s="1" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="274" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="274" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D274" s="21" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="E274" s="21" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="F274" s="21" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="G274" s="21" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="V274" s="1"/>
       <c r="BN274" s="23"/>
     </row>
-    <row r="275" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="275" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D275" s="21" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="E275" s="21" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="F275" s="21" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="G275" s="21">
         <v>5</v>
@@ -21769,15 +21118,15 @@
       <c r="V275" s="1"/>
       <c r="BN275" s="23"/>
     </row>
-    <row r="276" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="276" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D276" s="21" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="E276" s="21" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="F276" s="21" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="G276" s="21">
         <v>4</v>
@@ -21785,15 +21134,15 @@
       <c r="V276" s="1"/>
       <c r="BN276" s="23"/>
     </row>
-    <row r="277" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="277" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D277" s="21" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="E277" s="21" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="F277" s="21" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="G277" s="21">
         <v>3</v>
@@ -21801,15 +21150,15 @@
       <c r="V277" s="1"/>
       <c r="BN277" s="23"/>
     </row>
-    <row r="278" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="278" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D278" s="21" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="E278" s="21" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="F278" s="21" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="G278" s="21">
         <v>2</v>
@@ -21817,15 +21166,15 @@
       <c r="V278" s="1"/>
       <c r="BN278" s="23"/>
     </row>
-    <row r="279" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="279" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D279" s="21" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="E279" s="21" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="F279" s="21" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="G279" s="21">
         <v>1</v>
@@ -21833,36 +21182,36 @@
       <c r="V279" s="1"/>
       <c r="BN279" s="23"/>
     </row>
-    <row r="282" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="282" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D282" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="283" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="283" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D283" s="21" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="E283" s="21" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="F283" s="21" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="G283" s="21" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="V283" s="1"/>
       <c r="BN283" s="23"/>
     </row>
-    <row r="284" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="284" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D284" s="21" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="E284" s="21" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="F284" s="21" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="G284" s="21">
         <v>5</v>
@@ -21870,15 +21219,15 @@
       <c r="V284" s="1"/>
       <c r="BN284" s="23"/>
     </row>
-    <row r="285" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="285" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D285" s="21" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="E285" s="21" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="F285" s="21" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="G285" s="21">
         <v>4</v>
@@ -21886,15 +21235,15 @@
       <c r="V285" s="1"/>
       <c r="BN285" s="23"/>
     </row>
-    <row r="286" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="286" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D286" s="21" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="E286" s="21" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="F286" s="21" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="G286" s="21">
         <v>3</v>
@@ -21902,15 +21251,15 @@
       <c r="V286" s="1"/>
       <c r="BN286" s="23"/>
     </row>
-    <row r="287" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="287" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D287" s="21" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="E287" s="21" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="F287" s="21" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="G287" s="21">
         <v>2</v>
@@ -21918,15 +21267,15 @@
       <c r="V287" s="1"/>
       <c r="BN287" s="23"/>
     </row>
-    <row r="288" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="288" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D288" s="21" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="E288" s="21" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="F288" s="21" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="G288" s="21">
         <v>1</v>
@@ -21934,36 +21283,36 @@
       <c r="V288" s="1"/>
       <c r="BN288" s="23"/>
     </row>
-    <row r="291" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="291" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D291" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="292" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="292" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D292" s="21" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="E292" s="21" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="F292" s="21" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="G292" s="21" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="V292" s="1"/>
       <c r="BN292" s="23"/>
     </row>
-    <row r="293" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="293" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D293" s="21" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="E293" s="21" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="F293" s="21" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="G293" s="21">
         <v>5</v>
@@ -21971,15 +21320,15 @@
       <c r="V293" s="1"/>
       <c r="BN293" s="23"/>
     </row>
-    <row r="294" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="294" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D294" s="21" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="E294" s="21" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="F294" s="21" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="G294" s="21">
         <v>4</v>
@@ -21987,15 +21336,15 @@
       <c r="V294" s="1"/>
       <c r="BN294" s="23"/>
     </row>
-    <row r="295" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="295" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D295" s="21" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="E295" s="21" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="F295" s="21" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="G295" s="21">
         <v>3</v>
@@ -22003,15 +21352,15 @@
       <c r="V295" s="1"/>
       <c r="BN295" s="23"/>
     </row>
-    <row r="296" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="296" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D296" s="21" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="E296" s="21" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="F296" s="21" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="G296" s="21">
         <v>2</v>
@@ -22019,15 +21368,15 @@
       <c r="V296" s="1"/>
       <c r="BN296" s="23"/>
     </row>
-    <row r="297" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
+    <row r="297" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D297" s="21" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="E297" s="21" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="F297" s="21" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="G297" s="21">
         <v>1</v>
@@ -22069,26 +21418,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -22283,6 +21612,26 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
@@ -22292,9 +21641,20 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -22311,20 +21671,9 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>